--- a/test-cases-reports/selinium-test/selenium_web_report.xlsx
+++ b/test-cases-reports/selinium-test/selenium_web_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="475">
   <si>
     <t>STRIVECAMPUS WEB E2E TEST SUMMARY</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>90.80s</t>
+    <t>90.91s</t>
   </si>
   <si>
     <t>Deployable Status</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>4.38s</t>
+    <t>4.27s</t>
   </si>
   <si>
     <t>-</t>
@@ -101,24 +101,24 @@
     <t>UI002: Splash Screen app name display</t>
   </si>
   <si>
+    <t>0.01s</t>
+  </si>
+  <si>
+    <t>UI003: Splash Screen tagline text</t>
+  </si>
+  <si>
+    <t>0.03s</t>
+  </si>
+  <si>
+    <t>UI004: Onboarding page 1 title display</t>
+  </si>
+  <si>
     <t>0.02s</t>
   </si>
   <si>
-    <t>UI003: Splash Screen tagline text</t>
-  </si>
-  <si>
-    <t>UI004: Onboarding page 1 title display</t>
-  </si>
-  <si>
-    <t>0.03s</t>
-  </si>
-  <si>
     <t>UI005: Onboarding page 1 description text layout</t>
   </si>
   <si>
-    <t>0.01s</t>
-  </si>
-  <si>
     <t>UI006: Onboarding page 1 button text</t>
   </si>
   <si>
@@ -143,412 +143,406 @@
     <t>UI012: Onboarding page 3 title display</t>
   </si>
   <si>
+    <t>UI013: Onboarding page 3 description text layout</t>
+  </si>
+  <si>
+    <t>UI014: Onboarding page 3 Get Started button layout</t>
+  </si>
+  <si>
+    <t>UI015: Login Screen background card shape</t>
+  </si>
+  <si>
+    <t>4.74s</t>
+  </si>
+  <si>
+    <t>UI016: Login screen email input container styling</t>
+  </si>
+  <si>
+    <t>4.10s</t>
+  </si>
+  <si>
+    <t>UI017: Login screen password input container styling</t>
+  </si>
+  <si>
+    <t>UI018: Login button background design</t>
+  </si>
+  <si>
+    <t>UI019: Login header branding typography</t>
+  </si>
+  <si>
+    <t>UI020: Register screen fields typography and spacing</t>
+  </si>
+  <si>
+    <t>2.16s</t>
+  </si>
+  <si>
+    <t>UI021: Register button border radius</t>
+  </si>
+  <si>
+    <t>0.04s</t>
+  </si>
+  <si>
+    <t>UI022: Register footer link styling</t>
+  </si>
+  <si>
+    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
+  </si>
+  <si>
+    <t>UI024: Dashboard header title formatting</t>
+  </si>
+  <si>
+    <t>UI025: Theme toggler button visual contrast</t>
+  </si>
+  <si>
+    <t>UI026: Light mode dashboard theme colors</t>
+  </si>
+  <si>
+    <t>UI027: Dark mode theme transition styles</t>
+  </si>
+  <si>
+    <t>0.00s</t>
+  </si>
+  <si>
+    <t>UI028: Profile screen user avatar size layout</t>
+  </si>
+  <si>
+    <t>UI029: Test session card border margins</t>
+  </si>
+  <si>
+    <t>UI030: AI Feedback dialog spacing layout</t>
+  </si>
+  <si>
+    <t>UI031: Onboarding page dot animation transition duration checks</t>
+  </si>
+  <si>
+    <t>UI032: Onboarding skip button typography style properties matching</t>
+  </si>
+  <si>
+    <t>UI033: Splash logo container dimensions ratio verification</t>
+  </si>
+  <si>
+    <t>UI034: Splash loader indicator circular progress thickness details</t>
+  </si>
+  <si>
+    <t>UI035: Authentication textfield error messaging text font style alignment</t>
+  </si>
+  <si>
+    <t>UI036: Login submit button responsive hover opacity changes</t>
+  </si>
+  <si>
+    <t>UI037: Register page input padding offsets consistency checks</t>
+  </si>
+  <si>
+    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
+  </si>
+  <si>
+    <t>UI039: Dark mode active body background color matching parameters</t>
+  </si>
+  <si>
+    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
+  </si>
+  <si>
+    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
+  </si>
+  <si>
+    <t>UI042: AI mock interview feedback container border lines styling</t>
+  </si>
+  <si>
+    <t>UI043: Chatbot user response chat bubble alignment properties</t>
+  </si>
+  <si>
+    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
+  </si>
+  <si>
+    <t>UI045: Profile user name typography scale weight and contrast check</t>
+  </si>
+  <si>
+    <t>UI046: Settings theme toggle switch active color verification parameters</t>
+  </si>
+  <si>
+    <t>UI047: Onboarding title layout alignment centered checking</t>
+  </si>
+  <si>
+    <t>UI048: Textfields active cursor focus color validation</t>
+  </si>
+  <si>
+    <t>UI049: Error messages warning badge layout constraints</t>
+  </si>
+  <si>
+    <t>UI050: App notification icon badges count scaling parameters</t>
+  </si>
+  <si>
+    <t>UI051: Profile card statistics counts label typography sizing</t>
+  </si>
+  <si>
+    <t>UI052: HR round option button icons visual alignment</t>
+  </si>
+  <si>
+    <t>UI053: Tech round option card layout spacing check</t>
+  </si>
+  <si>
+    <t>UI054: Aptitude test category cards layout alignment parameters</t>
+  </si>
+  <si>
+    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
+  </si>
+  <si>
+    <t>UI056: Alert dialog box overlay transparency index verification</t>
+  </si>
+  <si>
+    <t>UI057: Groq feedback score badge layout circular border alignment</t>
+  </si>
+  <si>
+    <t>UI058: Speech input icon active mic glow styling parameters</t>
+  </si>
+  <si>
+    <t>UI059: Dark theme input borders contrast rating validation</t>
+  </si>
+  <si>
+    <t>UI060: Onboarding next button icon placement side margins checking</t>
+  </si>
+  <si>
+    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
+  </si>
+  <si>
+    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
+  </si>
+  <si>
+    <t>UI063: Aptitude quiz progress bar line color status verification</t>
+  </si>
+  <si>
+    <t>UI064: Custom card elements scaling values on larger resolutions</t>
+  </si>
+  <si>
+    <t>UI065: Custom list dividers height thickness checking parameters</t>
+  </si>
+  <si>
+    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
+  </si>
+  <si>
+    <t>UI067: App header icon menu spacing and positioning specifications</t>
+  </si>
+  <si>
+    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
+  </si>
+  <si>
+    <t>UI069: Text input fields placeholder character font styling rules</t>
+  </si>
+  <si>
+    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
+  </si>
+  <si>
+    <t>UI071: Profile credentials edit inputs layout alignment values</t>
+  </si>
+  <si>
+    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
+  </si>
+  <si>
+    <t>UI073: Custom snackbar popup notifications container design styles</t>
+  </si>
+  <si>
+    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
+  </si>
+  <si>
+    <t>UI075: Webapp container shadow outline styling matching specifications</t>
+  </si>
+  <si>
+    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
+  </si>
+  <si>
+    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
+  </si>
+  <si>
+    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
+  </si>
+  <si>
+    <t>UI079: Chat suggestion chips outline border thickness details</t>
+  </si>
+  <si>
+    <t>UI080: Settings section headers font size transformations checking</t>
+  </si>
+  <si>
+    <t>UI081: Login forgot password link visual underline toggle checks</t>
+  </si>
+  <si>
+    <t>UI082: Register legal policies agreements text box layouts checks</t>
+  </si>
+  <si>
+    <t>UI083: Placement details document viewer layout padding verification</t>
+  </si>
+  <si>
+    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
+  </si>
+  <si>
+    <t>UI085: Custom dropdown selectors hover outline border width check</t>
+  </si>
+  <si>
+    <t>UI086: Dialog confirmations layouts check icon centering values</t>
+  </si>
+  <si>
+    <t>UI087: Chat input field icons click state opacity level updates</t>
+  </si>
+  <si>
+    <t>UI088: User avatar badge active placement online status display</t>
+  </si>
+  <si>
+    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
+  </si>
+  <si>
+    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
+  </si>
+  <si>
+    <t>UI091: Aptitude result summary page visual headers scaling check</t>
+  </si>
+  <si>
+    <t>UI092: AI feedback details accordion expand collapse height values</t>
+  </si>
+  <si>
+    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
+  </si>
+  <si>
+    <t>UI094: Navigation bar labels selected font color parameter checks</t>
+  </si>
+  <si>
+    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
+  </si>
+  <si>
+    <t>UI096: Settings section divider margins layout alignment specifications</t>
+  </si>
+  <si>
+    <t>UI097: Placement company filters panel layout drawer design styles</t>
+  </si>
+  <si>
+    <t>UI098: Notification toggle buttons sliding animation duration check</t>
+  </si>
+  <si>
+    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
+  </si>
+  <si>
+    <t>UI100: Auth form title secondary text decoration attributes check</t>
+  </si>
+  <si>
+    <t>UI101: Chat message time badge indicator font weight properties</t>
+  </si>
+  <si>
+    <t>UI102: Profile page history entries list spacing parameters</t>
+  </si>
+  <si>
+    <t>UI103: Feedback text block alignment rules inside cards check</t>
+  </si>
+  <si>
+    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
+  </si>
+  <si>
+    <t>UI105: Interview review card layout horizontal borders constraint</t>
+  </si>
+  <si>
+    <t>UI106: Light mode inputs focus border shadow layout checks</t>
+  </si>
+  <si>
+    <t>UI107: Settings clear cache option text style parameters matching</t>
+  </si>
+  <si>
+    <t>UI108: Placement job card badges layout visual check rules</t>
+  </si>
+  <si>
+    <t>UI109: Speech processing overlay spinner styling visual verification</t>
+  </si>
+  <si>
+    <t>UI110: Test report dashboard header title color styling verification</t>
+  </si>
+  <si>
+    <t>FN001: Load app page successfully</t>
+  </si>
+  <si>
+    <t>4.14s</t>
+  </si>
+  <si>
+    <t>FN002: Click Next to access page 2</t>
+  </si>
+  <si>
+    <t>2.10s</t>
+  </si>
+  <si>
+    <t>FN003: Click Next to access page 3</t>
+  </si>
+  <si>
+    <t>FN004: Skip button bypasses onboarding screen</t>
+  </si>
+  <si>
+    <t>6.21s</t>
+  </si>
+  <si>
+    <t>FN005: Complete onboarding and transition to authentication page</t>
+  </si>
+  <si>
     <t>2.06s</t>
   </si>
   <si>
-    <t>UI013: Onboarding page 3 description text layout</t>
-  </si>
-  <si>
-    <t>UI014: Onboarding page 3 Get Started button layout</t>
-  </si>
-  <si>
-    <t>UI015: Login Screen background card shape</t>
-  </si>
-  <si>
-    <t>4.18s</t>
-  </si>
-  <si>
-    <t>UI016: Login screen email input container styling</t>
-  </si>
-  <si>
-    <t>4.11s</t>
-  </si>
-  <si>
-    <t>UI017: Login screen password input container styling</t>
-  </si>
-  <si>
-    <t>UI018: Login button background design</t>
-  </si>
-  <si>
-    <t>0.00s</t>
-  </si>
-  <si>
-    <t>UI019: Login header branding typography</t>
-  </si>
-  <si>
-    <t>UI020: Register screen fields typography and spacing</t>
-  </si>
-  <si>
-    <t>2.05s</t>
-  </si>
-  <si>
-    <t>UI021: Register button border radius</t>
-  </si>
-  <si>
-    <t>UI022: Register footer link styling</t>
-  </si>
-  <si>
-    <t>0.04s</t>
-  </si>
-  <si>
-    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
-  </si>
-  <si>
-    <t>UI024: Dashboard header title formatting</t>
-  </si>
-  <si>
-    <t>UI025: Theme toggler button visual contrast</t>
-  </si>
-  <si>
-    <t>UI026: Light mode dashboard theme colors</t>
-  </si>
-  <si>
-    <t>UI027: Dark mode theme transition styles</t>
-  </si>
-  <si>
-    <t>UI028: Profile screen user avatar size layout</t>
-  </si>
-  <si>
-    <t>UI029: Test session card border margins</t>
-  </si>
-  <si>
-    <t>UI030: AI Feedback dialog spacing layout</t>
-  </si>
-  <si>
-    <t>UI031: Onboarding page dot animation transition duration checks</t>
-  </si>
-  <si>
-    <t>UI032: Onboarding skip button typography style properties matching</t>
-  </si>
-  <si>
-    <t>UI033: Splash logo container dimensions ratio verification</t>
-  </si>
-  <si>
-    <t>UI034: Splash loader indicator circular progress thickness details</t>
-  </si>
-  <si>
-    <t>UI035: Authentication textfield error messaging text font style alignment</t>
-  </si>
-  <si>
-    <t>UI036: Login submit button responsive hover opacity changes</t>
-  </si>
-  <si>
-    <t>UI037: Register page input padding offsets consistency checks</t>
-  </si>
-  <si>
-    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
-  </si>
-  <si>
-    <t>UI039: Dark mode active body background color matching parameters</t>
-  </si>
-  <si>
-    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
-  </si>
-  <si>
-    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
-  </si>
-  <si>
-    <t>UI042: AI mock interview feedback container border lines styling</t>
-  </si>
-  <si>
-    <t>UI043: Chatbot user response chat bubble alignment properties</t>
-  </si>
-  <si>
-    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
-  </si>
-  <si>
-    <t>UI045: Profile user name typography scale weight and contrast check</t>
-  </si>
-  <si>
-    <t>UI046: Settings theme toggle switch active color verification parameters</t>
-  </si>
-  <si>
-    <t>UI047: Onboarding title layout alignment centered checking</t>
-  </si>
-  <si>
-    <t>UI048: Textfields active cursor focus color validation</t>
-  </si>
-  <si>
-    <t>UI049: Error messages warning badge layout constraints</t>
-  </si>
-  <si>
-    <t>UI050: App notification icon badges count scaling parameters</t>
-  </si>
-  <si>
-    <t>UI051: Profile card statistics counts label typography sizing</t>
-  </si>
-  <si>
-    <t>UI052: HR round option button icons visual alignment</t>
-  </si>
-  <si>
-    <t>UI053: Tech round option card layout spacing check</t>
-  </si>
-  <si>
-    <t>UI054: Aptitude test category cards layout alignment parameters</t>
-  </si>
-  <si>
-    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
-  </si>
-  <si>
-    <t>UI056: Alert dialog box overlay transparency index verification</t>
-  </si>
-  <si>
-    <t>UI057: Groq feedback score badge layout circular border alignment</t>
-  </si>
-  <si>
-    <t>UI058: Speech input icon active mic glow styling parameters</t>
-  </si>
-  <si>
-    <t>UI059: Dark theme input borders contrast rating validation</t>
-  </si>
-  <si>
-    <t>UI060: Onboarding next button icon placement side margins checking</t>
-  </si>
-  <si>
-    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
-  </si>
-  <si>
-    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
-  </si>
-  <si>
-    <t>UI063: Aptitude quiz progress bar line color status verification</t>
-  </si>
-  <si>
-    <t>UI064: Custom card elements scaling values on larger resolutions</t>
-  </si>
-  <si>
-    <t>UI065: Custom list dividers height thickness checking parameters</t>
-  </si>
-  <si>
-    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
-  </si>
-  <si>
-    <t>UI067: App header icon menu spacing and positioning specifications</t>
-  </si>
-  <si>
-    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
-  </si>
-  <si>
-    <t>UI069: Text input fields placeholder character font styling rules</t>
-  </si>
-  <si>
-    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
-  </si>
-  <si>
-    <t>UI071: Profile credentials edit inputs layout alignment values</t>
-  </si>
-  <si>
-    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
-  </si>
-  <si>
-    <t>UI073: Custom snackbar popup notifications container design styles</t>
-  </si>
-  <si>
-    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
-  </si>
-  <si>
-    <t>UI075: Webapp container shadow outline styling matching specifications</t>
-  </si>
-  <si>
-    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
-  </si>
-  <si>
-    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
-  </si>
-  <si>
-    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
-  </si>
-  <si>
-    <t>UI079: Chat suggestion chips outline border thickness details</t>
-  </si>
-  <si>
-    <t>UI080: Settings section headers font size transformations checking</t>
-  </si>
-  <si>
-    <t>UI081: Login forgot password link visual underline toggle checks</t>
-  </si>
-  <si>
-    <t>UI082: Register legal policies agreements text box layouts checks</t>
-  </si>
-  <si>
-    <t>UI083: Placement details document viewer layout padding verification</t>
-  </si>
-  <si>
-    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
-  </si>
-  <si>
-    <t>UI085: Custom dropdown selectors hover outline border width check</t>
-  </si>
-  <si>
-    <t>UI086: Dialog confirmations layouts check icon centering values</t>
-  </si>
-  <si>
-    <t>UI087: Chat input field icons click state opacity level updates</t>
-  </si>
-  <si>
-    <t>UI088: User avatar badge active placement online status display</t>
-  </si>
-  <si>
-    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
-  </si>
-  <si>
-    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
-  </si>
-  <si>
-    <t>UI091: Aptitude result summary page visual headers scaling check</t>
-  </si>
-  <si>
-    <t>UI092: AI feedback details accordion expand collapse height values</t>
-  </si>
-  <si>
-    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
-  </si>
-  <si>
-    <t>UI094: Navigation bar labels selected font color parameter checks</t>
-  </si>
-  <si>
-    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
-  </si>
-  <si>
-    <t>UI096: Settings section divider margins layout alignment specifications</t>
-  </si>
-  <si>
-    <t>UI097: Placement company filters panel layout drawer design styles</t>
-  </si>
-  <si>
-    <t>UI098: Notification toggle buttons sliding animation duration check</t>
-  </si>
-  <si>
-    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
-  </si>
-  <si>
-    <t>UI100: Auth form title secondary text decoration attributes check</t>
-  </si>
-  <si>
-    <t>UI101: Chat message time badge indicator font weight properties</t>
-  </si>
-  <si>
-    <t>UI102: Profile page history entries list spacing parameters</t>
-  </si>
-  <si>
-    <t>UI103: Feedback text block alignment rules inside cards check</t>
-  </si>
-  <si>
-    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
-  </si>
-  <si>
-    <t>UI105: Interview review card layout horizontal borders constraint</t>
-  </si>
-  <si>
-    <t>UI106: Light mode inputs focus border shadow layout checks</t>
-  </si>
-  <si>
-    <t>UI107: Settings clear cache option text style parameters matching</t>
-  </si>
-  <si>
-    <t>UI108: Placement job card badges layout visual check rules</t>
-  </si>
-  <si>
-    <t>UI109: Speech processing overlay spinner styling visual verification</t>
-  </si>
-  <si>
-    <t>UI110: Test report dashboard header title color styling verification</t>
-  </si>
-  <si>
-    <t>FN001: Load app page successfully</t>
+    <t>FN006: Select register navigation path</t>
+  </si>
+  <si>
+    <t>FN007: Register a new account with valid unique details</t>
+  </si>
+  <si>
+    <t>2.08s</t>
+  </si>
+  <si>
+    <t>FN008: Submit register account credentials to Firestore</t>
+  </si>
+  <si>
+    <t>FN009: Verify user main dashboard is successfully loaded</t>
+  </si>
+  <si>
+    <t>0.51s</t>
+  </si>
+  <si>
+    <t>FN010: Navigate to Aptitude &amp; Technical Tests tab</t>
+  </si>
+  <si>
+    <t>FN011: Render Aptitude list categories</t>
+  </si>
+  <si>
+    <t>FN012: Switch tests list to Technical category</t>
+  </si>
+  <si>
+    <t>FN013: Switch tests list to HR category</t>
+  </si>
+  <si>
+    <t>FN014: Select HR Mock Interview session card</t>
+  </si>
+  <si>
+    <t>2.04s</t>
+  </si>
+  <si>
+    <t>FN015: Set question counts in configuration card</t>
+  </si>
+  <si>
+    <t>FN016: Launch the HR Interview round</t>
+  </si>
+  <si>
+    <t>FN017: Wait for AI Interviewer to load question details</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>FN018: Retrieve visual text of mock question</t>
+  </si>
+  <si>
+    <t>FN019: Input answer to the generated mock question</t>
   </si>
   <si>
     <t>4.13s</t>
   </si>
   <si>
-    <t>FN002: Click Next to access page 2</t>
-  </si>
-  <si>
-    <t>FN003: Click Next to access page 3</t>
-  </si>
-  <si>
-    <t>2.04s</t>
-  </si>
-  <si>
-    <t>FN004: Skip button bypasses onboarding screen</t>
-  </si>
-  <si>
-    <t>6.18s</t>
-  </si>
-  <si>
-    <t>FN005: Complete onboarding and transition to authentication page</t>
-  </si>
-  <si>
-    <t>2.08s</t>
-  </si>
-  <si>
-    <t>FN006: Select register navigation path</t>
-  </si>
-  <si>
-    <t>2.09s</t>
-  </si>
-  <si>
-    <t>FN007: Register a new account with valid unique details</t>
-  </si>
-  <si>
-    <t>FN008: Submit register account credentials to Firestore</t>
-  </si>
-  <si>
-    <t>FN009: Verify user main dashboard is successfully loaded</t>
-  </si>
-  <si>
-    <t>0.53s</t>
-  </si>
-  <si>
-    <t>FN010: Navigate to Aptitude &amp; Technical Tests tab</t>
-  </si>
-  <si>
-    <t>2.11s</t>
-  </si>
-  <si>
-    <t>FN011: Render Aptitude list categories</t>
-  </si>
-  <si>
-    <t>FN012: Switch tests list to Technical category</t>
-  </si>
-  <si>
-    <t>FN013: Switch tests list to HR category</t>
-  </si>
-  <si>
-    <t>FN014: Select HR Mock Interview session card</t>
-  </si>
-  <si>
-    <t>FN015: Set question counts in configuration card</t>
-  </si>
-  <si>
-    <t>FN016: Launch the HR Interview round</t>
-  </si>
-  <si>
-    <t>2.10s</t>
-  </si>
-  <si>
-    <t>FN017: Wait for AI Interviewer to load question details</t>
-  </si>
-  <si>
-    <t>1.51s</t>
-  </si>
-  <si>
-    <t>FN018: Retrieve visual text of mock question</t>
-  </si>
-  <si>
-    <t>FN019: Input answer to the generated mock question</t>
-  </si>
-  <si>
-    <t>4.15s</t>
-  </si>
-  <si>
     <t>FN020: Submit answer to AI evaluation engine</t>
   </si>
   <si>
     <t>FN021: Retrieve feedback score from Groq API response</t>
   </si>
   <si>
-    <t>2.02s</t>
+    <t>2.01s</t>
   </si>
   <si>
     <t>FN022: Display evaluation advice layout</t>
@@ -566,7 +560,7 @@
     <t>FN026: Enter custom text message in chat query input</t>
   </si>
   <si>
-    <t>4.19s</t>
+    <t>4.12s</t>
   </si>
   <si>
     <t>FN027: Receive chatbot answer correctly</t>
@@ -758,12 +752,21 @@
     <t>FN088: Career openings criteria checks matches candidate GPA rating</t>
   </si>
   <si>
+    <t>0.06s</t>
+  </si>
+  <si>
     <t>FN089: Interactive notifications triggers direct deep links</t>
   </si>
   <si>
+    <t>0.21s</t>
+  </si>
+  <si>
     <t>FN090: Placement opening application submits file uploads checks</t>
   </si>
   <si>
+    <t>0.05s</t>
+  </si>
+  <si>
     <t>FN091: Aptitude test summary shows score history visual graphs</t>
   </si>
   <si>
@@ -815,6 +818,9 @@
     <t>FN107: Settings clear logs deletes internal session records</t>
   </si>
   <si>
+    <t>0.09s</t>
+  </si>
+  <si>
     <t>FN108: Job card bookmarks actions updates quick save collections</t>
   </si>
   <si>
@@ -1139,9 +1145,6 @@
     <t>VL003: Register user blank email validation toast</t>
   </si>
   <si>
-    <t>0.13s</t>
-  </si>
-  <si>
     <t>VL004: Register user invalid email format display</t>
   </si>
   <si>
@@ -1157,16 +1160,16 @@
     <t>VL008: Submit empty text answer to HR Interviewer returns validation message</t>
   </si>
   <si>
+    <t>VL009: Check question counts upper limit constraint</t>
+  </si>
+  <si>
+    <t>VL010: Check question counts lower limit constraint</t>
+  </si>
+  <si>
+    <t>VL011: Submit aptitude test with no questions answered displays alert dialog</t>
+  </si>
+  <si>
     <t>0.12s</t>
-  </si>
-  <si>
-    <t>VL009: Check question counts upper limit constraint</t>
-  </si>
-  <si>
-    <t>VL010: Check question counts lower limit constraint</t>
-  </si>
-  <si>
-    <t>VL011: Submit aptitude test with no questions answered displays alert dialog</t>
   </si>
   <si>
     <t>VL012: Save offline test session log validation check</t>
@@ -2125,7 +2128,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>27</v>
@@ -2136,13 +2139,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>27</v>
@@ -2153,13 +2156,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>27</v>
@@ -2176,7 +2179,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>27</v>
@@ -2193,7 +2196,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>27</v>
@@ -2244,7 +2247,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>27</v>
@@ -2261,7 +2264,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>27</v>
@@ -2278,7 +2281,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>27</v>
@@ -2289,13 +2292,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>27</v>
@@ -2306,7 +2309,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>25</v>
@@ -2323,13 +2326,13 @@
         <v>7</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>27</v>
@@ -2340,13 +2343,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>49</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>27</v>
@@ -2357,13 +2360,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>27</v>
@@ -2374,13 +2377,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>27</v>
@@ -2391,13 +2394,13 @@
         <v>7</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>27</v>
@@ -2408,13 +2411,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>27</v>
@@ -2425,13 +2428,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>27</v>
@@ -2442,13 +2445,13 @@
         <v>7</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>27</v>
@@ -2459,13 +2462,13 @@
         <v>7</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>27</v>
@@ -2476,13 +2479,13 @@
         <v>7</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>27</v>
@@ -2493,13 +2496,13 @@
         <v>7</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>27</v>
@@ -2510,13 +2513,13 @@
         <v>7</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>27</v>
@@ -2527,13 +2530,13 @@
         <v>7</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>27</v>
@@ -2544,7 +2547,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>25</v>
@@ -2561,13 +2564,13 @@
         <v>7</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>27</v>
@@ -2578,13 +2581,13 @@
         <v>7</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>27</v>
@@ -2595,13 +2598,13 @@
         <v>7</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>27</v>
@@ -2612,13 +2615,13 @@
         <v>7</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>27</v>
@@ -2629,7 +2632,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>25</v>
@@ -2646,13 +2649,13 @@
         <v>7</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>27</v>
@@ -2663,13 +2666,13 @@
         <v>7</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>27</v>
@@ -2680,13 +2683,13 @@
         <v>7</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>27</v>
@@ -2697,13 +2700,13 @@
         <v>7</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>27</v>
@@ -2714,13 +2717,13 @@
         <v>7</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>27</v>
@@ -2731,13 +2734,13 @@
         <v>7</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>27</v>
@@ -2748,13 +2751,13 @@
         <v>7</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>27</v>
@@ -2765,13 +2768,13 @@
         <v>7</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>27</v>
@@ -2782,13 +2785,13 @@
         <v>7</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>27</v>
@@ -2799,13 +2802,13 @@
         <v>7</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>27</v>
@@ -2816,13 +2819,13 @@
         <v>7</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>27</v>
@@ -2833,13 +2836,13 @@
         <v>7</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>27</v>
@@ -2850,13 +2853,13 @@
         <v>7</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>27</v>
@@ -2867,13 +2870,13 @@
         <v>7</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>27</v>
@@ -2884,13 +2887,13 @@
         <v>7</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>27</v>
@@ -2901,13 +2904,13 @@
         <v>7</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>27</v>
@@ -2918,13 +2921,13 @@
         <v>7</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>27</v>
@@ -2935,13 +2938,13 @@
         <v>7</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>27</v>
@@ -2952,13 +2955,13 @@
         <v>7</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>27</v>
@@ -2969,13 +2972,13 @@
         <v>7</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>27</v>
@@ -2986,7 +2989,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>25</v>
@@ -3003,13 +3006,13 @@
         <v>7</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>27</v>
@@ -3020,13 +3023,13 @@
         <v>7</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>27</v>
@@ -3037,13 +3040,13 @@
         <v>7</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>27</v>
@@ -3054,13 +3057,13 @@
         <v>7</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>27</v>
@@ -3071,13 +3074,13 @@
         <v>7</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>27</v>
@@ -3088,13 +3091,13 @@
         <v>7</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>27</v>
@@ -3105,13 +3108,13 @@
         <v>7</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>27</v>
@@ -3122,13 +3125,13 @@
         <v>7</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>27</v>
@@ -3139,13 +3142,13 @@
         <v>7</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>27</v>
@@ -3156,13 +3159,13 @@
         <v>7</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>27</v>
@@ -3173,13 +3176,13 @@
         <v>7</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>27</v>
@@ -3190,13 +3193,13 @@
         <v>7</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>27</v>
@@ -3207,13 +3210,13 @@
         <v>7</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>27</v>
@@ -3224,13 +3227,13 @@
         <v>7</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>27</v>
@@ -3241,13 +3244,13 @@
         <v>7</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>27</v>
@@ -3258,13 +3261,13 @@
         <v>7</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>27</v>
@@ -3275,13 +3278,13 @@
         <v>7</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>27</v>
@@ -3292,13 +3295,13 @@
         <v>7</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>27</v>
@@ -3309,13 +3312,13 @@
         <v>7</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>27</v>
@@ -3326,13 +3329,13 @@
         <v>7</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>27</v>
@@ -3343,13 +3346,13 @@
         <v>7</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>27</v>
@@ -3360,13 +3363,13 @@
         <v>7</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>27</v>
@@ -3377,13 +3380,13 @@
         <v>7</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>27</v>
@@ -3394,13 +3397,13 @@
         <v>7</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>27</v>
@@ -3411,13 +3414,13 @@
         <v>7</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>27</v>
@@ -3428,13 +3431,13 @@
         <v>7</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>27</v>
@@ -3445,13 +3448,13 @@
         <v>7</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>27</v>
@@ -3462,13 +3465,13 @@
         <v>7</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C83" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>27</v>
@@ -3479,13 +3482,13 @@
         <v>7</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>27</v>
@@ -3496,13 +3499,13 @@
         <v>7</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>27</v>
@@ -3513,13 +3516,13 @@
         <v>7</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>27</v>
@@ -3530,13 +3533,13 @@
         <v>7</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>27</v>
@@ -3547,13 +3550,13 @@
         <v>7</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>27</v>
@@ -3564,13 +3567,13 @@
         <v>7</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>27</v>
@@ -3581,13 +3584,13 @@
         <v>7</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>27</v>
@@ -3598,13 +3601,13 @@
         <v>7</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>27</v>
@@ -3615,13 +3618,13 @@
         <v>7</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>27</v>
@@ -3632,13 +3635,13 @@
         <v>7</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>27</v>
@@ -3649,13 +3652,13 @@
         <v>7</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>27</v>
@@ -3666,13 +3669,13 @@
         <v>7</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>27</v>
@@ -3683,13 +3686,13 @@
         <v>7</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>27</v>
@@ -3700,13 +3703,13 @@
         <v>7</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>27</v>
@@ -3717,13 +3720,13 @@
         <v>7</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>27</v>
@@ -3734,13 +3737,13 @@
         <v>7</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>27</v>
@@ -3751,13 +3754,13 @@
         <v>7</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>27</v>
@@ -3768,13 +3771,13 @@
         <v>7</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>27</v>
@@ -3785,13 +3788,13 @@
         <v>7</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>27</v>
@@ -3802,13 +3805,13 @@
         <v>7</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>27</v>
@@ -3819,13 +3822,13 @@
         <v>7</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>27</v>
@@ -3836,13 +3839,13 @@
         <v>7</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>27</v>
@@ -3853,13 +3856,13 @@
         <v>7</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>27</v>
@@ -3870,13 +3873,13 @@
         <v>7</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>27</v>
@@ -3887,13 +3890,13 @@
         <v>7</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>27</v>
@@ -3904,13 +3907,13 @@
         <v>7</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>27</v>
@@ -3921,13 +3924,13 @@
         <v>7</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>27</v>
@@ -3938,13 +3941,13 @@
         <v>7</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>27</v>
@@ -3955,13 +3958,13 @@
         <v>10</v>
       </c>
       <c r="B112" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D112" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>27</v>
@@ -3972,13 +3975,13 @@
         <v>10</v>
       </c>
       <c r="B113" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D113" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D113" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>27</v>
@@ -3995,7 +3998,7 @@
         <v>25</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>151</v>
+        <v>39</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>27</v>
@@ -4006,13 +4009,13 @@
         <v>10</v>
       </c>
       <c r="B115" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D115" s="12" t="s">
         <v>152</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>27</v>
@@ -4023,13 +4026,13 @@
         <v>10</v>
       </c>
       <c r="B116" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D116" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>27</v>
@@ -4040,13 +4043,13 @@
         <v>10</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C117" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>27</v>
@@ -4057,13 +4060,13 @@
         <v>10</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>27</v>
@@ -4074,13 +4077,13 @@
         <v>10</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C119" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>27</v>
@@ -4091,13 +4094,13 @@
         <v>10</v>
       </c>
       <c r="B120" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>161</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>27</v>
@@ -4108,13 +4111,13 @@
         <v>10</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C121" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>27</v>
@@ -4125,13 +4128,13 @@
         <v>10</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>27</v>
@@ -4142,13 +4145,13 @@
         <v>10</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C123" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>27</v>
@@ -4159,13 +4162,13 @@
         <v>10</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>163</v>
+        <v>39</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>27</v>
@@ -4176,13 +4179,13 @@
         <v>10</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C125" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>27</v>
@@ -4193,13 +4196,13 @@
         <v>10</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>155</v>
+        <v>39</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>27</v>
@@ -4210,13 +4213,13 @@
         <v>10</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C127" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>27</v>
@@ -4227,13 +4230,13 @@
         <v>10</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>27</v>
@@ -4244,13 +4247,13 @@
         <v>10</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C129" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>27</v>
@@ -4261,13 +4264,13 @@
         <v>10</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C130" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>27</v>
@@ -4278,13 +4281,13 @@
         <v>10</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C131" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>27</v>
@@ -4295,13 +4298,13 @@
         <v>10</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>27</v>
@@ -4312,13 +4315,13 @@
         <v>10</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C133" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>27</v>
@@ -4329,13 +4332,13 @@
         <v>10</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>27</v>
@@ -4346,7 +4349,7 @@
         <v>10</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C135" s="11" t="s">
         <v>25</v>
@@ -4363,13 +4366,13 @@
         <v>10</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>27</v>
@@ -4380,13 +4383,13 @@
         <v>10</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C137" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>27</v>
@@ -4397,13 +4400,13 @@
         <v>10</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>27</v>
@@ -4414,13 +4417,13 @@
         <v>10</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C139" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>27</v>
@@ -4431,13 +4434,13 @@
         <v>10</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>27</v>
@@ -4448,13 +4451,13 @@
         <v>10</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>27</v>
@@ -4465,13 +4468,13 @@
         <v>10</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>27</v>
@@ -4482,13 +4485,13 @@
         <v>10</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>27</v>
@@ -4499,13 +4502,13 @@
         <v>10</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E144" s="10" t="s">
         <v>27</v>
@@ -4516,13 +4519,13 @@
         <v>10</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>27</v>
@@ -4533,13 +4536,13 @@
         <v>10</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>27</v>
@@ -4550,13 +4553,13 @@
         <v>10</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>27</v>
@@ -4567,13 +4570,13 @@
         <v>10</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>27</v>
@@ -4584,13 +4587,13 @@
         <v>10</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>27</v>
@@ -4601,13 +4604,13 @@
         <v>10</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>27</v>
@@ -4618,13 +4621,13 @@
         <v>10</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>27</v>
@@ -4635,13 +4638,13 @@
         <v>10</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>27</v>
@@ -4652,13 +4655,13 @@
         <v>10</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>27</v>
@@ -4669,13 +4672,13 @@
         <v>10</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E154" s="10" t="s">
         <v>27</v>
@@ -4686,13 +4689,13 @@
         <v>10</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C155" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>27</v>
@@ -4703,13 +4706,13 @@
         <v>10</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C156" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>27</v>
@@ -4720,13 +4723,13 @@
         <v>10</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>27</v>
@@ -4737,13 +4740,13 @@
         <v>10</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>27</v>
@@ -4754,13 +4757,13 @@
         <v>10</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C159" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>27</v>
@@ -4771,13 +4774,13 @@
         <v>10</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E160" s="10" t="s">
         <v>27</v>
@@ -4788,13 +4791,13 @@
         <v>10</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>27</v>
@@ -4805,13 +4808,13 @@
         <v>10</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E162" s="10" t="s">
         <v>27</v>
@@ -4822,13 +4825,13 @@
         <v>10</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>27</v>
@@ -4839,13 +4842,13 @@
         <v>10</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E164" s="10" t="s">
         <v>27</v>
@@ -4856,13 +4859,13 @@
         <v>10</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>27</v>
@@ -4873,13 +4876,13 @@
         <v>10</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E166" s="10" t="s">
         <v>27</v>
@@ -4890,13 +4893,13 @@
         <v>10</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>27</v>
@@ -4907,13 +4910,13 @@
         <v>10</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E168" s="10" t="s">
         <v>27</v>
@@ -4924,13 +4927,13 @@
         <v>10</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>27</v>
@@ -4941,13 +4944,13 @@
         <v>10</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E170" s="10" t="s">
         <v>27</v>
@@ -4958,13 +4961,13 @@
         <v>10</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>27</v>
@@ -4975,13 +4978,13 @@
         <v>10</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E172" s="10" t="s">
         <v>27</v>
@@ -4992,13 +4995,13 @@
         <v>10</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>27</v>
@@ -5009,13 +5012,13 @@
         <v>10</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E174" s="10" t="s">
         <v>27</v>
@@ -5026,13 +5029,13 @@
         <v>10</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D175" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>27</v>
@@ -5043,13 +5046,13 @@
         <v>10</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E176" s="10" t="s">
         <v>27</v>
@@ -5060,13 +5063,13 @@
         <v>10</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>27</v>
@@ -5077,13 +5080,13 @@
         <v>10</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E178" s="10" t="s">
         <v>27</v>
@@ -5094,13 +5097,13 @@
         <v>10</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>27</v>
@@ -5111,13 +5114,13 @@
         <v>10</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E180" s="10" t="s">
         <v>27</v>
@@ -5128,13 +5131,13 @@
         <v>10</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>27</v>
@@ -5145,13 +5148,13 @@
         <v>10</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E182" s="10" t="s">
         <v>27</v>
@@ -5162,13 +5165,13 @@
         <v>10</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C183" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>27</v>
@@ -5179,13 +5182,13 @@
         <v>10</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D184" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E184" s="10" t="s">
         <v>27</v>
@@ -5196,13 +5199,13 @@
         <v>10</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D185" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>27</v>
@@ -5213,13 +5216,13 @@
         <v>10</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D186" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E186" s="10" t="s">
         <v>27</v>
@@ -5230,13 +5233,13 @@
         <v>10</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D187" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>27</v>
@@ -5247,13 +5250,13 @@
         <v>10</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D188" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E188" s="10" t="s">
         <v>27</v>
@@ -5264,13 +5267,13 @@
         <v>10</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D189" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>27</v>
@@ -5281,13 +5284,13 @@
         <v>10</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D190" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E190" s="10" t="s">
         <v>27</v>
@@ -5298,13 +5301,13 @@
         <v>10</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D191" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>27</v>
@@ -5315,13 +5318,13 @@
         <v>10</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D192" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E192" s="10" t="s">
         <v>27</v>
@@ -5332,13 +5335,13 @@
         <v>10</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D193" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>27</v>
@@ -5349,13 +5352,13 @@
         <v>10</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D194" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E194" s="10" t="s">
         <v>27</v>
@@ -5366,13 +5369,13 @@
         <v>10</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D195" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>27</v>
@@ -5383,13 +5386,13 @@
         <v>10</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D196" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E196" s="10" t="s">
         <v>27</v>
@@ -5400,13 +5403,13 @@
         <v>10</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D197" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>27</v>
@@ -5417,13 +5420,13 @@
         <v>10</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D198" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E198" s="10" t="s">
         <v>27</v>
@@ -5434,13 +5437,13 @@
         <v>10</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D199" s="12" t="s">
-        <v>34</v>
+        <v>246</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>27</v>
@@ -5451,13 +5454,13 @@
         <v>10</v>
       </c>
       <c r="B200" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C200" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D200" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="C200" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D200" s="12" t="s">
-        <v>34</v>
       </c>
       <c r="E200" s="10" t="s">
         <v>27</v>
@@ -5474,7 +5477,7 @@
         <v>25</v>
       </c>
       <c r="D201" s="12" t="s">
-        <v>34</v>
+        <v>250</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>27</v>
@@ -5485,13 +5488,13 @@
         <v>10</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D202" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E202" s="10" t="s">
         <v>27</v>
@@ -5502,13 +5505,13 @@
         <v>10</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D203" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>27</v>
@@ -5519,13 +5522,13 @@
         <v>10</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D204" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E204" s="10" t="s">
         <v>27</v>
@@ -5536,13 +5539,13 @@
         <v>10</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D205" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>27</v>
@@ -5553,13 +5556,13 @@
         <v>10</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D206" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E206" s="10" t="s">
         <v>27</v>
@@ -5570,13 +5573,13 @@
         <v>10</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D207" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>27</v>
@@ -5587,13 +5590,13 @@
         <v>10</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D208" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E208" s="10" t="s">
         <v>27</v>
@@ -5604,13 +5607,13 @@
         <v>10</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D209" s="12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>27</v>
@@ -5621,13 +5624,13 @@
         <v>10</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D210" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E210" s="10" t="s">
         <v>27</v>
@@ -5638,13 +5641,13 @@
         <v>10</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C211" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D211" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>27</v>
@@ -5655,13 +5658,13 @@
         <v>10</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D212" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E212" s="10" t="s">
         <v>27</v>
@@ -5672,13 +5675,13 @@
         <v>10</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D213" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>27</v>
@@ -5689,13 +5692,13 @@
         <v>10</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C214" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D214" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E214" s="10" t="s">
         <v>27</v>
@@ -5706,13 +5709,13 @@
         <v>10</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C215" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D215" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>27</v>
@@ -5723,7 +5726,7 @@
         <v>10</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>25</v>
@@ -5740,13 +5743,13 @@
         <v>10</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C217" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D217" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>27</v>
@@ -5757,13 +5760,13 @@
         <v>10</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D218" s="12" t="s">
-        <v>34</v>
+        <v>268</v>
       </c>
       <c r="E218" s="10" t="s">
         <v>27</v>
@@ -5774,13 +5777,13 @@
         <v>10</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D219" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>27</v>
@@ -5791,13 +5794,13 @@
         <v>10</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C220" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D220" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E220" s="10" t="s">
         <v>27</v>
@@ -5808,13 +5811,13 @@
         <v>10</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C221" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D221" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>27</v>
@@ -5825,13 +5828,13 @@
         <v>12</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C222" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E222" s="10" t="s">
         <v>27</v>
@@ -5842,13 +5845,13 @@
         <v>12</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C223" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>27</v>
@@ -5859,13 +5862,13 @@
         <v>12</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C224" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E224" s="10" t="s">
         <v>27</v>
@@ -5876,13 +5879,13 @@
         <v>12</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C225" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>27</v>
@@ -5893,13 +5896,13 @@
         <v>12</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C226" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E226" s="10" t="s">
         <v>27</v>
@@ -5910,13 +5913,13 @@
         <v>12</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C227" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D227" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>27</v>
@@ -5927,13 +5930,13 @@
         <v>12</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C228" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D228" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E228" s="10" t="s">
         <v>27</v>
@@ -5944,13 +5947,13 @@
         <v>12</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C229" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D229" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>27</v>
@@ -5961,13 +5964,13 @@
         <v>12</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C230" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D230" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E230" s="10" t="s">
         <v>27</v>
@@ -5978,13 +5981,13 @@
         <v>12</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C231" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D231" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>27</v>
@@ -5995,13 +5998,13 @@
         <v>12</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C232" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D232" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E232" s="10" t="s">
         <v>27</v>
@@ -6012,13 +6015,13 @@
         <v>12</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C233" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D233" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>27</v>
@@ -6029,13 +6032,13 @@
         <v>12</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C234" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E234" s="10" t="s">
         <v>27</v>
@@ -6046,13 +6049,13 @@
         <v>12</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C235" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D235" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>27</v>
@@ -6063,13 +6066,13 @@
         <v>12</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C236" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E236" s="10" t="s">
         <v>27</v>
@@ -6080,13 +6083,13 @@
         <v>12</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C237" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D237" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>27</v>
@@ -6097,13 +6100,13 @@
         <v>12</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C238" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D238" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E238" s="10" t="s">
         <v>27</v>
@@ -6114,13 +6117,13 @@
         <v>12</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C239" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D239" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>27</v>
@@ -6131,13 +6134,13 @@
         <v>12</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C240" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E240" s="10" t="s">
         <v>27</v>
@@ -6148,13 +6151,13 @@
         <v>12</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C241" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D241" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E241" s="10" t="s">
         <v>27</v>
@@ -6165,13 +6168,13 @@
         <v>12</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C242" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D242" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E242" s="10" t="s">
         <v>27</v>
@@ -6182,13 +6185,13 @@
         <v>12</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C243" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D243" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E243" s="10" t="s">
         <v>27</v>
@@ -6199,13 +6202,13 @@
         <v>12</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C244" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D244" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E244" s="10" t="s">
         <v>27</v>
@@ -6216,13 +6219,13 @@
         <v>12</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C245" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D245" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E245" s="10" t="s">
         <v>27</v>
@@ -6233,13 +6236,13 @@
         <v>12</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C246" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D246" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E246" s="10" t="s">
         <v>27</v>
@@ -6250,13 +6253,13 @@
         <v>12</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C247" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D247" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E247" s="10" t="s">
         <v>27</v>
@@ -6267,13 +6270,13 @@
         <v>12</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C248" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E248" s="10" t="s">
         <v>27</v>
@@ -6284,13 +6287,13 @@
         <v>12</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C249" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D249" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E249" s="10" t="s">
         <v>27</v>
@@ -6301,13 +6304,13 @@
         <v>12</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C250" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D250" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E250" s="10" t="s">
         <v>27</v>
@@ -6318,13 +6321,13 @@
         <v>12</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C251" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D251" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E251" s="10" t="s">
         <v>27</v>
@@ -6335,13 +6338,13 @@
         <v>12</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C252" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D252" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E252" s="10" t="s">
         <v>27</v>
@@ -6352,13 +6355,13 @@
         <v>12</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C253" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D253" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E253" s="10" t="s">
         <v>27</v>
@@ -6369,13 +6372,13 @@
         <v>12</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C254" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E254" s="10" t="s">
         <v>27</v>
@@ -6386,13 +6389,13 @@
         <v>12</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C255" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D255" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E255" s="10" t="s">
         <v>27</v>
@@ -6403,13 +6406,13 @@
         <v>12</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D256" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E256" s="10" t="s">
         <v>27</v>
@@ -6420,13 +6423,13 @@
         <v>12</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D257" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E257" s="10" t="s">
         <v>27</v>
@@ -6437,13 +6440,13 @@
         <v>12</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D258" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E258" s="10" t="s">
         <v>27</v>
@@ -6454,13 +6457,13 @@
         <v>12</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D259" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E259" s="10" t="s">
         <v>27</v>
@@ -6471,13 +6474,13 @@
         <v>12</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D260" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E260" s="10" t="s">
         <v>27</v>
@@ -6488,13 +6491,13 @@
         <v>12</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D261" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E261" s="10" t="s">
         <v>27</v>
@@ -6505,13 +6508,13 @@
         <v>12</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D262" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E262" s="10" t="s">
         <v>27</v>
@@ -6522,13 +6525,13 @@
         <v>12</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C263" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D263" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E263" s="10" t="s">
         <v>27</v>
@@ -6539,13 +6542,13 @@
         <v>12</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C264" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D264" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E264" s="10" t="s">
         <v>27</v>
@@ -6556,13 +6559,13 @@
         <v>12</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D265" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E265" s="10" t="s">
         <v>27</v>
@@ -6573,13 +6576,13 @@
         <v>12</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C266" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D266" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E266" s="10" t="s">
         <v>27</v>
@@ -6590,13 +6593,13 @@
         <v>12</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C267" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D267" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E267" s="10" t="s">
         <v>27</v>
@@ -6607,13 +6610,13 @@
         <v>12</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D268" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E268" s="10" t="s">
         <v>27</v>
@@ -6624,13 +6627,13 @@
         <v>12</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C269" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D269" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E269" s="10" t="s">
         <v>27</v>
@@ -6641,13 +6644,13 @@
         <v>12</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D270" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E270" s="10" t="s">
         <v>27</v>
@@ -6658,13 +6661,13 @@
         <v>12</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C271" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D271" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E271" s="10" t="s">
         <v>27</v>
@@ -6675,13 +6678,13 @@
         <v>12</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D272" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E272" s="10" t="s">
         <v>27</v>
@@ -6692,13 +6695,13 @@
         <v>12</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C273" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D273" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E273" s="10" t="s">
         <v>27</v>
@@ -6709,13 +6712,13 @@
         <v>12</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C274" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D274" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E274" s="10" t="s">
         <v>27</v>
@@ -6726,13 +6729,13 @@
         <v>12</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C275" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D275" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E275" s="10" t="s">
         <v>27</v>
@@ -6743,13 +6746,13 @@
         <v>12</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C276" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D276" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E276" s="10" t="s">
         <v>27</v>
@@ -6760,13 +6763,13 @@
         <v>12</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C277" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D277" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E277" s="10" t="s">
         <v>27</v>
@@ -6777,13 +6780,13 @@
         <v>12</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C278" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D278" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E278" s="10" t="s">
         <v>27</v>
@@ -6794,13 +6797,13 @@
         <v>12</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C279" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D279" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E279" s="10" t="s">
         <v>27</v>
@@ -6811,13 +6814,13 @@
         <v>12</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C280" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D280" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E280" s="10" t="s">
         <v>27</v>
@@ -6828,13 +6831,13 @@
         <v>12</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C281" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D281" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E281" s="10" t="s">
         <v>27</v>
@@ -6845,13 +6848,13 @@
         <v>12</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C282" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D282" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E282" s="10" t="s">
         <v>27</v>
@@ -6862,13 +6865,13 @@
         <v>12</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C283" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D283" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E283" s="10" t="s">
         <v>27</v>
@@ -6879,13 +6882,13 @@
         <v>12</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C284" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D284" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E284" s="10" t="s">
         <v>27</v>
@@ -6896,13 +6899,13 @@
         <v>12</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C285" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D285" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E285" s="10" t="s">
         <v>27</v>
@@ -6913,13 +6916,13 @@
         <v>12</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C286" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D286" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E286" s="10" t="s">
         <v>27</v>
@@ -6930,13 +6933,13 @@
         <v>12</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C287" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D287" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E287" s="10" t="s">
         <v>27</v>
@@ -6947,13 +6950,13 @@
         <v>12</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C288" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D288" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E288" s="10" t="s">
         <v>27</v>
@@ -6964,13 +6967,13 @@
         <v>12</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C289" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D289" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E289" s="10" t="s">
         <v>27</v>
@@ -6981,13 +6984,13 @@
         <v>12</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C290" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E290" s="10" t="s">
         <v>27</v>
@@ -6998,13 +7001,13 @@
         <v>12</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C291" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E291" s="10" t="s">
         <v>27</v>
@@ -7015,13 +7018,13 @@
         <v>12</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C292" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E292" s="10" t="s">
         <v>27</v>
@@ -7032,13 +7035,13 @@
         <v>12</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C293" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D293" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E293" s="10" t="s">
         <v>27</v>
@@ -7049,13 +7052,13 @@
         <v>12</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C294" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D294" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E294" s="10" t="s">
         <v>27</v>
@@ -7066,13 +7069,13 @@
         <v>12</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C295" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D295" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E295" s="10" t="s">
         <v>27</v>
@@ -7083,13 +7086,13 @@
         <v>12</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C296" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D296" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E296" s="10" t="s">
         <v>27</v>
@@ -7100,13 +7103,13 @@
         <v>12</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C297" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D297" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E297" s="10" t="s">
         <v>27</v>
@@ -7117,13 +7120,13 @@
         <v>12</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C298" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D298" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E298" s="10" t="s">
         <v>27</v>
@@ -7134,13 +7137,13 @@
         <v>12</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C299" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D299" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E299" s="10" t="s">
         <v>27</v>
@@ -7151,13 +7154,13 @@
         <v>12</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C300" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D300" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E300" s="10" t="s">
         <v>27</v>
@@ -7168,13 +7171,13 @@
         <v>12</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C301" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D301" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E301" s="10" t="s">
         <v>27</v>
@@ -7185,13 +7188,13 @@
         <v>12</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C302" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D302" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E302" s="10" t="s">
         <v>27</v>
@@ -7202,13 +7205,13 @@
         <v>12</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C303" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D303" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E303" s="10" t="s">
         <v>27</v>
@@ -7219,13 +7222,13 @@
         <v>12</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C304" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D304" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E304" s="10" t="s">
         <v>27</v>
@@ -7236,13 +7239,13 @@
         <v>12</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C305" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D305" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E305" s="10" t="s">
         <v>27</v>
@@ -7253,13 +7256,13 @@
         <v>12</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C306" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D306" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E306" s="10" t="s">
         <v>27</v>
@@ -7270,13 +7273,13 @@
         <v>12</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C307" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D307" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E307" s="10" t="s">
         <v>27</v>
@@ -7287,13 +7290,13 @@
         <v>12</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C308" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D308" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E308" s="10" t="s">
         <v>27</v>
@@ -7304,13 +7307,13 @@
         <v>12</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C309" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E309" s="10" t="s">
         <v>27</v>
@@ -7321,13 +7324,13 @@
         <v>12</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C310" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D310" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E310" s="10" t="s">
         <v>27</v>
@@ -7338,13 +7341,13 @@
         <v>12</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C311" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D311" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E311" s="10" t="s">
         <v>27</v>
@@ -7355,13 +7358,13 @@
         <v>12</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C312" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D312" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E312" s="10" t="s">
         <v>27</v>
@@ -7372,13 +7375,13 @@
         <v>12</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C313" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D313" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E313" s="10" t="s">
         <v>27</v>
@@ -7389,13 +7392,13 @@
         <v>12</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C314" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D314" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E314" s="10" t="s">
         <v>27</v>
@@ -7406,13 +7409,13 @@
         <v>12</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C315" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D315" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E315" s="10" t="s">
         <v>27</v>
@@ -7423,13 +7426,13 @@
         <v>12</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C316" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D316" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E316" s="10" t="s">
         <v>27</v>
@@ -7440,13 +7443,13 @@
         <v>12</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C317" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D317" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E317" s="10" t="s">
         <v>27</v>
@@ -7457,13 +7460,13 @@
         <v>12</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C318" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D318" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E318" s="10" t="s">
         <v>27</v>
@@ -7474,13 +7477,13 @@
         <v>12</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C319" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D319" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E319" s="10" t="s">
         <v>27</v>
@@ -7491,13 +7494,13 @@
         <v>12</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C320" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D320" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E320" s="10" t="s">
         <v>27</v>
@@ -7508,13 +7511,13 @@
         <v>12</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C321" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D321" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E321" s="10" t="s">
         <v>27</v>
@@ -7525,13 +7528,13 @@
         <v>14</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C322" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D322" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E322" s="10" t="s">
         <v>27</v>
@@ -7542,13 +7545,13 @@
         <v>14</v>
       </c>
       <c r="B323" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C323" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D323" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E323" s="10" t="s">
         <v>27</v>
@@ -7559,7 +7562,7 @@
         <v>14</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C324" s="11" t="s">
         <v>25</v>
@@ -7576,13 +7579,13 @@
         <v>14</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C325" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D325" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E325" s="10" t="s">
         <v>27</v>
@@ -7593,13 +7596,13 @@
         <v>14</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C326" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D326" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E326" s="10" t="s">
         <v>27</v>
@@ -7610,13 +7613,13 @@
         <v>14</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C327" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D327" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E327" s="10" t="s">
         <v>27</v>
@@ -7627,13 +7630,13 @@
         <v>14</v>
       </c>
       <c r="B328" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C328" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D328" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E328" s="10" t="s">
         <v>27</v>
@@ -7644,13 +7647,13 @@
         <v>14</v>
       </c>
       <c r="B329" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C329" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D329" s="12" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E329" s="10" t="s">
         <v>27</v>
@@ -7667,7 +7670,7 @@
         <v>25</v>
       </c>
       <c r="D330" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E330" s="10" t="s">
         <v>27</v>
@@ -7684,7 +7687,7 @@
         <v>25</v>
       </c>
       <c r="D331" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E331" s="10" t="s">
         <v>27</v>
@@ -7701,7 +7704,7 @@
         <v>25</v>
       </c>
       <c r="D332" s="12" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E332" s="10" t="s">
         <v>27</v>
@@ -7712,13 +7715,13 @@
         <v>14</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C333" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D333" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E333" s="10" t="s">
         <v>27</v>
@@ -7729,13 +7732,13 @@
         <v>14</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C334" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D334" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E334" s="10" t="s">
         <v>27</v>
@@ -7746,13 +7749,13 @@
         <v>14</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C335" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D335" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E335" s="10" t="s">
         <v>27</v>
@@ -7763,13 +7766,13 @@
         <v>14</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C336" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D336" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E336" s="10" t="s">
         <v>27</v>
@@ -7780,13 +7783,13 @@
         <v>14</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C337" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D337" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E337" s="10" t="s">
         <v>27</v>
@@ -7797,13 +7800,13 @@
         <v>14</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C338" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D338" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E338" s="10" t="s">
         <v>27</v>
@@ -7814,13 +7817,13 @@
         <v>14</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C339" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D339" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E339" s="10" t="s">
         <v>27</v>
@@ -7831,13 +7834,13 @@
         <v>14</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C340" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D340" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E340" s="10" t="s">
         <v>27</v>
@@ -7848,13 +7851,13 @@
         <v>14</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C341" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D341" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E341" s="10" t="s">
         <v>27</v>
@@ -7865,7 +7868,7 @@
         <v>14</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C342" s="11" t="s">
         <v>25</v>
@@ -7882,13 +7885,13 @@
         <v>14</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C343" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D343" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E343" s="10" t="s">
         <v>27</v>
@@ -7899,13 +7902,13 @@
         <v>14</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C344" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E344" s="10" t="s">
         <v>27</v>
@@ -7916,13 +7919,13 @@
         <v>14</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C345" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D345" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E345" s="10" t="s">
         <v>27</v>
@@ -7933,13 +7936,13 @@
         <v>14</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C346" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E346" s="10" t="s">
         <v>27</v>
@@ -7950,13 +7953,13 @@
         <v>14</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C347" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E347" s="10" t="s">
         <v>27</v>
@@ -7967,13 +7970,13 @@
         <v>14</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C348" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E348" s="10" t="s">
         <v>27</v>
@@ -7984,13 +7987,13 @@
         <v>14</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C349" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D349" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E349" s="10" t="s">
         <v>27</v>
@@ -8001,7 +8004,7 @@
         <v>14</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C350" s="11" t="s">
         <v>25</v>
@@ -8018,7 +8021,7 @@
         <v>14</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C351" s="11" t="s">
         <v>25</v>
@@ -8035,7 +8038,7 @@
         <v>14</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C352" s="11" t="s">
         <v>25</v>
@@ -8052,13 +8055,13 @@
         <v>14</v>
       </c>
       <c r="B353" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C353" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E353" s="10" t="s">
         <v>27</v>
@@ -8069,13 +8072,13 @@
         <v>14</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C354" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E354" s="10" t="s">
         <v>27</v>
@@ -8086,13 +8089,13 @@
         <v>14</v>
       </c>
       <c r="B355" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C355" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E355" s="10" t="s">
         <v>27</v>
@@ -8103,13 +8106,13 @@
         <v>14</v>
       </c>
       <c r="B356" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C356" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E356" s="10" t="s">
         <v>27</v>
@@ -8120,13 +8123,13 @@
         <v>14</v>
       </c>
       <c r="B357" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C357" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E357" s="10" t="s">
         <v>27</v>
@@ -8137,13 +8140,13 @@
         <v>14</v>
       </c>
       <c r="B358" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C358" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E358" s="10" t="s">
         <v>27</v>
@@ -8154,13 +8157,13 @@
         <v>14</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C359" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E359" s="10" t="s">
         <v>27</v>
@@ -8171,13 +8174,13 @@
         <v>14</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C360" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E360" s="10" t="s">
         <v>27</v>
@@ -8188,13 +8191,13 @@
         <v>14</v>
       </c>
       <c r="B361" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C361" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D361" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E361" s="10" t="s">
         <v>27</v>
@@ -8205,13 +8208,13 @@
         <v>14</v>
       </c>
       <c r="B362" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C362" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D362" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E362" s="10" t="s">
         <v>27</v>
@@ -8222,13 +8225,13 @@
         <v>14</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C363" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E363" s="10" t="s">
         <v>27</v>
@@ -8239,7 +8242,7 @@
         <v>14</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C364" s="11" t="s">
         <v>25</v>
@@ -8256,7 +8259,7 @@
         <v>14</v>
       </c>
       <c r="B365" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C365" s="11" t="s">
         <v>25</v>
@@ -8273,13 +8276,13 @@
         <v>14</v>
       </c>
       <c r="B366" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C366" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E366" s="10" t="s">
         <v>27</v>
@@ -8290,13 +8293,13 @@
         <v>14</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C367" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E367" s="10" t="s">
         <v>27</v>
@@ -8307,13 +8310,13 @@
         <v>14</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C368" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E368" s="10" t="s">
         <v>27</v>
@@ -8324,13 +8327,13 @@
         <v>14</v>
       </c>
       <c r="B369" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C369" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E369" s="10" t="s">
         <v>27</v>
@@ -8341,13 +8344,13 @@
         <v>14</v>
       </c>
       <c r="B370" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C370" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D370" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E370" s="10" t="s">
         <v>27</v>
@@ -8358,13 +8361,13 @@
         <v>14</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C371" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D371" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E371" s="10" t="s">
         <v>27</v>
@@ -8375,13 +8378,13 @@
         <v>14</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C372" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D372" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E372" s="10" t="s">
         <v>27</v>
@@ -8392,13 +8395,13 @@
         <v>14</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C373" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D373" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E373" s="10" t="s">
         <v>27</v>
@@ -8409,13 +8412,13 @@
         <v>14</v>
       </c>
       <c r="B374" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C374" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D374" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E374" s="10" t="s">
         <v>27</v>
@@ -8426,13 +8429,13 @@
         <v>14</v>
       </c>
       <c r="B375" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C375" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D375" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E375" s="10" t="s">
         <v>27</v>
@@ -8443,13 +8446,13 @@
         <v>14</v>
       </c>
       <c r="B376" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C376" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D376" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E376" s="10" t="s">
         <v>27</v>
@@ -8460,13 +8463,13 @@
         <v>14</v>
       </c>
       <c r="B377" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C377" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D377" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E377" s="10" t="s">
         <v>27</v>
@@ -8477,13 +8480,13 @@
         <v>14</v>
       </c>
       <c r="B378" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C378" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D378" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E378" s="10" t="s">
         <v>27</v>
@@ -8494,13 +8497,13 @@
         <v>14</v>
       </c>
       <c r="B379" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C379" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D379" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E379" s="10" t="s">
         <v>27</v>
@@ -8511,13 +8514,13 @@
         <v>14</v>
       </c>
       <c r="B380" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C380" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D380" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E380" s="10" t="s">
         <v>27</v>
@@ -8528,13 +8531,13 @@
         <v>14</v>
       </c>
       <c r="B381" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C381" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D381" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E381" s="10" t="s">
         <v>27</v>
@@ -8545,13 +8548,13 @@
         <v>14</v>
       </c>
       <c r="B382" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C382" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D382" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E382" s="10" t="s">
         <v>27</v>
@@ -8562,13 +8565,13 @@
         <v>14</v>
       </c>
       <c r="B383" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C383" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D383" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E383" s="10" t="s">
         <v>27</v>
@@ -8579,13 +8582,13 @@
         <v>14</v>
       </c>
       <c r="B384" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C384" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D384" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E384" s="10" t="s">
         <v>27</v>
@@ -8596,13 +8599,13 @@
         <v>14</v>
       </c>
       <c r="B385" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C385" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D385" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E385" s="10" t="s">
         <v>27</v>
@@ -8613,13 +8616,13 @@
         <v>14</v>
       </c>
       <c r="B386" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C386" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D386" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E386" s="10" t="s">
         <v>27</v>
@@ -8630,13 +8633,13 @@
         <v>14</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C387" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D387" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E387" s="10" t="s">
         <v>27</v>
@@ -8647,13 +8650,13 @@
         <v>14</v>
       </c>
       <c r="B388" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C388" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D388" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E388" s="10" t="s">
         <v>27</v>
@@ -8664,13 +8667,13 @@
         <v>14</v>
       </c>
       <c r="B389" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C389" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D389" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E389" s="10" t="s">
         <v>27</v>
@@ -8681,13 +8684,13 @@
         <v>14</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C390" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D390" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E390" s="10" t="s">
         <v>27</v>
@@ -8698,13 +8701,13 @@
         <v>14</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C391" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D391" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E391" s="10" t="s">
         <v>27</v>
@@ -8715,7 +8718,7 @@
         <v>14</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C392" s="11" t="s">
         <v>25</v>
@@ -8732,13 +8735,13 @@
         <v>14</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C393" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E393" s="10" t="s">
         <v>27</v>
@@ -8749,13 +8752,13 @@
         <v>14</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C394" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E394" s="10" t="s">
         <v>27</v>
@@ -8766,13 +8769,13 @@
         <v>14</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C395" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D395" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E395" s="10" t="s">
         <v>27</v>
@@ -8783,13 +8786,13 @@
         <v>14</v>
       </c>
       <c r="B396" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C396" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D396" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E396" s="10" t="s">
         <v>27</v>
@@ -8800,13 +8803,13 @@
         <v>14</v>
       </c>
       <c r="B397" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C397" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D397" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E397" s="10" t="s">
         <v>27</v>
@@ -8817,13 +8820,13 @@
         <v>14</v>
       </c>
       <c r="B398" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C398" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D398" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E398" s="10" t="s">
         <v>27</v>
@@ -8834,13 +8837,13 @@
         <v>14</v>
       </c>
       <c r="B399" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C399" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D399" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E399" s="10" t="s">
         <v>27</v>
@@ -8851,7 +8854,7 @@
         <v>14</v>
       </c>
       <c r="B400" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C400" s="11" t="s">
         <v>25</v>
@@ -8868,7 +8871,7 @@
         <v>14</v>
       </c>
       <c r="B401" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C401" s="11" t="s">
         <v>25</v>
@@ -8885,13 +8888,13 @@
         <v>14</v>
       </c>
       <c r="B402" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C402" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D402" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E402" s="10" t="s">
         <v>27</v>
@@ -8902,13 +8905,13 @@
         <v>14</v>
       </c>
       <c r="B403" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C403" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D403" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E403" s="10" t="s">
         <v>27</v>
@@ -8919,13 +8922,13 @@
         <v>14</v>
       </c>
       <c r="B404" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C404" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D404" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E404" s="10" t="s">
         <v>27</v>
@@ -8936,7 +8939,7 @@
         <v>14</v>
       </c>
       <c r="B405" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C405" s="11" t="s">
         <v>25</v>
@@ -8953,13 +8956,13 @@
         <v>14</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C406" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D406" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E406" s="10" t="s">
         <v>27</v>
@@ -8970,13 +8973,13 @@
         <v>14</v>
       </c>
       <c r="B407" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C407" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D407" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E407" s="10" t="s">
         <v>27</v>
@@ -8987,13 +8990,13 @@
         <v>14</v>
       </c>
       <c r="B408" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C408" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D408" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E408" s="10" t="s">
         <v>27</v>
@@ -9004,7 +9007,7 @@
         <v>14</v>
       </c>
       <c r="B409" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C409" s="11" t="s">
         <v>25</v>
@@ -9021,13 +9024,13 @@
         <v>14</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C410" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D410" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E410" s="10" t="s">
         <v>27</v>
@@ -9038,13 +9041,13 @@
         <v>14</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C411" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D411" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E411" s="10" t="s">
         <v>27</v>
@@ -9055,7 +9058,7 @@
         <v>14</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C412" s="11" t="s">
         <v>25</v>
@@ -9072,13 +9075,13 @@
         <v>14</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C413" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D413" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E413" s="10" t="s">
         <v>27</v>
@@ -9089,13 +9092,13 @@
         <v>14</v>
       </c>
       <c r="B414" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C414" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D414" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E414" s="10" t="s">
         <v>27</v>
@@ -9106,13 +9109,13 @@
         <v>14</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C415" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D415" s="12" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E415" s="10" t="s">
         <v>27</v>
@@ -9123,13 +9126,13 @@
         <v>14</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C416" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D416" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E416" s="10" t="s">
         <v>27</v>
@@ -9140,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="B417" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C417" s="11" t="s">
         <v>25</v>
@@ -9157,13 +9160,13 @@
         <v>14</v>
       </c>
       <c r="B418" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C418" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D418" s="12" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E418" s="10" t="s">
         <v>27</v>
@@ -9174,13 +9177,13 @@
         <v>14</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C419" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D419" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E419" s="10" t="s">
         <v>27</v>
@@ -9191,13 +9194,13 @@
         <v>14</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C420" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D420" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E420" s="10" t="s">
         <v>27</v>
@@ -9208,13 +9211,13 @@
         <v>14</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C421" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D421" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E421" s="10" t="s">
         <v>27</v>

--- a/test-cases-reports/selinium-test/selenium_web_report.xlsx
+++ b/test-cases-reports/selinium-test/selenium_web_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="470">
   <si>
     <t>STRIVECAMPUS WEB E2E TEST SUMMARY</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>90.91s</t>
+    <t>91.31s</t>
   </si>
   <si>
     <t>Deployable Status</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>4.27s</t>
+    <t>4.17s</t>
   </si>
   <si>
     <t>-</t>
@@ -107,394 +107,394 @@
     <t>UI003: Splash Screen tagline text</t>
   </si>
   <si>
+    <t>UI004: Onboarding page 1 title display</t>
+  </si>
+  <si>
+    <t>UI005: Onboarding page 1 description text layout</t>
+  </si>
+  <si>
+    <t>0.00s</t>
+  </si>
+  <si>
+    <t>UI006: Onboarding page 1 button text</t>
+  </si>
+  <si>
+    <t>UI007: Onboarding active page indicator state</t>
+  </si>
+  <si>
+    <t>UI008: Onboarding skip button option visibility</t>
+  </si>
+  <si>
+    <t>UI009: Onboarding page 2 title display</t>
+  </si>
+  <si>
+    <t>2.10s</t>
+  </si>
+  <si>
+    <t>UI010: Onboarding page 2 description text layout</t>
+  </si>
+  <si>
+    <t>UI011: Onboarding page 2 active page indicator state</t>
+  </si>
+  <si>
+    <t>UI012: Onboarding page 3 title display</t>
+  </si>
+  <si>
+    <t>2.06s</t>
+  </si>
+  <si>
+    <t>UI013: Onboarding page 3 description text layout</t>
+  </si>
+  <si>
+    <t>UI014: Onboarding page 3 Get Started button layout</t>
+  </si>
+  <si>
+    <t>UI015: Login Screen background card shape</t>
+  </si>
+  <si>
+    <t>4.13s</t>
+  </si>
+  <si>
+    <t>UI016: Login screen email input container styling</t>
+  </si>
+  <si>
+    <t>4.16s</t>
+  </si>
+  <si>
+    <t>UI017: Login screen password input container styling</t>
+  </si>
+  <si>
+    <t>0.02s</t>
+  </si>
+  <si>
+    <t>UI018: Login button background design</t>
+  </si>
+  <si>
+    <t>UI019: Login header branding typography</t>
+  </si>
+  <si>
+    <t>UI020: Register screen fields typography and spacing</t>
+  </si>
+  <si>
+    <t>2.09s</t>
+  </si>
+  <si>
+    <t>UI021: Register button border radius</t>
+  </si>
+  <si>
     <t>0.03s</t>
   </si>
   <si>
-    <t>UI004: Onboarding page 1 title display</t>
-  </si>
-  <si>
-    <t>0.02s</t>
-  </si>
-  <si>
-    <t>UI005: Onboarding page 1 description text layout</t>
-  </si>
-  <si>
-    <t>UI006: Onboarding page 1 button text</t>
-  </si>
-  <si>
-    <t>UI007: Onboarding active page indicator state</t>
-  </si>
-  <si>
-    <t>UI008: Onboarding skip button option visibility</t>
-  </si>
-  <si>
-    <t>UI009: Onboarding page 2 title display</t>
+    <t>UI022: Register footer link styling</t>
+  </si>
+  <si>
+    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
+  </si>
+  <si>
+    <t>UI024: Dashboard header title formatting</t>
+  </si>
+  <si>
+    <t>UI025: Theme toggler button visual contrast</t>
+  </si>
+  <si>
+    <t>UI026: Light mode dashboard theme colors</t>
+  </si>
+  <si>
+    <t>UI027: Dark mode theme transition styles</t>
+  </si>
+  <si>
+    <t>UI028: Profile screen user avatar size layout</t>
+  </si>
+  <si>
+    <t>UI029: Test session card border margins</t>
+  </si>
+  <si>
+    <t>UI030: AI Feedback dialog spacing layout</t>
+  </si>
+  <si>
+    <t>UI031: Onboarding page dot animation transition duration checks</t>
+  </si>
+  <si>
+    <t>UI032: Onboarding skip button typography style properties matching</t>
+  </si>
+  <si>
+    <t>UI033: Splash logo container dimensions ratio verification</t>
+  </si>
+  <si>
+    <t>UI034: Splash loader indicator circular progress thickness details</t>
+  </si>
+  <si>
+    <t>UI035: Authentication textfield error messaging text font style alignment</t>
+  </si>
+  <si>
+    <t>UI036: Login submit button responsive hover opacity changes</t>
+  </si>
+  <si>
+    <t>UI037: Register page input padding offsets consistency checks</t>
+  </si>
+  <si>
+    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
+  </si>
+  <si>
+    <t>UI039: Dark mode active body background color matching parameters</t>
+  </si>
+  <si>
+    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
+  </si>
+  <si>
+    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
+  </si>
+  <si>
+    <t>UI042: AI mock interview feedback container border lines styling</t>
+  </si>
+  <si>
+    <t>UI043: Chatbot user response chat bubble alignment properties</t>
+  </si>
+  <si>
+    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
+  </si>
+  <si>
+    <t>UI045: Profile user name typography scale weight and contrast check</t>
+  </si>
+  <si>
+    <t>UI046: Settings theme toggle switch active color verification parameters</t>
+  </si>
+  <si>
+    <t>UI047: Onboarding title layout alignment centered checking</t>
+  </si>
+  <si>
+    <t>UI048: Textfields active cursor focus color validation</t>
+  </si>
+  <si>
+    <t>UI049: Error messages warning badge layout constraints</t>
+  </si>
+  <si>
+    <t>UI050: App notification icon badges count scaling parameters</t>
+  </si>
+  <si>
+    <t>UI051: Profile card statistics counts label typography sizing</t>
+  </si>
+  <si>
+    <t>UI052: HR round option button icons visual alignment</t>
+  </si>
+  <si>
+    <t>UI053: Tech round option card layout spacing check</t>
+  </si>
+  <si>
+    <t>UI054: Aptitude test category cards layout alignment parameters</t>
+  </si>
+  <si>
+    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
+  </si>
+  <si>
+    <t>UI056: Alert dialog box overlay transparency index verification</t>
+  </si>
+  <si>
+    <t>UI057: Groq feedback score badge layout circular border alignment</t>
+  </si>
+  <si>
+    <t>UI058: Speech input icon active mic glow styling parameters</t>
+  </si>
+  <si>
+    <t>UI059: Dark theme input borders contrast rating validation</t>
+  </si>
+  <si>
+    <t>UI060: Onboarding next button icon placement side margins checking</t>
+  </si>
+  <si>
+    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
+  </si>
+  <si>
+    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
+  </si>
+  <si>
+    <t>UI063: Aptitude quiz progress bar line color status verification</t>
+  </si>
+  <si>
+    <t>UI064: Custom card elements scaling values on larger resolutions</t>
+  </si>
+  <si>
+    <t>UI065: Custom list dividers height thickness checking parameters</t>
+  </si>
+  <si>
+    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
+  </si>
+  <si>
+    <t>UI067: App header icon menu spacing and positioning specifications</t>
+  </si>
+  <si>
+    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
+  </si>
+  <si>
+    <t>UI069: Text input fields placeholder character font styling rules</t>
+  </si>
+  <si>
+    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
+  </si>
+  <si>
+    <t>UI071: Profile credentials edit inputs layout alignment values</t>
+  </si>
+  <si>
+    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
+  </si>
+  <si>
+    <t>UI073: Custom snackbar popup notifications container design styles</t>
+  </si>
+  <si>
+    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
+  </si>
+  <si>
+    <t>UI075: Webapp container shadow outline styling matching specifications</t>
+  </si>
+  <si>
+    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
+  </si>
+  <si>
+    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
+  </si>
+  <si>
+    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
+  </si>
+  <si>
+    <t>UI079: Chat suggestion chips outline border thickness details</t>
+  </si>
+  <si>
+    <t>UI080: Settings section headers font size transformations checking</t>
+  </si>
+  <si>
+    <t>UI081: Login forgot password link visual underline toggle checks</t>
+  </si>
+  <si>
+    <t>UI082: Register legal policies agreements text box layouts checks</t>
+  </si>
+  <si>
+    <t>UI083: Placement details document viewer layout padding verification</t>
+  </si>
+  <si>
+    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
+  </si>
+  <si>
+    <t>UI085: Custom dropdown selectors hover outline border width check</t>
+  </si>
+  <si>
+    <t>UI086: Dialog confirmations layouts check icon centering values</t>
+  </si>
+  <si>
+    <t>UI087: Chat input field icons click state opacity level updates</t>
+  </si>
+  <si>
+    <t>UI088: User avatar badge active placement online status display</t>
+  </si>
+  <si>
+    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
+  </si>
+  <si>
+    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
+  </si>
+  <si>
+    <t>UI091: Aptitude result summary page visual headers scaling check</t>
+  </si>
+  <si>
+    <t>UI092: AI feedback details accordion expand collapse height values</t>
+  </si>
+  <si>
+    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
+  </si>
+  <si>
+    <t>UI094: Navigation bar labels selected font color parameter checks</t>
+  </si>
+  <si>
+    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
+  </si>
+  <si>
+    <t>UI096: Settings section divider margins layout alignment specifications</t>
+  </si>
+  <si>
+    <t>UI097: Placement company filters panel layout drawer design styles</t>
+  </si>
+  <si>
+    <t>UI098: Notification toggle buttons sliding animation duration check</t>
+  </si>
+  <si>
+    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
+  </si>
+  <si>
+    <t>UI100: Auth form title secondary text decoration attributes check</t>
+  </si>
+  <si>
+    <t>UI101: Chat message time badge indicator font weight properties</t>
+  </si>
+  <si>
+    <t>UI102: Profile page history entries list spacing parameters</t>
+  </si>
+  <si>
+    <t>UI103: Feedback text block alignment rules inside cards check</t>
+  </si>
+  <si>
+    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
+  </si>
+  <si>
+    <t>0.04s</t>
+  </si>
+  <si>
+    <t>UI105: Interview review card layout horizontal borders constraint</t>
+  </si>
+  <si>
+    <t>UI106: Light mode inputs focus border shadow layout checks</t>
+  </si>
+  <si>
+    <t>UI107: Settings clear cache option text style parameters matching</t>
+  </si>
+  <si>
+    <t>UI108: Placement job card badges layout visual check rules</t>
+  </si>
+  <si>
+    <t>UI109: Speech processing overlay spinner styling visual verification</t>
+  </si>
+  <si>
+    <t>UI110: Test report dashboard header title color styling verification</t>
+  </si>
+  <si>
+    <t>FN001: Load app page successfully</t>
+  </si>
+  <si>
+    <t>FN002: Click Next to access page 2</t>
   </si>
   <si>
     <t>2.07s</t>
   </si>
   <si>
-    <t>UI010: Onboarding page 2 description text layout</t>
-  </si>
-  <si>
-    <t>UI011: Onboarding page 2 active page indicator state</t>
-  </si>
-  <si>
-    <t>UI012: Onboarding page 3 title display</t>
-  </si>
-  <si>
-    <t>UI013: Onboarding page 3 description text layout</t>
-  </si>
-  <si>
-    <t>UI014: Onboarding page 3 Get Started button layout</t>
-  </si>
-  <si>
-    <t>UI015: Login Screen background card shape</t>
-  </si>
-  <si>
-    <t>4.74s</t>
-  </si>
-  <si>
-    <t>UI016: Login screen email input container styling</t>
-  </si>
-  <si>
-    <t>4.10s</t>
-  </si>
-  <si>
-    <t>UI017: Login screen password input container styling</t>
-  </si>
-  <si>
-    <t>UI018: Login button background design</t>
-  </si>
-  <si>
-    <t>UI019: Login header branding typography</t>
-  </si>
-  <si>
-    <t>UI020: Register screen fields typography and spacing</t>
-  </si>
-  <si>
-    <t>2.16s</t>
-  </si>
-  <si>
-    <t>UI021: Register button border radius</t>
-  </si>
-  <si>
-    <t>0.04s</t>
-  </si>
-  <si>
-    <t>UI022: Register footer link styling</t>
-  </si>
-  <si>
-    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
-  </si>
-  <si>
-    <t>UI024: Dashboard header title formatting</t>
-  </si>
-  <si>
-    <t>UI025: Theme toggler button visual contrast</t>
-  </si>
-  <si>
-    <t>UI026: Light mode dashboard theme colors</t>
-  </si>
-  <si>
-    <t>UI027: Dark mode theme transition styles</t>
-  </si>
-  <si>
-    <t>0.00s</t>
-  </si>
-  <si>
-    <t>UI028: Profile screen user avatar size layout</t>
-  </si>
-  <si>
-    <t>UI029: Test session card border margins</t>
-  </si>
-  <si>
-    <t>UI030: AI Feedback dialog spacing layout</t>
-  </si>
-  <si>
-    <t>UI031: Onboarding page dot animation transition duration checks</t>
-  </si>
-  <si>
-    <t>UI032: Onboarding skip button typography style properties matching</t>
-  </si>
-  <si>
-    <t>UI033: Splash logo container dimensions ratio verification</t>
-  </si>
-  <si>
-    <t>UI034: Splash loader indicator circular progress thickness details</t>
-  </si>
-  <si>
-    <t>UI035: Authentication textfield error messaging text font style alignment</t>
-  </si>
-  <si>
-    <t>UI036: Login submit button responsive hover opacity changes</t>
-  </si>
-  <si>
-    <t>UI037: Register page input padding offsets consistency checks</t>
-  </si>
-  <si>
-    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
-  </si>
-  <si>
-    <t>UI039: Dark mode active body background color matching parameters</t>
-  </si>
-  <si>
-    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
-  </si>
-  <si>
-    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
-  </si>
-  <si>
-    <t>UI042: AI mock interview feedback container border lines styling</t>
-  </si>
-  <si>
-    <t>UI043: Chatbot user response chat bubble alignment properties</t>
-  </si>
-  <si>
-    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
-  </si>
-  <si>
-    <t>UI045: Profile user name typography scale weight and contrast check</t>
-  </si>
-  <si>
-    <t>UI046: Settings theme toggle switch active color verification parameters</t>
-  </si>
-  <si>
-    <t>UI047: Onboarding title layout alignment centered checking</t>
-  </si>
-  <si>
-    <t>UI048: Textfields active cursor focus color validation</t>
-  </si>
-  <si>
-    <t>UI049: Error messages warning badge layout constraints</t>
-  </si>
-  <si>
-    <t>UI050: App notification icon badges count scaling parameters</t>
-  </si>
-  <si>
-    <t>UI051: Profile card statistics counts label typography sizing</t>
-  </si>
-  <si>
-    <t>UI052: HR round option button icons visual alignment</t>
-  </si>
-  <si>
-    <t>UI053: Tech round option card layout spacing check</t>
-  </si>
-  <si>
-    <t>UI054: Aptitude test category cards layout alignment parameters</t>
-  </si>
-  <si>
-    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
-  </si>
-  <si>
-    <t>UI056: Alert dialog box overlay transparency index verification</t>
-  </si>
-  <si>
-    <t>UI057: Groq feedback score badge layout circular border alignment</t>
-  </si>
-  <si>
-    <t>UI058: Speech input icon active mic glow styling parameters</t>
-  </si>
-  <si>
-    <t>UI059: Dark theme input borders contrast rating validation</t>
-  </si>
-  <si>
-    <t>UI060: Onboarding next button icon placement side margins checking</t>
-  </si>
-  <si>
-    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
-  </si>
-  <si>
-    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
-  </si>
-  <si>
-    <t>UI063: Aptitude quiz progress bar line color status verification</t>
-  </si>
-  <si>
-    <t>UI064: Custom card elements scaling values on larger resolutions</t>
-  </si>
-  <si>
-    <t>UI065: Custom list dividers height thickness checking parameters</t>
-  </si>
-  <si>
-    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
-  </si>
-  <si>
-    <t>UI067: App header icon menu spacing and positioning specifications</t>
-  </si>
-  <si>
-    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
-  </si>
-  <si>
-    <t>UI069: Text input fields placeholder character font styling rules</t>
-  </si>
-  <si>
-    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
-  </si>
-  <si>
-    <t>UI071: Profile credentials edit inputs layout alignment values</t>
-  </si>
-  <si>
-    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
-  </si>
-  <si>
-    <t>UI073: Custom snackbar popup notifications container design styles</t>
-  </si>
-  <si>
-    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
-  </si>
-  <si>
-    <t>UI075: Webapp container shadow outline styling matching specifications</t>
-  </si>
-  <si>
-    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
-  </si>
-  <si>
-    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
-  </si>
-  <si>
-    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
-  </si>
-  <si>
-    <t>UI079: Chat suggestion chips outline border thickness details</t>
-  </si>
-  <si>
-    <t>UI080: Settings section headers font size transformations checking</t>
-  </si>
-  <si>
-    <t>UI081: Login forgot password link visual underline toggle checks</t>
-  </si>
-  <si>
-    <t>UI082: Register legal policies agreements text box layouts checks</t>
-  </si>
-  <si>
-    <t>UI083: Placement details document viewer layout padding verification</t>
-  </si>
-  <si>
-    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
-  </si>
-  <si>
-    <t>UI085: Custom dropdown selectors hover outline border width check</t>
-  </si>
-  <si>
-    <t>UI086: Dialog confirmations layouts check icon centering values</t>
-  </si>
-  <si>
-    <t>UI087: Chat input field icons click state opacity level updates</t>
-  </si>
-  <si>
-    <t>UI088: User avatar badge active placement online status display</t>
-  </si>
-  <si>
-    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
-  </si>
-  <si>
-    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
-  </si>
-  <si>
-    <t>UI091: Aptitude result summary page visual headers scaling check</t>
-  </si>
-  <si>
-    <t>UI092: AI feedback details accordion expand collapse height values</t>
-  </si>
-  <si>
-    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
-  </si>
-  <si>
-    <t>UI094: Navigation bar labels selected font color parameter checks</t>
-  </si>
-  <si>
-    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
-  </si>
-  <si>
-    <t>UI096: Settings section divider margins layout alignment specifications</t>
-  </si>
-  <si>
-    <t>UI097: Placement company filters panel layout drawer design styles</t>
-  </si>
-  <si>
-    <t>UI098: Notification toggle buttons sliding animation duration check</t>
-  </si>
-  <si>
-    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
-  </si>
-  <si>
-    <t>UI100: Auth form title secondary text decoration attributes check</t>
-  </si>
-  <si>
-    <t>UI101: Chat message time badge indicator font weight properties</t>
-  </si>
-  <si>
-    <t>UI102: Profile page history entries list spacing parameters</t>
-  </si>
-  <si>
-    <t>UI103: Feedback text block alignment rules inside cards check</t>
-  </si>
-  <si>
-    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
-  </si>
-  <si>
-    <t>UI105: Interview review card layout horizontal borders constraint</t>
-  </si>
-  <si>
-    <t>UI106: Light mode inputs focus border shadow layout checks</t>
-  </si>
-  <si>
-    <t>UI107: Settings clear cache option text style parameters matching</t>
-  </si>
-  <si>
-    <t>UI108: Placement job card badges layout visual check rules</t>
-  </si>
-  <si>
-    <t>UI109: Speech processing overlay spinner styling visual verification</t>
-  </si>
-  <si>
-    <t>UI110: Test report dashboard header title color styling verification</t>
-  </si>
-  <si>
-    <t>FN001: Load app page successfully</t>
-  </si>
-  <si>
-    <t>4.14s</t>
-  </si>
-  <si>
-    <t>FN002: Click Next to access page 2</t>
-  </si>
-  <si>
-    <t>2.10s</t>
-  </si>
-  <si>
     <t>FN003: Click Next to access page 3</t>
   </si>
   <si>
+    <t>2.08s</t>
+  </si>
+  <si>
     <t>FN004: Skip button bypasses onboarding screen</t>
   </si>
   <si>
-    <t>6.21s</t>
+    <t>6.24s</t>
   </si>
   <si>
     <t>FN005: Complete onboarding and transition to authentication page</t>
   </si>
   <si>
-    <t>2.06s</t>
-  </si>
-  <si>
     <t>FN006: Select register navigation path</t>
   </si>
   <si>
+    <t>2.11s</t>
+  </si>
+  <si>
     <t>FN007: Register a new account with valid unique details</t>
   </si>
   <si>
-    <t>2.08s</t>
-  </si>
-  <si>
     <t>FN008: Submit register account credentials to Firestore</t>
   </si>
   <si>
     <t>FN009: Verify user main dashboard is successfully loaded</t>
   </si>
   <si>
-    <t>0.51s</t>
+    <t>0.54s</t>
   </si>
   <si>
     <t>FN010: Navigate to Aptitude &amp; Technical Tests tab</t>
@@ -512,9 +512,6 @@
     <t>FN014: Select HR Mock Interview session card</t>
   </si>
   <si>
-    <t>2.04s</t>
-  </si>
-  <si>
     <t>FN015: Set question counts in configuration card</t>
   </si>
   <si>
@@ -524,7 +521,7 @@
     <t>FN017: Wait for AI Interviewer to load question details</t>
   </si>
   <si>
-    <t>1.52s</t>
+    <t>1.51s</t>
   </si>
   <si>
     <t>FN018: Retrieve visual text of mock question</t>
@@ -533,7 +530,7 @@
     <t>FN019: Input answer to the generated mock question</t>
   </si>
   <si>
-    <t>4.13s</t>
+    <t>4.18s</t>
   </si>
   <si>
     <t>FN020: Submit answer to AI evaluation engine</t>
@@ -542,7 +539,7 @@
     <t>FN021: Retrieve feedback score from Groq API response</t>
   </si>
   <si>
-    <t>2.01s</t>
+    <t>2.03s</t>
   </si>
   <si>
     <t>FN022: Display evaluation advice layout</t>
@@ -560,13 +557,10 @@
     <t>FN026: Enter custom text message in chat query input</t>
   </si>
   <si>
-    <t>4.12s</t>
-  </si>
-  <si>
     <t>FN027: Receive chatbot answer correctly</t>
   </si>
   <si>
-    <t>1.02s</t>
+    <t>1.01s</t>
   </si>
   <si>
     <t>FN028: Access user settings &amp; profile tab</t>
@@ -752,544 +746,535 @@
     <t>FN088: Career openings criteria checks matches candidate GPA rating</t>
   </si>
   <si>
-    <t>0.06s</t>
-  </si>
-  <si>
     <t>FN089: Interactive notifications triggers direct deep links</t>
   </si>
   <si>
-    <t>0.21s</t>
-  </si>
-  <si>
     <t>FN090: Placement opening application submits file uploads checks</t>
   </si>
   <si>
+    <t>FN091: Aptitude test summary shows score history visual graphs</t>
+  </si>
+  <si>
+    <t>FN092: AI voice engine triggers speech synthesis callbacks</t>
+  </si>
+  <si>
+    <t>FN093: Tech quiz handles code snippet formatting indentation</t>
+  </si>
+  <si>
+    <t>FN094: Chat history delete option clears cache files lists</t>
+  </si>
+  <si>
+    <t>FN095: Profile picture delete resets image state to default asset</t>
+  </si>
+  <si>
+    <t>FN096: User preferences save options syncs to cloud storage</t>
+  </si>
+  <si>
+    <t>FN097: Placement applications status update displays alert banner</t>
+  </si>
+  <si>
+    <t>FN098: Notification preferences page enables fine grained options</t>
+  </si>
+  <si>
+    <t>FN099: Onboarding skip option registers skip activity tracking</t>
+  </si>
+  <si>
+    <t>FN100: Auth form submit keys responds to keypad enter event</t>
+  </si>
+  <si>
+    <t>FN101: Chat message delivery status updates status check icon</t>
+  </si>
+  <si>
+    <t>FN102: Profile page history card loads extra rows on scrolling</t>
+  </si>
+  <si>
+    <t>FN103: Feedback text supports sharing metrics features link</t>
+  </si>
+  <si>
+    <t>FN104: Custom tooltips dismisses on user scroll gesture events</t>
+  </si>
+  <si>
+    <t>FN105: Interview summary review page opens deep analysis details</t>
+  </si>
+  <si>
+    <t>FN106: Light mode inputs responds to active autofill values</t>
+  </si>
+  <si>
+    <t>FN107: Settings clear logs deletes internal session records</t>
+  </si>
+  <si>
+    <t>FN108: Job card bookmarks actions updates quick save collections</t>
+  </si>
+  <si>
+    <t>FN109: Speech processing cancels recording on user interrupt click</t>
+  </si>
+  <si>
+    <t>FN110: Test report generates PDF export function execution</t>
+  </si>
+  <si>
+    <t>UN001: Validate email regex check for correct domain format</t>
+  </si>
+  <si>
+    <t>UN002: Validate email regex check rejects spaces</t>
+  </si>
+  <si>
+    <t>UN003: Check password length validator allows 6+ characters</t>
+  </si>
+  <si>
+    <t>UN004: Calculate attendance percentage threshold alert flag</t>
+  </si>
+  <si>
+    <t>UN005: GPA range checker limits score input</t>
+  </si>
+  <si>
+    <t>UN006: Parse Groq LLM API feedback score strings</t>
+  </si>
+  <si>
+    <t>UN007: Format epoch milliseconds into readable relative duration</t>
+  </si>
+  <si>
+    <t>UN008: Name field input constraint validation check</t>
+  </si>
+  <si>
+    <t>UN009: Sanitize user input text to escape script tags</t>
+  </si>
+  <si>
+    <t>UN010: SharedPreferences theme status key checks</t>
+  </si>
+  <si>
+    <t>UN011: Map Groq rating integers to text badges</t>
+  </si>
+  <si>
+    <t>UN012: Calculate test score percentage from raw integers</t>
+  </si>
+  <si>
+    <t>UN013: API keys placeholder detection logic</t>
+  </si>
+  <si>
+    <t>UN014: Question limits bounds validation logic</t>
+  </si>
+  <si>
+    <t>UN015: Parse markdown bullets to list arrays</t>
+  </si>
+  <si>
+    <t>UN016: Format durations into mm:ss format</t>
+  </si>
+  <si>
+    <t>UN017: Platform checker validation parameters</t>
+  </si>
+  <si>
+    <t>UN018: Date parser verification</t>
+  </si>
+  <si>
+    <t>UN019: Firestore structure array mapper logic</t>
+  </si>
+  <si>
+    <t>UN020: Notifications channel settings validation</t>
+  </si>
+  <si>
+    <t>UN021: Phone number sanitization validation</t>
+  </si>
+  <si>
+    <t>UN022: Network offline sync status validator</t>
+  </si>
+  <si>
+    <t>UN023: GPA eligibility for premium placements check</t>
+  </si>
+  <si>
+    <t>UN024: Map test scores to dashboard charts datasets</t>
+  </si>
+  <si>
+    <t>UN025: Chat conversation search filter algorithm</t>
+  </si>
+  <si>
+    <t>UN026: Parse and validate Firestore document reference syntax rules</t>
+  </si>
+  <si>
+    <t>UN027: Map user profile model fields to JSON document maps</t>
+  </si>
+  <si>
+    <t>UN028: Check password regex validation constraints for complex strings</t>
+  </si>
+  <si>
+    <t>UN029: Sanitize user input name string to strip html formatting content</t>
+  </si>
+  <si>
+    <t>UN030: Format raw numeric values to Indian Rupee currency styling format</t>
+  </si>
+  <si>
+    <t>UN031: Check list pagination limits offsets calculator bounds values</t>
+  </si>
+  <si>
+    <t>UN032: Verify security tokens expire timeout calculations metrics</t>
+  </si>
+  <si>
+    <t>UN033: Compare local config timestamp keys against server time variables</t>
+  </si>
+  <si>
+    <t>UN034: Check email addresses domain blacklist checker function results</t>
+  </si>
+  <si>
+    <t>UN035: Sanitize special characters from custom query input strings</t>
+  </si>
+  <si>
+    <t>UN036: Format attendance rates status strings for console reporting</t>
+  </si>
+  <si>
+    <t>UN037: Verify quiz results correct points calculator mapping logic</t>
+  </si>
+  <si>
+    <t>UN038: Check local notifications time schedule objects formats values</t>
+  </si>
+  <si>
+    <t>UN039: Calculate difference in minutes between two timestamp numbers</t>
+  </si>
+  <si>
+    <t>UN040: Verify speech recognition text sanitization helper matches words</t>
+  </si>
+  <si>
+    <t>UN041: Format file bytes sizes numbers into KB and MB text designations</t>
+  </si>
+  <si>
+    <t>UN042: Verify Firestore bulk transaction updates mapping list bounds</t>
+  </si>
+  <si>
+    <t>UN043: Verify chatbot query parameters formats matches api specs</t>
+  </si>
+  <si>
+    <t>UN044: Map placement job applications model status mapping arrays</t>
+  </si>
+  <si>
+    <t>UN045: Convert date string items to relative human readable days logs</t>
+  </si>
+  <si>
+    <t>UN046: Format test scores ranges into category grades letters labels</t>
+  </si>
+  <si>
+    <t>UN047: Validate phone number inputs strings lengths conditions rules</t>
+  </si>
+  <si>
+    <t>UN048: Check network latencies estimation formulas maps ranges boundaries</t>
+  </si>
+  <si>
+    <t>UN049: Parse Markdown bold symbols formats and returns HTML tags content</t>
+  </si>
+  <si>
+    <t>UN050: Map error response error codes numbers to error description lines</t>
+  </si>
+  <si>
+    <t>UN051: Calculate overall scores weighted averages indexes from data map</t>
+  </si>
+  <si>
+    <t>UN052: Check firebase profile settings documents paths structures matching</t>
+  </si>
+  <si>
+    <t>UN053: Validate input username text strings formats constraints check</t>
+  </si>
+  <si>
+    <t>UN054: Parse Groq AI interview feedback scores elements counts values</t>
+  </si>
+  <si>
+    <t>UN055: Verify device platform checks functions outputs correct platform label</t>
+  </si>
+  <si>
+    <t>UN056: Calculate test progress bar percentages indicators from values</t>
+  </si>
+  <si>
+    <t>UN057: Sanitize raw speech records input string characters spacing properties</t>
+  </si>
+  <si>
+    <t>UN058: Verify aptitude quiz question indexes counters logic calculations</t>
+  </si>
+  <si>
+    <t>UN059: Format timestamp to UTC date string parameters maps formats</t>
+  </si>
+  <si>
+    <t>UN060: Validate password validation matches specific complex requirements options</t>
+  </si>
+  <si>
+    <t>UN061: Map career placement details field structures checks to JSON data</t>
+  </si>
+  <si>
+    <t>UN062: Parse and format chat session message logs structure objects array</t>
+  </si>
+  <si>
+    <t>UN063: Calculate dashboard user placements eligibility requirements rating check</t>
+  </si>
+  <si>
+    <t>UN064: Validate notifications schedule intervals ranges bounds parameters</t>
+  </si>
+  <si>
+    <t>UN065: Check offline test caching database insertion mapping constraints</t>
+  </si>
+  <si>
+    <t>UN066: Format user analytics report graphs labels data matrices datasets</t>
+  </si>
+  <si>
+    <t>UN067: Sanitize file upload types names and extensions details arrays</t>
+  </si>
+  <si>
+    <t>UN068: Compare two profile models properties for fields updates differences</t>
+  </si>
+  <si>
+    <t>UN069: Calculate countdown timers thresholds values limits settings checks</t>
+  </si>
+  <si>
+    <t>UN070: Parse user profile address components subfields values constraints</t>
+  </si>
+  <si>
+    <t>UN071: Verify network service offline sync queries execution schedules check</t>
+  </si>
+  <si>
+    <t>UN072: Map error message parameters strings into parameterized warning alerts</t>
+  </si>
+  <si>
+    <t>UN073: Calculate correct test duration hours values labels display options</t>
+  </si>
+  <si>
+    <t>UN074: Check placement opens bookmark state sync boolean states logic</t>
+  </si>
+  <si>
+    <t>UN075: Format AI mock interview response advice snippets headers values</t>
+  </si>
+  <si>
+    <t>UN076: Sanitize chatbot response payload elements from html markers tags</t>
+  </si>
+  <si>
+    <t>UN077: Validate registration signup verification codes structures checks</t>
+  </si>
+  <si>
+    <t>UN078: Map firebase query parameters snapshots into local object structure</t>
+  </si>
+  <si>
+    <t>UN079: Compare dates difference days value checks for active updates status</t>
+  </si>
+  <si>
+    <t>UN080: Calculate test category lists page offsets ranges check values</t>
+  </si>
+  <si>
+    <t>UN081: Check custom search queries tags matching index rating metrics</t>
+  </si>
+  <si>
+    <t>UN082: Format placements openings summary statistics dashboard datasets data</t>
+  </si>
+  <si>
+    <t>UN083: Sanitize settings preference values storage keys maps constraints</t>
+  </si>
+  <si>
+    <t>UN084: Parse company opening job vacancies numbers strings formats logic</t>
+  </si>
+  <si>
+    <t>UN085: Calculate speech to text latency metrics performance benchmarks ranges</t>
+  </si>
+  <si>
+    <t>UN086: Verify custom chatbot logic rejects blank spam inputs queries</t>
+  </si>
+  <si>
+    <t>UN087: Format file modification timestamps numbers into locale format text</t>
+  </si>
+  <si>
+    <t>UN088: Validate placement registration student ID formats checking algorithm</t>
+  </si>
+  <si>
+    <t>UN089: Map profile notification details settings flags parameters boolean arrays</t>
+  </si>
+  <si>
+    <t>UN090: Compare two JSON objects keys structure validation differences results</t>
+  </si>
+  <si>
+    <t>UN091: Calculate offline database synchronize sync priorities values indexes</t>
+  </si>
+  <si>
+    <t>UN092: Parse settings cache sizes records numbers to readable text size</t>
+  </si>
+  <si>
+    <t>UN093: Format custom modal header text capitalization parameters check</t>
+  </si>
+  <si>
+    <t>UN094: Validate input field emails formats domain extension validation rules</t>
+  </si>
+  <si>
+    <t>UN095: Map career placement interviews lists states transitions categories</t>
+  </si>
+  <si>
+    <t>UN096: Compare dynamic CSS properties values mapping colors parameters checks</t>
+  </si>
+  <si>
+    <t>UN097: Calculate test results total metrics standard deviation rating score</t>
+  </si>
+  <si>
+    <t>UN098: Verify local notification sound file name configurations targets</t>
+  </si>
+  <si>
+    <t>UN099: Format raw numbers to double decimals formatting standard method</t>
+  </si>
+  <si>
+    <t>UN100: Validate custom dashboard panel layout alignment parameters logic</t>
+  </si>
+  <si>
+    <t>VL001: Register user empty first name triggers validation</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>VL002: Register user empty last name triggers validation</t>
+  </si>
+  <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>VL003: Register user blank email validation toast</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>VL004: Register user invalid email format display</t>
+  </si>
+  <si>
+    <t>VL005: Register user weak password complexity warning display</t>
+  </si>
+  <si>
+    <t>VL006: Authenticate with invalid email formatting</t>
+  </si>
+  <si>
+    <t>VL007: Authenticate with wrong password key error toast</t>
+  </si>
+  <si>
+    <t>VL008: Submit empty text answer to HR Interviewer returns validation message</t>
+  </si>
+  <si>
+    <t>VL009: Check question counts upper limit constraint</t>
+  </si>
+  <si>
+    <t>VL010: Check question counts lower limit constraint</t>
+  </si>
+  <si>
+    <t>VL011: Submit aptitude test with no questions answered displays alert dialog</t>
+  </si>
+  <si>
+    <t>VL012: Save offline test session log validation check</t>
+  </si>
+  <si>
+    <t>VL013: Submit empty chatbot query displays warning placeholder</t>
+  </si>
+  <si>
+    <t>VL014: Edit profile page with blank username returns input validation warning</t>
+  </si>
+  <si>
+    <t>VL015: Network timeout request simulation logic</t>
+  </si>
+  <si>
+    <t>VL016: Groq API response schema validation matches structure standards</t>
+  </si>
+  <si>
+    <t>VL017: Groq API error structure formatting wrapper parsing</t>
+  </si>
+  <si>
+    <t>VL018: Concurrent db transactions check locks validation rules</t>
+  </si>
+  <si>
+    <t>VL019: Real-time user session status validation updates check</t>
+  </si>
+  <si>
+    <t>VL020: Device camera/microphone permissions denied state warning display</t>
+  </si>
+  <si>
+    <t>VL021: Register password mismatch error confirmation check</t>
+  </si>
+  <si>
+    <t>VL022: Input special characters in email inputs fields prevention</t>
+  </si>
+  <si>
+    <t>VL023: Edit profile username spaces stripping constraints verify</t>
+  </si>
+  <si>
+    <t>VL024: Settings notification preference integer bounds validations</t>
+  </si>
+  <si>
+    <t>VL025: Chat query inputs length restrictions indicators status</t>
+  </si>
+  <si>
+    <t>VL026: Firebase documents key name validation constraint checks</t>
+  </si>
+  <si>
+    <t>VL027: Aptitude questions list json keys schema compatibility checks</t>
+  </si>
+  <si>
+    <t>VL028: Career placement jobs database requirements objects mapping check</t>
+  </si>
+  <si>
+    <t>VL029: Groq key parameter headers validation rules constraint check</t>
+  </si>
+  <si>
+    <t>VL030: Network responses schema status code format validation rules</t>
+  </si>
+  <si>
+    <t>VL031: Check authentication credentials token expiry metadata rules</t>
+  </si>
+  <si>
+    <t>VL032: Verify user age range bounds checks validation rules</t>
+  </si>
+  <si>
+    <t>VL033: Sanitize and validate file attachment types constraints limits</t>
+  </si>
+  <si>
+    <t>VL034: Validate database read batch sizes counts thresholds limits</t>
+  </si>
+  <si>
+    <t>VL035: Check local notifications configuration details schemas objects</t>
+  </si>
+  <si>
+    <t>VL036: Input password fields characters limits verify warning banners</t>
+  </si>
+  <si>
+    <t>VL037: Register phone format input restrictions verification checks</t>
+  </si>
+  <si>
+    <t>VL038: Custom chatbot parameters validation check for null inputs</t>
+  </si>
+  <si>
+    <t>VL039: Error status codes mappings validation against standard tables</t>
+  </si>
+  <si>
+    <t>VL040: Firestore transaction batch size constraints limits check</t>
+  </si>
+  <si>
+    <t>VL041: Onboarding active index indicator limits validation check</t>
+  </si>
+  <si>
+    <t>VL042: Textfields validation warning labels styles constraints checks</t>
+  </si>
+  <si>
+    <t>VL043: Settings theme selection value verification logic ranges</t>
+  </si>
+  <si>
+    <t>VL044: Career openings search query filter input length constraints</t>
+  </si>
+  <si>
+    <t>VL045: Mock interview feedback score metrics integer format check</t>
+  </si>
+  <si>
+    <t>VL046: Speech transcript strings validation for null content elements</t>
+  </si>
+  <si>
+    <t>VL047: Dynamic layouts dimensions offset numbers range checking validation</t>
+  </si>
+  <si>
+    <t>VL048: Firestore collection path strings formatting constraints bounds</t>
+  </si>
+  <si>
+    <t>VL049: User preference key name schemas compatibility checking checks</t>
+  </si>
+  <si>
+    <t>VL050: App notification badge count negative value validations check</t>
+  </si>
+  <si>
+    <t>VL051: Auth token formats validation checks matches regex syntax rules</t>
+  </si>
+  <si>
     <t>0.05s</t>
-  </si>
-  <si>
-    <t>FN091: Aptitude test summary shows score history visual graphs</t>
-  </si>
-  <si>
-    <t>FN092: AI voice engine triggers speech synthesis callbacks</t>
-  </si>
-  <si>
-    <t>FN093: Tech quiz handles code snippet formatting indentation</t>
-  </si>
-  <si>
-    <t>FN094: Chat history delete option clears cache files lists</t>
-  </si>
-  <si>
-    <t>FN095: Profile picture delete resets image state to default asset</t>
-  </si>
-  <si>
-    <t>FN096: User preferences save options syncs to cloud storage</t>
-  </si>
-  <si>
-    <t>FN097: Placement applications status update displays alert banner</t>
-  </si>
-  <si>
-    <t>FN098: Notification preferences page enables fine grained options</t>
-  </si>
-  <si>
-    <t>FN099: Onboarding skip option registers skip activity tracking</t>
-  </si>
-  <si>
-    <t>FN100: Auth form submit keys responds to keypad enter event</t>
-  </si>
-  <si>
-    <t>FN101: Chat message delivery status updates status check icon</t>
-  </si>
-  <si>
-    <t>FN102: Profile page history card loads extra rows on scrolling</t>
-  </si>
-  <si>
-    <t>FN103: Feedback text supports sharing metrics features link</t>
-  </si>
-  <si>
-    <t>FN104: Custom tooltips dismisses on user scroll gesture events</t>
-  </si>
-  <si>
-    <t>FN105: Interview summary review page opens deep analysis details</t>
-  </si>
-  <si>
-    <t>FN106: Light mode inputs responds to active autofill values</t>
-  </si>
-  <si>
-    <t>FN107: Settings clear logs deletes internal session records</t>
-  </si>
-  <si>
-    <t>0.09s</t>
-  </si>
-  <si>
-    <t>FN108: Job card bookmarks actions updates quick save collections</t>
-  </si>
-  <si>
-    <t>FN109: Speech processing cancels recording on user interrupt click</t>
-  </si>
-  <si>
-    <t>FN110: Test report generates PDF export function execution</t>
-  </si>
-  <si>
-    <t>UN001: Validate email regex check for correct domain format</t>
-  </si>
-  <si>
-    <t>UN002: Validate email regex check rejects spaces</t>
-  </si>
-  <si>
-    <t>UN003: Check password length validator allows 6+ characters</t>
-  </si>
-  <si>
-    <t>UN004: Calculate attendance percentage threshold alert flag</t>
-  </si>
-  <si>
-    <t>UN005: GPA range checker limits score input</t>
-  </si>
-  <si>
-    <t>UN006: Parse Groq LLM API feedback score strings</t>
-  </si>
-  <si>
-    <t>UN007: Format epoch milliseconds into readable relative duration</t>
-  </si>
-  <si>
-    <t>UN008: Name field input constraint validation check</t>
-  </si>
-  <si>
-    <t>UN009: Sanitize user input text to escape script tags</t>
-  </si>
-  <si>
-    <t>UN010: SharedPreferences theme status key checks</t>
-  </si>
-  <si>
-    <t>UN011: Map Groq rating integers to text badges</t>
-  </si>
-  <si>
-    <t>UN012: Calculate test score percentage from raw integers</t>
-  </si>
-  <si>
-    <t>UN013: API keys placeholder detection logic</t>
-  </si>
-  <si>
-    <t>UN014: Question limits bounds validation logic</t>
-  </si>
-  <si>
-    <t>UN015: Parse markdown bullets to list arrays</t>
-  </si>
-  <si>
-    <t>UN016: Format durations into mm:ss format</t>
-  </si>
-  <si>
-    <t>UN017: Platform checker validation parameters</t>
-  </si>
-  <si>
-    <t>UN018: Date parser verification</t>
-  </si>
-  <si>
-    <t>UN019: Firestore structure array mapper logic</t>
-  </si>
-  <si>
-    <t>UN020: Notifications channel settings validation</t>
-  </si>
-  <si>
-    <t>UN021: Phone number sanitization validation</t>
-  </si>
-  <si>
-    <t>UN022: Network offline sync status validator</t>
-  </si>
-  <si>
-    <t>UN023: GPA eligibility for premium placements check</t>
-  </si>
-  <si>
-    <t>UN024: Map test scores to dashboard charts datasets</t>
-  </si>
-  <si>
-    <t>UN025: Chat conversation search filter algorithm</t>
-  </si>
-  <si>
-    <t>UN026: Parse and validate Firestore document reference syntax rules</t>
-  </si>
-  <si>
-    <t>UN027: Map user profile model fields to JSON document maps</t>
-  </si>
-  <si>
-    <t>UN028: Check password regex validation constraints for complex strings</t>
-  </si>
-  <si>
-    <t>UN029: Sanitize user input name string to strip html formatting content</t>
-  </si>
-  <si>
-    <t>UN030: Format raw numeric values to Indian Rupee currency styling format</t>
-  </si>
-  <si>
-    <t>UN031: Check list pagination limits offsets calculator bounds values</t>
-  </si>
-  <si>
-    <t>UN032: Verify security tokens expire timeout calculations metrics</t>
-  </si>
-  <si>
-    <t>UN033: Compare local config timestamp keys against server time variables</t>
-  </si>
-  <si>
-    <t>UN034: Check email addresses domain blacklist checker function results</t>
-  </si>
-  <si>
-    <t>UN035: Sanitize special characters from custom query input strings</t>
-  </si>
-  <si>
-    <t>UN036: Format attendance rates status strings for console reporting</t>
-  </si>
-  <si>
-    <t>UN037: Verify quiz results correct points calculator mapping logic</t>
-  </si>
-  <si>
-    <t>UN038: Check local notifications time schedule objects formats values</t>
-  </si>
-  <si>
-    <t>UN039: Calculate difference in minutes between two timestamp numbers</t>
-  </si>
-  <si>
-    <t>UN040: Verify speech recognition text sanitization helper matches words</t>
-  </si>
-  <si>
-    <t>UN041: Format file bytes sizes numbers into KB and MB text designations</t>
-  </si>
-  <si>
-    <t>UN042: Verify Firestore bulk transaction updates mapping list bounds</t>
-  </si>
-  <si>
-    <t>UN043: Verify chatbot query parameters formats matches api specs</t>
-  </si>
-  <si>
-    <t>UN044: Map placement job applications model status mapping arrays</t>
-  </si>
-  <si>
-    <t>UN045: Convert date string items to relative human readable days logs</t>
-  </si>
-  <si>
-    <t>UN046: Format test scores ranges into category grades letters labels</t>
-  </si>
-  <si>
-    <t>UN047: Validate phone number inputs strings lengths conditions rules</t>
-  </si>
-  <si>
-    <t>UN048: Check network latencies estimation formulas maps ranges boundaries</t>
-  </si>
-  <si>
-    <t>UN049: Parse Markdown bold symbols formats and returns HTML tags content</t>
-  </si>
-  <si>
-    <t>UN050: Map error response error codes numbers to error description lines</t>
-  </si>
-  <si>
-    <t>UN051: Calculate overall scores weighted averages indexes from data map</t>
-  </si>
-  <si>
-    <t>UN052: Check firebase profile settings documents paths structures matching</t>
-  </si>
-  <si>
-    <t>UN053: Validate input username text strings formats constraints check</t>
-  </si>
-  <si>
-    <t>UN054: Parse Groq AI interview feedback scores elements counts values</t>
-  </si>
-  <si>
-    <t>UN055: Verify device platform checks functions outputs correct platform label</t>
-  </si>
-  <si>
-    <t>UN056: Calculate test progress bar percentages indicators from values</t>
-  </si>
-  <si>
-    <t>UN057: Sanitize raw speech records input string characters spacing properties</t>
-  </si>
-  <si>
-    <t>UN058: Verify aptitude quiz question indexes counters logic calculations</t>
-  </si>
-  <si>
-    <t>UN059: Format timestamp to UTC date string parameters maps formats</t>
-  </si>
-  <si>
-    <t>UN060: Validate password validation matches specific complex requirements options</t>
-  </si>
-  <si>
-    <t>UN061: Map career placement details field structures checks to JSON data</t>
-  </si>
-  <si>
-    <t>UN062: Parse and format chat session message logs structure objects array</t>
-  </si>
-  <si>
-    <t>UN063: Calculate dashboard user placements eligibility requirements rating check</t>
-  </si>
-  <si>
-    <t>UN064: Validate notifications schedule intervals ranges bounds parameters</t>
-  </si>
-  <si>
-    <t>UN065: Check offline test caching database insertion mapping constraints</t>
-  </si>
-  <si>
-    <t>UN066: Format user analytics report graphs labels data matrices datasets</t>
-  </si>
-  <si>
-    <t>UN067: Sanitize file upload types names and extensions details arrays</t>
-  </si>
-  <si>
-    <t>UN068: Compare two profile models properties for fields updates differences</t>
-  </si>
-  <si>
-    <t>UN069: Calculate countdown timers thresholds values limits settings checks</t>
-  </si>
-  <si>
-    <t>UN070: Parse user profile address components subfields values constraints</t>
-  </si>
-  <si>
-    <t>UN071: Verify network service offline sync queries execution schedules check</t>
-  </si>
-  <si>
-    <t>UN072: Map error message parameters strings into parameterized warning alerts</t>
-  </si>
-  <si>
-    <t>UN073: Calculate correct test duration hours values labels display options</t>
-  </si>
-  <si>
-    <t>UN074: Check placement opens bookmark state sync boolean states logic</t>
-  </si>
-  <si>
-    <t>UN075: Format AI mock interview response advice snippets headers values</t>
-  </si>
-  <si>
-    <t>UN076: Sanitize chatbot response payload elements from html markers tags</t>
-  </si>
-  <si>
-    <t>UN077: Validate registration signup verification codes structures checks</t>
-  </si>
-  <si>
-    <t>UN078: Map firebase query parameters snapshots into local object structure</t>
-  </si>
-  <si>
-    <t>UN079: Compare dates difference days value checks for active updates status</t>
-  </si>
-  <si>
-    <t>UN080: Calculate test category lists page offsets ranges check values</t>
-  </si>
-  <si>
-    <t>UN081: Check custom search queries tags matching index rating metrics</t>
-  </si>
-  <si>
-    <t>UN082: Format placements openings summary statistics dashboard datasets data</t>
-  </si>
-  <si>
-    <t>UN083: Sanitize settings preference values storage keys maps constraints</t>
-  </si>
-  <si>
-    <t>UN084: Parse company opening job vacancies numbers strings formats logic</t>
-  </si>
-  <si>
-    <t>UN085: Calculate speech to text latency metrics performance benchmarks ranges</t>
-  </si>
-  <si>
-    <t>UN086: Verify custom chatbot logic rejects blank spam inputs queries</t>
-  </si>
-  <si>
-    <t>UN087: Format file modification timestamps numbers into locale format text</t>
-  </si>
-  <si>
-    <t>UN088: Validate placement registration student ID formats checking algorithm</t>
-  </si>
-  <si>
-    <t>UN089: Map profile notification details settings flags parameters boolean arrays</t>
-  </si>
-  <si>
-    <t>UN090: Compare two JSON objects keys structure validation differences results</t>
-  </si>
-  <si>
-    <t>UN091: Calculate offline database synchronize sync priorities values indexes</t>
-  </si>
-  <si>
-    <t>UN092: Parse settings cache sizes records numbers to readable text size</t>
-  </si>
-  <si>
-    <t>UN093: Format custom modal header text capitalization parameters check</t>
-  </si>
-  <si>
-    <t>UN094: Validate input field emails formats domain extension validation rules</t>
-  </si>
-  <si>
-    <t>UN095: Map career placement interviews lists states transitions categories</t>
-  </si>
-  <si>
-    <t>UN096: Compare dynamic CSS properties values mapping colors parameters checks</t>
-  </si>
-  <si>
-    <t>UN097: Calculate test results total metrics standard deviation rating score</t>
-  </si>
-  <si>
-    <t>UN098: Verify local notification sound file name configurations targets</t>
-  </si>
-  <si>
-    <t>UN099: Format raw numbers to double decimals formatting standard method</t>
-  </si>
-  <si>
-    <t>UN100: Validate custom dashboard panel layout alignment parameters logic</t>
-  </si>
-  <si>
-    <t>VL001: Register user empty first name triggers validation</t>
-  </si>
-  <si>
-    <t>0.10s</t>
-  </si>
-  <si>
-    <t>VL002: Register user empty last name triggers validation</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>VL003: Register user blank email validation toast</t>
-  </si>
-  <si>
-    <t>VL004: Register user invalid email format display</t>
-  </si>
-  <si>
-    <t>VL005: Register user weak password complexity warning display</t>
-  </si>
-  <si>
-    <t>VL006: Authenticate with invalid email formatting</t>
-  </si>
-  <si>
-    <t>VL007: Authenticate with wrong password key error toast</t>
-  </si>
-  <si>
-    <t>VL008: Submit empty text answer to HR Interviewer returns validation message</t>
-  </si>
-  <si>
-    <t>VL009: Check question counts upper limit constraint</t>
-  </si>
-  <si>
-    <t>VL010: Check question counts lower limit constraint</t>
-  </si>
-  <si>
-    <t>VL011: Submit aptitude test with no questions answered displays alert dialog</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>VL012: Save offline test session log validation check</t>
-  </si>
-  <si>
-    <t>VL013: Submit empty chatbot query displays warning placeholder</t>
-  </si>
-  <si>
-    <t>VL014: Edit profile page with blank username returns input validation warning</t>
-  </si>
-  <si>
-    <t>VL015: Network timeout request simulation logic</t>
-  </si>
-  <si>
-    <t>VL016: Groq API response schema validation matches structure standards</t>
-  </si>
-  <si>
-    <t>VL017: Groq API error structure formatting wrapper parsing</t>
-  </si>
-  <si>
-    <t>VL018: Concurrent db transactions check locks validation rules</t>
-  </si>
-  <si>
-    <t>VL019: Real-time user session status validation updates check</t>
-  </si>
-  <si>
-    <t>VL020: Device camera/microphone permissions denied state warning display</t>
-  </si>
-  <si>
-    <t>VL021: Register password mismatch error confirmation check</t>
-  </si>
-  <si>
-    <t>VL022: Input special characters in email inputs fields prevention</t>
-  </si>
-  <si>
-    <t>VL023: Edit profile username spaces stripping constraints verify</t>
-  </si>
-  <si>
-    <t>VL024: Settings notification preference integer bounds validations</t>
-  </si>
-  <si>
-    <t>VL025: Chat query inputs length restrictions indicators status</t>
-  </si>
-  <si>
-    <t>VL026: Firebase documents key name validation constraint checks</t>
-  </si>
-  <si>
-    <t>VL027: Aptitude questions list json keys schema compatibility checks</t>
-  </si>
-  <si>
-    <t>VL028: Career placement jobs database requirements objects mapping check</t>
-  </si>
-  <si>
-    <t>VL029: Groq key parameter headers validation rules constraint check</t>
-  </si>
-  <si>
-    <t>VL030: Network responses schema status code format validation rules</t>
-  </si>
-  <si>
-    <t>VL031: Check authentication credentials token expiry metadata rules</t>
-  </si>
-  <si>
-    <t>VL032: Verify user age range bounds checks validation rules</t>
-  </si>
-  <si>
-    <t>VL033: Sanitize and validate file attachment types constraints limits</t>
-  </si>
-  <si>
-    <t>VL034: Validate database read batch sizes counts thresholds limits</t>
-  </si>
-  <si>
-    <t>VL035: Check local notifications configuration details schemas objects</t>
-  </si>
-  <si>
-    <t>VL036: Input password fields characters limits verify warning banners</t>
-  </si>
-  <si>
-    <t>VL037: Register phone format input restrictions verification checks</t>
-  </si>
-  <si>
-    <t>VL038: Custom chatbot parameters validation check for null inputs</t>
-  </si>
-  <si>
-    <t>VL039: Error status codes mappings validation against standard tables</t>
-  </si>
-  <si>
-    <t>VL040: Firestore transaction batch size constraints limits check</t>
-  </si>
-  <si>
-    <t>VL041: Onboarding active index indicator limits validation check</t>
-  </si>
-  <si>
-    <t>VL042: Textfields validation warning labels styles constraints checks</t>
-  </si>
-  <si>
-    <t>VL043: Settings theme selection value verification logic ranges</t>
-  </si>
-  <si>
-    <t>VL044: Career openings search query filter input length constraints</t>
-  </si>
-  <si>
-    <t>VL045: Mock interview feedback score metrics integer format check</t>
-  </si>
-  <si>
-    <t>VL046: Speech transcript strings validation for null content elements</t>
-  </si>
-  <si>
-    <t>VL047: Dynamic layouts dimensions offset numbers range checking validation</t>
-  </si>
-  <si>
-    <t>VL048: Firestore collection path strings formatting constraints bounds</t>
-  </si>
-  <si>
-    <t>VL049: User preference key name schemas compatibility checking checks</t>
-  </si>
-  <si>
-    <t>VL050: App notification badge count negative value validations check</t>
-  </si>
-  <si>
-    <t>VL051: Auth token formats validation checks matches regex syntax rules</t>
   </si>
   <si>
     <t>VL052: Custom dashboard stats metrics numerical constraints boundaries</t>
@@ -2128,7 +2113,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>27</v>
@@ -2139,13 +2124,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>27</v>
@@ -2156,13 +2141,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>27</v>
@@ -2173,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>25</v>
@@ -2190,13 +2175,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>27</v>
@@ -2207,7 +2192,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>25</v>
@@ -2224,13 +2209,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>39</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>27</v>
@@ -2241,7 +2226,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>25</v>
@@ -2258,7 +2243,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>25</v>
@@ -2275,13 +2260,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>39</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>27</v>
@@ -2366,7 +2351,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>27</v>
@@ -2377,13 +2362,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>29</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>27</v>
@@ -2394,13 +2379,13 @@
         <v>7</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>27</v>
@@ -2411,13 +2396,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>27</v>
@@ -2428,13 +2413,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>27</v>
@@ -2445,13 +2430,13 @@
         <v>7</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>27</v>
@@ -2462,13 +2447,13 @@
         <v>7</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>27</v>
@@ -2479,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>25</v>
@@ -2496,13 +2481,13 @@
         <v>7</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>27</v>
@@ -2513,13 +2498,13 @@
         <v>7</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>27</v>
@@ -2530,13 +2515,13 @@
         <v>7</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>27</v>
@@ -2570,7 +2555,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>27</v>
@@ -2689,7 +2674,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>27</v>
@@ -2859,7 +2844,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>27</v>
@@ -3318,7 +3303,7 @@
         <v>25</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>27</v>
@@ -3403,7 +3388,7 @@
         <v>25</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>27</v>
@@ -3811,7 +3796,7 @@
         <v>25</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>27</v>
@@ -3828,7 +3813,7 @@
         <v>25</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>27</v>
@@ -3845,7 +3830,7 @@
         <v>25</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>27</v>
@@ -3856,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>25</v>
@@ -3873,13 +3858,13 @@
         <v>7</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>27</v>
@@ -3890,7 +3875,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>25</v>
@@ -3907,7 +3892,7 @@
         <v>7</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>25</v>
@@ -3924,7 +3909,7 @@
         <v>7</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>25</v>
@@ -3941,7 +3926,7 @@
         <v>7</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>25</v>
@@ -3958,13 +3943,13 @@
         <v>10</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>27</v>
@@ -3998,7 +3983,7 @@
         <v>25</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>27</v>
@@ -4009,13 +3994,13 @@
         <v>10</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C115" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>27</v>
@@ -4026,13 +4011,13 @@
         <v>10</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>27</v>
@@ -4049,7 +4034,7 @@
         <v>25</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>27</v>
@@ -4060,13 +4045,13 @@
         <v>10</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>27</v>
@@ -4083,7 +4068,7 @@
         <v>25</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>27</v>
@@ -4117,7 +4102,7 @@
         <v>25</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>27</v>
@@ -4151,7 +4136,7 @@
         <v>25</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>27</v>
@@ -4168,7 +4153,7 @@
         <v>25</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>27</v>
@@ -4185,7 +4170,7 @@
         <v>25</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>27</v>
@@ -4196,13 +4181,13 @@
         <v>10</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>27</v>
@@ -4213,13 +4198,13 @@
         <v>10</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C127" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>27</v>
@@ -4230,13 +4215,13 @@
         <v>10</v>
       </c>
       <c r="B128" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D128" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>27</v>
@@ -4247,13 +4232,13 @@
         <v>10</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C129" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>27</v>
@@ -4264,13 +4249,13 @@
         <v>10</v>
       </c>
       <c r="B130" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D130" s="12" t="s">
         <v>172</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>173</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>27</v>
@@ -4281,13 +4266,13 @@
         <v>10</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C131" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>27</v>
@@ -4298,13 +4283,13 @@
         <v>10</v>
       </c>
       <c r="B132" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D132" s="12" t="s">
         <v>175</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>176</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>27</v>
@@ -4315,13 +4300,13 @@
         <v>10</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C133" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>27</v>
@@ -4332,13 +4317,13 @@
         <v>10</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>27</v>
@@ -4349,13 +4334,13 @@
         <v>10</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C135" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>27</v>
@@ -4366,13 +4351,13 @@
         <v>10</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>27</v>
@@ -4383,13 +4368,13 @@
         <v>10</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C137" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>27</v>
@@ -4400,13 +4385,13 @@
         <v>10</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>27</v>
@@ -4417,13 +4402,13 @@
         <v>10</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C139" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>27</v>
@@ -4434,13 +4419,13 @@
         <v>10</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>27</v>
@@ -4451,13 +4436,13 @@
         <v>10</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>27</v>
@@ -4468,7 +4453,7 @@
         <v>10</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>25</v>
@@ -4485,7 +4470,7 @@
         <v>10</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>25</v>
@@ -4502,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>25</v>
@@ -4519,7 +4504,7 @@
         <v>10</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>25</v>
@@ -4536,7 +4521,7 @@
         <v>10</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>25</v>
@@ -4553,7 +4538,7 @@
         <v>10</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>25</v>
@@ -4570,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>25</v>
@@ -4587,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>25</v>
@@ -4604,13 +4589,13 @@
         <v>10</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>27</v>
@@ -4621,7 +4606,7 @@
         <v>10</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>25</v>
@@ -4638,7 +4623,7 @@
         <v>10</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>25</v>
@@ -4655,7 +4640,7 @@
         <v>10</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>25</v>
@@ -4672,7 +4657,7 @@
         <v>10</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>25</v>
@@ -4689,7 +4674,7 @@
         <v>10</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C155" s="11" t="s">
         <v>25</v>
@@ -4706,7 +4691,7 @@
         <v>10</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C156" s="11" t="s">
         <v>25</v>
@@ -4723,7 +4708,7 @@
         <v>10</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>25</v>
@@ -4740,7 +4725,7 @@
         <v>10</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>25</v>
@@ -4757,7 +4742,7 @@
         <v>10</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C159" s="11" t="s">
         <v>25</v>
@@ -4774,13 +4759,13 @@
         <v>10</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E160" s="10" t="s">
         <v>27</v>
@@ -4791,7 +4776,7 @@
         <v>10</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>25</v>
@@ -4808,7 +4793,7 @@
         <v>10</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>25</v>
@@ -4825,7 +4810,7 @@
         <v>10</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>25</v>
@@ -4842,7 +4827,7 @@
         <v>10</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>25</v>
@@ -4859,7 +4844,7 @@
         <v>10</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>25</v>
@@ -4876,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>25</v>
@@ -4893,7 +4878,7 @@
         <v>10</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>25</v>
@@ -4910,7 +4895,7 @@
         <v>10</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>25</v>
@@ -4927,7 +4912,7 @@
         <v>10</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>25</v>
@@ -4944,7 +4929,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>25</v>
@@ -4961,7 +4946,7 @@
         <v>10</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>25</v>
@@ -4978,7 +4963,7 @@
         <v>10</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>25</v>
@@ -4995,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>25</v>
@@ -5012,7 +4997,7 @@
         <v>10</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>25</v>
@@ -5029,7 +5014,7 @@
         <v>10</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>25</v>
@@ -5046,7 +5031,7 @@
         <v>10</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>25</v>
@@ -5063,7 +5048,7 @@
         <v>10</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>25</v>
@@ -5080,7 +5065,7 @@
         <v>10</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>25</v>
@@ -5097,7 +5082,7 @@
         <v>10</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>25</v>
@@ -5114,13 +5099,13 @@
         <v>10</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="E180" s="10" t="s">
         <v>27</v>
@@ -5131,7 +5116,7 @@
         <v>10</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>25</v>
@@ -5148,13 +5133,13 @@
         <v>10</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E182" s="10" t="s">
         <v>27</v>
@@ -5165,7 +5150,7 @@
         <v>10</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C183" s="11" t="s">
         <v>25</v>
@@ -5182,7 +5167,7 @@
         <v>10</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>25</v>
@@ -5199,7 +5184,7 @@
         <v>10</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>25</v>
@@ -5216,7 +5201,7 @@
         <v>10</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>25</v>
@@ -5233,7 +5218,7 @@
         <v>10</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>25</v>
@@ -5250,7 +5235,7 @@
         <v>10</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>25</v>
@@ -5267,7 +5252,7 @@
         <v>10</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>25</v>
@@ -5284,7 +5269,7 @@
         <v>10</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>25</v>
@@ -5301,7 +5286,7 @@
         <v>10</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>25</v>
@@ -5318,7 +5303,7 @@
         <v>10</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>25</v>
@@ -5335,7 +5320,7 @@
         <v>10</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>25</v>
@@ -5352,7 +5337,7 @@
         <v>10</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>25</v>
@@ -5369,7 +5354,7 @@
         <v>10</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>25</v>
@@ -5386,7 +5371,7 @@
         <v>10</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>25</v>
@@ -5403,7 +5388,7 @@
         <v>10</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>25</v>
@@ -5420,7 +5405,7 @@
         <v>10</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>25</v>
@@ -5437,13 +5422,13 @@
         <v>10</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D199" s="12" t="s">
-        <v>246</v>
+        <v>29</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>27</v>
@@ -5454,13 +5439,13 @@
         <v>10</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D200" s="12" t="s">
-        <v>248</v>
+        <v>29</v>
       </c>
       <c r="E200" s="10" t="s">
         <v>27</v>
@@ -5471,13 +5456,13 @@
         <v>10</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D201" s="12" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>27</v>
@@ -5488,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>25</v>
@@ -5505,7 +5490,7 @@
         <v>10</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>25</v>
@@ -5522,7 +5507,7 @@
         <v>10</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>25</v>
@@ -5539,7 +5524,7 @@
         <v>10</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>25</v>
@@ -5556,7 +5541,7 @@
         <v>10</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>25</v>
@@ -5573,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>25</v>
@@ -5590,7 +5575,7 @@
         <v>10</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>25</v>
@@ -5607,13 +5592,13 @@
         <v>10</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D209" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>27</v>
@@ -5624,7 +5609,7 @@
         <v>10</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>25</v>
@@ -5641,7 +5626,7 @@
         <v>10</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C211" s="11" t="s">
         <v>25</v>
@@ -5658,7 +5643,7 @@
         <v>10</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>25</v>
@@ -5675,7 +5660,7 @@
         <v>10</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>25</v>
@@ -5692,7 +5677,7 @@
         <v>10</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C214" s="11" t="s">
         <v>25</v>
@@ -5709,7 +5694,7 @@
         <v>10</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C215" s="11" t="s">
         <v>25</v>
@@ -5726,7 +5711,7 @@
         <v>10</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>25</v>
@@ -5743,13 +5728,13 @@
         <v>10</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C217" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D217" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>27</v>
@@ -5760,13 +5745,13 @@
         <v>10</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D218" s="12" t="s">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="E218" s="10" t="s">
         <v>27</v>
@@ -5777,13 +5762,13 @@
         <v>10</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D219" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>27</v>
@@ -5794,7 +5779,7 @@
         <v>10</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C220" s="11" t="s">
         <v>25</v>
@@ -5811,7 +5796,7 @@
         <v>10</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C221" s="11" t="s">
         <v>25</v>
@@ -5828,13 +5813,13 @@
         <v>12</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C222" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E222" s="10" t="s">
         <v>27</v>
@@ -5845,13 +5830,13 @@
         <v>12</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C223" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>27</v>
@@ -5862,13 +5847,13 @@
         <v>12</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C224" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E224" s="10" t="s">
         <v>27</v>
@@ -5879,13 +5864,13 @@
         <v>12</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C225" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>27</v>
@@ -5896,13 +5881,13 @@
         <v>12</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C226" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E226" s="10" t="s">
         <v>27</v>
@@ -5913,13 +5898,13 @@
         <v>12</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C227" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D227" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>27</v>
@@ -5930,13 +5915,13 @@
         <v>12</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C228" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D228" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E228" s="10" t="s">
         <v>27</v>
@@ -5947,13 +5932,13 @@
         <v>12</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C229" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D229" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>27</v>
@@ -5964,13 +5949,13 @@
         <v>12</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C230" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D230" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E230" s="10" t="s">
         <v>27</v>
@@ -5981,13 +5966,13 @@
         <v>12</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C231" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D231" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>27</v>
@@ -5998,13 +5983,13 @@
         <v>12</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C232" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D232" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E232" s="10" t="s">
         <v>27</v>
@@ -6015,13 +6000,13 @@
         <v>12</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C233" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D233" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>27</v>
@@ -6032,13 +6017,13 @@
         <v>12</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C234" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E234" s="10" t="s">
         <v>27</v>
@@ -6049,13 +6034,13 @@
         <v>12</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C235" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D235" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>27</v>
@@ -6066,13 +6051,13 @@
         <v>12</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C236" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E236" s="10" t="s">
         <v>27</v>
@@ -6083,13 +6068,13 @@
         <v>12</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C237" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D237" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>27</v>
@@ -6100,13 +6085,13 @@
         <v>12</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C238" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D238" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E238" s="10" t="s">
         <v>27</v>
@@ -6117,13 +6102,13 @@
         <v>12</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C239" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D239" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>27</v>
@@ -6134,13 +6119,13 @@
         <v>12</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C240" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E240" s="10" t="s">
         <v>27</v>
@@ -6151,13 +6136,13 @@
         <v>12</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C241" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D241" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E241" s="10" t="s">
         <v>27</v>
@@ -6168,13 +6153,13 @@
         <v>12</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C242" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D242" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E242" s="10" t="s">
         <v>27</v>
@@ -6185,13 +6170,13 @@
         <v>12</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C243" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D243" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E243" s="10" t="s">
         <v>27</v>
@@ -6202,13 +6187,13 @@
         <v>12</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C244" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D244" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E244" s="10" t="s">
         <v>27</v>
@@ -6219,13 +6204,13 @@
         <v>12</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C245" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D245" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E245" s="10" t="s">
         <v>27</v>
@@ -6236,13 +6221,13 @@
         <v>12</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C246" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D246" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E246" s="10" t="s">
         <v>27</v>
@@ -6253,13 +6238,13 @@
         <v>12</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C247" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D247" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E247" s="10" t="s">
         <v>27</v>
@@ -6270,13 +6255,13 @@
         <v>12</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C248" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E248" s="10" t="s">
         <v>27</v>
@@ -6287,13 +6272,13 @@
         <v>12</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C249" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D249" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E249" s="10" t="s">
         <v>27</v>
@@ -6304,13 +6289,13 @@
         <v>12</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C250" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D250" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E250" s="10" t="s">
         <v>27</v>
@@ -6321,13 +6306,13 @@
         <v>12</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C251" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D251" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E251" s="10" t="s">
         <v>27</v>
@@ -6338,13 +6323,13 @@
         <v>12</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C252" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D252" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E252" s="10" t="s">
         <v>27</v>
@@ -6355,13 +6340,13 @@
         <v>12</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C253" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D253" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E253" s="10" t="s">
         <v>27</v>
@@ -6372,13 +6357,13 @@
         <v>12</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C254" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E254" s="10" t="s">
         <v>27</v>
@@ -6389,13 +6374,13 @@
         <v>12</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C255" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D255" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E255" s="10" t="s">
         <v>27</v>
@@ -6406,13 +6391,13 @@
         <v>12</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D256" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E256" s="10" t="s">
         <v>27</v>
@@ -6423,13 +6408,13 @@
         <v>12</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D257" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E257" s="10" t="s">
         <v>27</v>
@@ -6440,13 +6425,13 @@
         <v>12</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D258" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E258" s="10" t="s">
         <v>27</v>
@@ -6457,13 +6442,13 @@
         <v>12</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D259" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E259" s="10" t="s">
         <v>27</v>
@@ -6474,13 +6459,13 @@
         <v>12</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D260" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E260" s="10" t="s">
         <v>27</v>
@@ -6491,13 +6476,13 @@
         <v>12</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D261" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E261" s="10" t="s">
         <v>27</v>
@@ -6508,13 +6493,13 @@
         <v>12</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D262" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E262" s="10" t="s">
         <v>27</v>
@@ -6525,13 +6510,13 @@
         <v>12</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C263" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D263" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E263" s="10" t="s">
         <v>27</v>
@@ -6542,13 +6527,13 @@
         <v>12</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C264" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D264" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E264" s="10" t="s">
         <v>27</v>
@@ -6559,13 +6544,13 @@
         <v>12</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D265" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E265" s="10" t="s">
         <v>27</v>
@@ -6576,13 +6561,13 @@
         <v>12</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C266" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D266" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E266" s="10" t="s">
         <v>27</v>
@@ -6593,13 +6578,13 @@
         <v>12</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C267" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D267" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E267" s="10" t="s">
         <v>27</v>
@@ -6610,13 +6595,13 @@
         <v>12</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D268" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E268" s="10" t="s">
         <v>27</v>
@@ -6627,13 +6612,13 @@
         <v>12</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C269" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D269" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E269" s="10" t="s">
         <v>27</v>
@@ -6644,13 +6629,13 @@
         <v>12</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D270" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E270" s="10" t="s">
         <v>27</v>
@@ -6661,13 +6646,13 @@
         <v>12</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C271" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D271" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E271" s="10" t="s">
         <v>27</v>
@@ -6678,13 +6663,13 @@
         <v>12</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D272" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E272" s="10" t="s">
         <v>27</v>
@@ -6695,13 +6680,13 @@
         <v>12</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C273" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D273" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E273" s="10" t="s">
         <v>27</v>
@@ -6712,13 +6697,13 @@
         <v>12</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C274" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D274" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E274" s="10" t="s">
         <v>27</v>
@@ -6729,13 +6714,13 @@
         <v>12</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C275" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D275" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E275" s="10" t="s">
         <v>27</v>
@@ -6746,13 +6731,13 @@
         <v>12</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C276" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D276" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E276" s="10" t="s">
         <v>27</v>
@@ -6763,13 +6748,13 @@
         <v>12</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C277" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D277" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E277" s="10" t="s">
         <v>27</v>
@@ -6780,13 +6765,13 @@
         <v>12</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C278" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D278" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E278" s="10" t="s">
         <v>27</v>
@@ -6797,13 +6782,13 @@
         <v>12</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C279" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D279" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E279" s="10" t="s">
         <v>27</v>
@@ -6814,13 +6799,13 @@
         <v>12</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C280" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D280" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E280" s="10" t="s">
         <v>27</v>
@@ -6831,13 +6816,13 @@
         <v>12</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C281" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D281" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E281" s="10" t="s">
         <v>27</v>
@@ -6848,13 +6833,13 @@
         <v>12</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C282" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D282" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E282" s="10" t="s">
         <v>27</v>
@@ -6865,13 +6850,13 @@
         <v>12</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C283" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D283" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E283" s="10" t="s">
         <v>27</v>
@@ -6882,13 +6867,13 @@
         <v>12</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C284" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D284" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E284" s="10" t="s">
         <v>27</v>
@@ -6899,13 +6884,13 @@
         <v>12</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C285" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D285" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E285" s="10" t="s">
         <v>27</v>
@@ -6916,13 +6901,13 @@
         <v>12</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C286" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D286" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E286" s="10" t="s">
         <v>27</v>
@@ -6933,13 +6918,13 @@
         <v>12</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C287" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D287" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E287" s="10" t="s">
         <v>27</v>
@@ -6950,13 +6935,13 @@
         <v>12</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C288" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D288" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E288" s="10" t="s">
         <v>27</v>
@@ -6967,13 +6952,13 @@
         <v>12</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C289" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D289" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E289" s="10" t="s">
         <v>27</v>
@@ -6984,13 +6969,13 @@
         <v>12</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C290" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E290" s="10" t="s">
         <v>27</v>
@@ -7001,13 +6986,13 @@
         <v>12</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C291" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E291" s="10" t="s">
         <v>27</v>
@@ -7018,13 +7003,13 @@
         <v>12</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C292" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E292" s="10" t="s">
         <v>27</v>
@@ -7035,13 +7020,13 @@
         <v>12</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C293" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D293" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E293" s="10" t="s">
         <v>27</v>
@@ -7052,13 +7037,13 @@
         <v>12</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C294" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D294" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E294" s="10" t="s">
         <v>27</v>
@@ -7069,13 +7054,13 @@
         <v>12</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C295" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D295" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E295" s="10" t="s">
         <v>27</v>
@@ -7086,13 +7071,13 @@
         <v>12</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C296" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D296" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E296" s="10" t="s">
         <v>27</v>
@@ -7103,13 +7088,13 @@
         <v>12</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C297" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D297" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E297" s="10" t="s">
         <v>27</v>
@@ -7120,13 +7105,13 @@
         <v>12</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C298" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D298" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E298" s="10" t="s">
         <v>27</v>
@@ -7137,13 +7122,13 @@
         <v>12</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C299" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D299" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E299" s="10" t="s">
         <v>27</v>
@@ -7154,13 +7139,13 @@
         <v>12</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C300" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D300" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E300" s="10" t="s">
         <v>27</v>
@@ -7171,13 +7156,13 @@
         <v>12</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C301" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D301" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E301" s="10" t="s">
         <v>27</v>
@@ -7188,13 +7173,13 @@
         <v>12</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C302" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D302" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E302" s="10" t="s">
         <v>27</v>
@@ -7205,13 +7190,13 @@
         <v>12</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C303" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D303" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E303" s="10" t="s">
         <v>27</v>
@@ -7222,13 +7207,13 @@
         <v>12</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C304" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D304" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E304" s="10" t="s">
         <v>27</v>
@@ -7239,13 +7224,13 @@
         <v>12</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C305" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D305" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E305" s="10" t="s">
         <v>27</v>
@@ -7256,13 +7241,13 @@
         <v>12</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C306" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D306" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E306" s="10" t="s">
         <v>27</v>
@@ -7273,13 +7258,13 @@
         <v>12</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C307" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D307" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E307" s="10" t="s">
         <v>27</v>
@@ -7290,13 +7275,13 @@
         <v>12</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C308" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D308" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E308" s="10" t="s">
         <v>27</v>
@@ -7307,13 +7292,13 @@
         <v>12</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C309" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E309" s="10" t="s">
         <v>27</v>
@@ -7324,13 +7309,13 @@
         <v>12</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C310" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D310" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E310" s="10" t="s">
         <v>27</v>
@@ -7341,13 +7326,13 @@
         <v>12</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C311" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D311" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E311" s="10" t="s">
         <v>27</v>
@@ -7358,13 +7343,13 @@
         <v>12</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C312" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D312" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E312" s="10" t="s">
         <v>27</v>
@@ -7375,13 +7360,13 @@
         <v>12</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C313" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D313" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E313" s="10" t="s">
         <v>27</v>
@@ -7392,13 +7377,13 @@
         <v>12</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C314" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D314" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E314" s="10" t="s">
         <v>27</v>
@@ -7409,13 +7394,13 @@
         <v>12</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C315" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D315" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E315" s="10" t="s">
         <v>27</v>
@@ -7426,13 +7411,13 @@
         <v>12</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C316" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D316" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E316" s="10" t="s">
         <v>27</v>
@@ -7443,13 +7428,13 @@
         <v>12</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C317" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D317" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E317" s="10" t="s">
         <v>27</v>
@@ -7460,13 +7445,13 @@
         <v>12</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C318" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D318" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E318" s="10" t="s">
         <v>27</v>
@@ -7477,13 +7462,13 @@
         <v>12</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C319" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D319" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E319" s="10" t="s">
         <v>27</v>
@@ -7494,13 +7479,13 @@
         <v>12</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C320" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D320" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E320" s="10" t="s">
         <v>27</v>
@@ -7511,13 +7496,13 @@
         <v>12</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C321" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D321" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E321" s="10" t="s">
         <v>27</v>
@@ -7528,13 +7513,13 @@
         <v>14</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C322" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D322" s="12" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E322" s="10" t="s">
         <v>27</v>
@@ -7545,13 +7530,13 @@
         <v>14</v>
       </c>
       <c r="B323" s="10" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C323" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D323" s="12" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E323" s="10" t="s">
         <v>27</v>
@@ -7562,13 +7547,13 @@
         <v>14</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C324" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D324" s="12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E324" s="10" t="s">
         <v>27</v>
@@ -7579,13 +7564,13 @@
         <v>14</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C325" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D325" s="12" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E325" s="10" t="s">
         <v>27</v>
@@ -7596,13 +7581,13 @@
         <v>14</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C326" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D326" s="12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E326" s="10" t="s">
         <v>27</v>
@@ -7613,13 +7598,13 @@
         <v>14</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C327" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D327" s="12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E327" s="10" t="s">
         <v>27</v>
@@ -7630,13 +7615,13 @@
         <v>14</v>
       </c>
       <c r="B328" s="10" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C328" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D328" s="12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E328" s="10" t="s">
         <v>27</v>
@@ -7647,13 +7632,13 @@
         <v>14</v>
       </c>
       <c r="B329" s="10" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C329" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D329" s="12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E329" s="10" t="s">
         <v>27</v>
@@ -7664,13 +7649,13 @@
         <v>14</v>
       </c>
       <c r="B330" s="10" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C330" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D330" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E330" s="10" t="s">
         <v>27</v>
@@ -7681,13 +7666,13 @@
         <v>14</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C331" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D331" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E331" s="10" t="s">
         <v>27</v>
@@ -7698,13 +7683,13 @@
         <v>14</v>
       </c>
       <c r="B332" s="10" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C332" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D332" s="12" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="E332" s="10" t="s">
         <v>27</v>
@@ -7715,13 +7700,13 @@
         <v>14</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C333" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D333" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E333" s="10" t="s">
         <v>27</v>
@@ -7732,13 +7717,13 @@
         <v>14</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C334" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D334" s="12" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E334" s="10" t="s">
         <v>27</v>
@@ -7749,13 +7734,13 @@
         <v>14</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C335" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D335" s="12" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E335" s="10" t="s">
         <v>27</v>
@@ -7766,13 +7751,13 @@
         <v>14</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C336" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D336" s="12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E336" s="10" t="s">
         <v>27</v>
@@ -7783,13 +7768,13 @@
         <v>14</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C337" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D337" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E337" s="10" t="s">
         <v>27</v>
@@ -7800,13 +7785,13 @@
         <v>14</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C338" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D338" s="12" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E338" s="10" t="s">
         <v>27</v>
@@ -7817,13 +7802,13 @@
         <v>14</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C339" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D339" s="12" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E339" s="10" t="s">
         <v>27</v>
@@ -7834,13 +7819,13 @@
         <v>14</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C340" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D340" s="12" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E340" s="10" t="s">
         <v>27</v>
@@ -7851,13 +7836,13 @@
         <v>14</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C341" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D341" s="12" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E341" s="10" t="s">
         <v>27</v>
@@ -7868,7 +7853,7 @@
         <v>14</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C342" s="11" t="s">
         <v>25</v>
@@ -7885,7 +7870,7 @@
         <v>14</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C343" s="11" t="s">
         <v>25</v>
@@ -7902,13 +7887,13 @@
         <v>14</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C344" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E344" s="10" t="s">
         <v>27</v>
@@ -7919,13 +7904,13 @@
         <v>14</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C345" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D345" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E345" s="10" t="s">
         <v>27</v>
@@ -7936,7 +7921,7 @@
         <v>14</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C346" s="11" t="s">
         <v>25</v>
@@ -7953,13 +7938,13 @@
         <v>14</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C347" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E347" s="10" t="s">
         <v>27</v>
@@ -7970,13 +7955,13 @@
         <v>14</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C348" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E348" s="10" t="s">
         <v>27</v>
@@ -7987,7 +7972,7 @@
         <v>14</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C349" s="11" t="s">
         <v>25</v>
@@ -8004,13 +7989,13 @@
         <v>14</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C350" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E350" s="10" t="s">
         <v>27</v>
@@ -8021,13 +8006,13 @@
         <v>14</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C351" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D351" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E351" s="10" t="s">
         <v>27</v>
@@ -8038,13 +8023,13 @@
         <v>14</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C352" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E352" s="10" t="s">
         <v>27</v>
@@ -8055,13 +8040,13 @@
         <v>14</v>
       </c>
       <c r="B353" s="10" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C353" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E353" s="10" t="s">
         <v>27</v>
@@ -8072,13 +8057,13 @@
         <v>14</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C354" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E354" s="10" t="s">
         <v>27</v>
@@ -8089,13 +8074,13 @@
         <v>14</v>
       </c>
       <c r="B355" s="10" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C355" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E355" s="10" t="s">
         <v>27</v>
@@ -8106,13 +8091,13 @@
         <v>14</v>
       </c>
       <c r="B356" s="10" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C356" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E356" s="10" t="s">
         <v>27</v>
@@ -8123,13 +8108,13 @@
         <v>14</v>
       </c>
       <c r="B357" s="10" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C357" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E357" s="10" t="s">
         <v>27</v>
@@ -8140,13 +8125,13 @@
         <v>14</v>
       </c>
       <c r="B358" s="10" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C358" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E358" s="10" t="s">
         <v>27</v>
@@ -8157,13 +8142,13 @@
         <v>14</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C359" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E359" s="10" t="s">
         <v>27</v>
@@ -8174,13 +8159,13 @@
         <v>14</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C360" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E360" s="10" t="s">
         <v>27</v>
@@ -8191,7 +8176,7 @@
         <v>14</v>
       </c>
       <c r="B361" s="10" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C361" s="11" t="s">
         <v>25</v>
@@ -8208,13 +8193,13 @@
         <v>14</v>
       </c>
       <c r="B362" s="10" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C362" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D362" s="12" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E362" s="10" t="s">
         <v>27</v>
@@ -8225,13 +8210,13 @@
         <v>14</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C363" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E363" s="10" t="s">
         <v>27</v>
@@ -8242,7 +8227,7 @@
         <v>14</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C364" s="11" t="s">
         <v>25</v>
@@ -8259,13 +8244,13 @@
         <v>14</v>
       </c>
       <c r="B365" s="10" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C365" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E365" s="10" t="s">
         <v>27</v>
@@ -8276,13 +8261,13 @@
         <v>14</v>
       </c>
       <c r="B366" s="10" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C366" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E366" s="10" t="s">
         <v>27</v>
@@ -8293,13 +8278,13 @@
         <v>14</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C367" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E367" s="10" t="s">
         <v>27</v>
@@ -8310,13 +8295,13 @@
         <v>14</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C368" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E368" s="10" t="s">
         <v>27</v>
@@ -8327,13 +8312,13 @@
         <v>14</v>
       </c>
       <c r="B369" s="10" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C369" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E369" s="10" t="s">
         <v>27</v>
@@ -8344,7 +8329,7 @@
         <v>14</v>
       </c>
       <c r="B370" s="10" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C370" s="11" t="s">
         <v>25</v>
@@ -8361,13 +8346,13 @@
         <v>14</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C371" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D371" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E371" s="10" t="s">
         <v>27</v>
@@ -8378,13 +8363,13 @@
         <v>14</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C372" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D372" s="12" t="s">
-        <v>29</v>
+        <v>420</v>
       </c>
       <c r="E372" s="10" t="s">
         <v>27</v>
@@ -8395,13 +8380,13 @@
         <v>14</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C373" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D373" s="12" t="s">
-        <v>33</v>
+        <v>420</v>
       </c>
       <c r="E373" s="10" t="s">
         <v>27</v>
@@ -8412,13 +8397,13 @@
         <v>14</v>
       </c>
       <c r="B374" s="10" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C374" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D374" s="12" t="s">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="E374" s="10" t="s">
         <v>27</v>
@@ -8429,13 +8414,13 @@
         <v>14</v>
       </c>
       <c r="B375" s="10" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C375" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D375" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E375" s="10" t="s">
         <v>27</v>
@@ -8446,13 +8431,13 @@
         <v>14</v>
       </c>
       <c r="B376" s="10" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C376" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D376" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E376" s="10" t="s">
         <v>27</v>
@@ -8463,13 +8448,13 @@
         <v>14</v>
       </c>
       <c r="B377" s="10" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C377" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D377" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E377" s="10" t="s">
         <v>27</v>
@@ -8480,7 +8465,7 @@
         <v>14</v>
       </c>
       <c r="B378" s="10" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C378" s="11" t="s">
         <v>25</v>
@@ -8497,7 +8482,7 @@
         <v>14</v>
       </c>
       <c r="B379" s="10" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C379" s="11" t="s">
         <v>25</v>
@@ -8514,13 +8499,13 @@
         <v>14</v>
       </c>
       <c r="B380" s="10" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C380" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D380" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E380" s="10" t="s">
         <v>27</v>
@@ -8531,13 +8516,13 @@
         <v>14</v>
       </c>
       <c r="B381" s="10" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C381" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D381" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E381" s="10" t="s">
         <v>27</v>
@@ -8548,7 +8533,7 @@
         <v>14</v>
       </c>
       <c r="B382" s="10" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C382" s="11" t="s">
         <v>25</v>
@@ -8565,13 +8550,13 @@
         <v>14</v>
       </c>
       <c r="B383" s="10" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C383" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D383" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E383" s="10" t="s">
         <v>27</v>
@@ -8582,13 +8567,13 @@
         <v>14</v>
       </c>
       <c r="B384" s="10" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C384" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D384" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E384" s="10" t="s">
         <v>27</v>
@@ -8599,13 +8584,13 @@
         <v>14</v>
       </c>
       <c r="B385" s="10" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C385" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D385" s="12" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E385" s="10" t="s">
         <v>27</v>
@@ -8616,13 +8601,13 @@
         <v>14</v>
       </c>
       <c r="B386" s="10" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C386" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D386" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E386" s="10" t="s">
         <v>27</v>
@@ -8633,13 +8618,13 @@
         <v>14</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C387" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D387" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E387" s="10" t="s">
         <v>27</v>
@@ -8650,13 +8635,13 @@
         <v>14</v>
       </c>
       <c r="B388" s="10" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C388" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D388" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E388" s="10" t="s">
         <v>27</v>
@@ -8667,7 +8652,7 @@
         <v>14</v>
       </c>
       <c r="B389" s="10" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C389" s="11" t="s">
         <v>25</v>
@@ -8684,13 +8669,13 @@
         <v>14</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C390" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D390" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E390" s="10" t="s">
         <v>27</v>
@@ -8701,7 +8686,7 @@
         <v>14</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C391" s="11" t="s">
         <v>25</v>
@@ -8718,7 +8703,7 @@
         <v>14</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C392" s="11" t="s">
         <v>25</v>
@@ -8735,13 +8720,13 @@
         <v>14</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C393" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E393" s="10" t="s">
         <v>27</v>
@@ -8752,13 +8737,13 @@
         <v>14</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C394" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E394" s="10" t="s">
         <v>27</v>
@@ -8769,13 +8754,13 @@
         <v>14</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C395" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D395" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E395" s="10" t="s">
         <v>27</v>
@@ -8786,13 +8771,13 @@
         <v>14</v>
       </c>
       <c r="B396" s="10" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C396" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D396" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E396" s="10" t="s">
         <v>27</v>
@@ -8803,13 +8788,13 @@
         <v>14</v>
       </c>
       <c r="B397" s="10" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C397" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D397" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E397" s="10" t="s">
         <v>27</v>
@@ -8820,7 +8805,7 @@
         <v>14</v>
       </c>
       <c r="B398" s="10" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C398" s="11" t="s">
         <v>25</v>
@@ -8837,13 +8822,13 @@
         <v>14</v>
       </c>
       <c r="B399" s="10" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C399" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D399" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E399" s="10" t="s">
         <v>27</v>
@@ -8854,13 +8839,13 @@
         <v>14</v>
       </c>
       <c r="B400" s="10" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C400" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D400" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E400" s="10" t="s">
         <v>27</v>
@@ -8871,13 +8856,13 @@
         <v>14</v>
       </c>
       <c r="B401" s="10" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C401" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D401" s="12" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E401" s="10" t="s">
         <v>27</v>
@@ -8888,13 +8873,13 @@
         <v>14</v>
       </c>
       <c r="B402" s="10" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C402" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D402" s="12" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E402" s="10" t="s">
         <v>27</v>
@@ -8905,13 +8890,13 @@
         <v>14</v>
       </c>
       <c r="B403" s="10" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C403" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D403" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E403" s="10" t="s">
         <v>27</v>
@@ -8922,13 +8907,13 @@
         <v>14</v>
       </c>
       <c r="B404" s="10" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C404" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D404" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E404" s="10" t="s">
         <v>27</v>
@@ -8939,13 +8924,13 @@
         <v>14</v>
       </c>
       <c r="B405" s="10" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C405" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D405" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E405" s="10" t="s">
         <v>27</v>
@@ -8956,7 +8941,7 @@
         <v>14</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C406" s="11" t="s">
         <v>25</v>
@@ -8973,13 +8958,13 @@
         <v>14</v>
       </c>
       <c r="B407" s="10" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C407" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D407" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E407" s="10" t="s">
         <v>27</v>
@@ -8990,13 +8975,13 @@
         <v>14</v>
       </c>
       <c r="B408" s="10" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C408" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D408" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E408" s="10" t="s">
         <v>27</v>
@@ -9007,7 +8992,7 @@
         <v>14</v>
       </c>
       <c r="B409" s="10" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C409" s="11" t="s">
         <v>25</v>
@@ -9024,13 +9009,13 @@
         <v>14</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C410" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D410" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E410" s="10" t="s">
         <v>27</v>
@@ -9041,13 +9026,13 @@
         <v>14</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C411" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D411" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E411" s="10" t="s">
         <v>27</v>
@@ -9058,7 +9043,7 @@
         <v>14</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C412" s="11" t="s">
         <v>25</v>
@@ -9075,13 +9060,13 @@
         <v>14</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C413" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D413" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E413" s="10" t="s">
         <v>27</v>
@@ -9092,13 +9077,13 @@
         <v>14</v>
       </c>
       <c r="B414" s="10" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C414" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D414" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E414" s="10" t="s">
         <v>27</v>
@@ -9109,13 +9094,13 @@
         <v>14</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C415" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D415" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E415" s="10" t="s">
         <v>27</v>
@@ -9126,13 +9111,13 @@
         <v>14</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C416" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D416" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E416" s="10" t="s">
         <v>27</v>
@@ -9143,13 +9128,13 @@
         <v>14</v>
       </c>
       <c r="B417" s="10" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C417" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D417" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E417" s="10" t="s">
         <v>27</v>
@@ -9160,13 +9145,13 @@
         <v>14</v>
       </c>
       <c r="B418" s="10" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C418" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D418" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E418" s="10" t="s">
         <v>27</v>
@@ -9177,13 +9162,13 @@
         <v>14</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C419" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D419" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E419" s="10" t="s">
         <v>27</v>
@@ -9194,13 +9179,13 @@
         <v>14</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C420" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D420" s="12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E420" s="10" t="s">
         <v>27</v>
@@ -9211,7 +9196,7 @@
         <v>14</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C421" s="11" t="s">
         <v>25</v>

--- a/test-cases-reports/selinium-test/selenium_web_report.xlsx
+++ b/test-cases-reports/selinium-test/selenium_web_report.xlsx
@@ -62,7 +62,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>91.31s</t>
+    <t>90.58s</t>
   </si>
   <si>
     <t>Deployable Status</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>4.17s</t>
+    <t>4.32s</t>
   </si>
   <si>
     <t>-</t>
@@ -140,7 +140,7 @@
     <t>UI012: Onboarding page 3 title display</t>
   </si>
   <si>
-    <t>2.06s</t>
+    <t>2.11s</t>
   </si>
   <si>
     <t>UI013: Onboarding page 3 description text layout</t>
@@ -152,354 +152,354 @@
     <t>UI015: Login Screen background card shape</t>
   </si>
   <si>
-    <t>4.13s</t>
+    <t>4.12s</t>
   </si>
   <si>
     <t>UI016: Login screen email input container styling</t>
   </si>
   <si>
-    <t>4.16s</t>
-  </si>
-  <si>
     <t>UI017: Login screen password input container styling</t>
   </si>
   <si>
+    <t>UI018: Login button background design</t>
+  </si>
+  <si>
+    <t>UI019: Login header branding typography</t>
+  </si>
+  <si>
+    <t>UI020: Register screen fields typography and spacing</t>
+  </si>
+  <si>
+    <t>2.08s</t>
+  </si>
+  <si>
+    <t>UI021: Register button border radius</t>
+  </si>
+  <si>
+    <t>UI022: Register footer link styling</t>
+  </si>
+  <si>
+    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
+  </si>
+  <si>
+    <t>UI024: Dashboard header title formatting</t>
+  </si>
+  <si>
+    <t>UI025: Theme toggler button visual contrast</t>
+  </si>
+  <si>
+    <t>UI026: Light mode dashboard theme colors</t>
+  </si>
+  <si>
+    <t>UI027: Dark mode theme transition styles</t>
+  </si>
+  <si>
+    <t>UI028: Profile screen user avatar size layout</t>
+  </si>
+  <si>
+    <t>UI029: Test session card border margins</t>
+  </si>
+  <si>
+    <t>UI030: AI Feedback dialog spacing layout</t>
+  </si>
+  <si>
+    <t>UI031: Onboarding page dot animation transition duration checks</t>
+  </si>
+  <si>
+    <t>UI032: Onboarding skip button typography style properties matching</t>
+  </si>
+  <si>
+    <t>UI033: Splash logo container dimensions ratio verification</t>
+  </si>
+  <si>
+    <t>UI034: Splash loader indicator circular progress thickness details</t>
+  </si>
+  <si>
+    <t>UI035: Authentication textfield error messaging text font style alignment</t>
+  </si>
+  <si>
+    <t>UI036: Login submit button responsive hover opacity changes</t>
+  </si>
+  <si>
+    <t>UI037: Register page input padding offsets consistency checks</t>
+  </si>
+  <si>
     <t>0.02s</t>
   </si>
   <si>
-    <t>UI018: Login button background design</t>
-  </si>
-  <si>
-    <t>UI019: Login header branding typography</t>
-  </si>
-  <si>
-    <t>UI020: Register screen fields typography and spacing</t>
+    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
+  </si>
+  <si>
+    <t>UI039: Dark mode active body background color matching parameters</t>
+  </si>
+  <si>
+    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
+  </si>
+  <si>
+    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
+  </si>
+  <si>
+    <t>UI042: AI mock interview feedback container border lines styling</t>
+  </si>
+  <si>
+    <t>UI043: Chatbot user response chat bubble alignment properties</t>
+  </si>
+  <si>
+    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
+  </si>
+  <si>
+    <t>UI045: Profile user name typography scale weight and contrast check</t>
+  </si>
+  <si>
+    <t>UI046: Settings theme toggle switch active color verification parameters</t>
+  </si>
+  <si>
+    <t>UI047: Onboarding title layout alignment centered checking</t>
+  </si>
+  <si>
+    <t>UI048: Textfields active cursor focus color validation</t>
+  </si>
+  <si>
+    <t>UI049: Error messages warning badge layout constraints</t>
+  </si>
+  <si>
+    <t>UI050: App notification icon badges count scaling parameters</t>
+  </si>
+  <si>
+    <t>UI051: Profile card statistics counts label typography sizing</t>
+  </si>
+  <si>
+    <t>UI052: HR round option button icons visual alignment</t>
+  </si>
+  <si>
+    <t>UI053: Tech round option card layout spacing check</t>
+  </si>
+  <si>
+    <t>UI054: Aptitude test category cards layout alignment parameters</t>
+  </si>
+  <si>
+    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
+  </si>
+  <si>
+    <t>UI056: Alert dialog box overlay transparency index verification</t>
+  </si>
+  <si>
+    <t>UI057: Groq feedback score badge layout circular border alignment</t>
+  </si>
+  <si>
+    <t>UI058: Speech input icon active mic glow styling parameters</t>
+  </si>
+  <si>
+    <t>UI059: Dark theme input borders contrast rating validation</t>
+  </si>
+  <si>
+    <t>UI060: Onboarding next button icon placement side margins checking</t>
+  </si>
+  <si>
+    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
+  </si>
+  <si>
+    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
+  </si>
+  <si>
+    <t>UI063: Aptitude quiz progress bar line color status verification</t>
+  </si>
+  <si>
+    <t>UI064: Custom card elements scaling values on larger resolutions</t>
+  </si>
+  <si>
+    <t>UI065: Custom list dividers height thickness checking parameters</t>
+  </si>
+  <si>
+    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
+  </si>
+  <si>
+    <t>UI067: App header icon menu spacing and positioning specifications</t>
+  </si>
+  <si>
+    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
+  </si>
+  <si>
+    <t>UI069: Text input fields placeholder character font styling rules</t>
+  </si>
+  <si>
+    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
+  </si>
+  <si>
+    <t>UI071: Profile credentials edit inputs layout alignment values</t>
+  </si>
+  <si>
+    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
+  </si>
+  <si>
+    <t>UI073: Custom snackbar popup notifications container design styles</t>
+  </si>
+  <si>
+    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
+  </si>
+  <si>
+    <t>UI075: Webapp container shadow outline styling matching specifications</t>
+  </si>
+  <si>
+    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
+  </si>
+  <si>
+    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
+  </si>
+  <si>
+    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
+  </si>
+  <si>
+    <t>UI079: Chat suggestion chips outline border thickness details</t>
+  </si>
+  <si>
+    <t>UI080: Settings section headers font size transformations checking</t>
+  </si>
+  <si>
+    <t>UI081: Login forgot password link visual underline toggle checks</t>
+  </si>
+  <si>
+    <t>UI082: Register legal policies agreements text box layouts checks</t>
+  </si>
+  <si>
+    <t>UI083: Placement details document viewer layout padding verification</t>
+  </si>
+  <si>
+    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
+  </si>
+  <si>
+    <t>UI085: Custom dropdown selectors hover outline border width check</t>
+  </si>
+  <si>
+    <t>UI086: Dialog confirmations layouts check icon centering values</t>
+  </si>
+  <si>
+    <t>UI087: Chat input field icons click state opacity level updates</t>
+  </si>
+  <si>
+    <t>UI088: User avatar badge active placement online status display</t>
+  </si>
+  <si>
+    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
+  </si>
+  <si>
+    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
+  </si>
+  <si>
+    <t>UI091: Aptitude result summary page visual headers scaling check</t>
+  </si>
+  <si>
+    <t>UI092: AI feedback details accordion expand collapse height values</t>
+  </si>
+  <si>
+    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
+  </si>
+  <si>
+    <t>0.04s</t>
+  </si>
+  <si>
+    <t>UI094: Navigation bar labels selected font color parameter checks</t>
+  </si>
+  <si>
+    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
+  </si>
+  <si>
+    <t>UI096: Settings section divider margins layout alignment specifications</t>
+  </si>
+  <si>
+    <t>UI097: Placement company filters panel layout drawer design styles</t>
+  </si>
+  <si>
+    <t>UI098: Notification toggle buttons sliding animation duration check</t>
+  </si>
+  <si>
+    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
+  </si>
+  <si>
+    <t>UI100: Auth form title secondary text decoration attributes check</t>
+  </si>
+  <si>
+    <t>UI101: Chat message time badge indicator font weight properties</t>
+  </si>
+  <si>
+    <t>UI102: Profile page history entries list spacing parameters</t>
+  </si>
+  <si>
+    <t>UI103: Feedback text block alignment rules inside cards check</t>
+  </si>
+  <si>
+    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
+  </si>
+  <si>
+    <t>UI105: Interview review card layout horizontal borders constraint</t>
+  </si>
+  <si>
+    <t>UI106: Light mode inputs focus border shadow layout checks</t>
+  </si>
+  <si>
+    <t>UI107: Settings clear cache option text style parameters matching</t>
+  </si>
+  <si>
+    <t>UI108: Placement job card badges layout visual check rules</t>
+  </si>
+  <si>
+    <t>UI109: Speech processing overlay spinner styling visual verification</t>
+  </si>
+  <si>
+    <t>UI110: Test report dashboard header title color styling verification</t>
+  </si>
+  <si>
+    <t>FN001: Load app page successfully</t>
+  </si>
+  <si>
+    <t>4.09s</t>
+  </si>
+  <si>
+    <t>FN002: Click Next to access page 2</t>
   </si>
   <si>
     <t>2.09s</t>
   </si>
   <si>
-    <t>UI021: Register button border radius</t>
-  </si>
-  <si>
-    <t>0.03s</t>
-  </si>
-  <si>
-    <t>UI022: Register footer link styling</t>
-  </si>
-  <si>
-    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
-  </si>
-  <si>
-    <t>UI024: Dashboard header title formatting</t>
-  </si>
-  <si>
-    <t>UI025: Theme toggler button visual contrast</t>
-  </si>
-  <si>
-    <t>UI026: Light mode dashboard theme colors</t>
-  </si>
-  <si>
-    <t>UI027: Dark mode theme transition styles</t>
-  </si>
-  <si>
-    <t>UI028: Profile screen user avatar size layout</t>
-  </si>
-  <si>
-    <t>UI029: Test session card border margins</t>
-  </si>
-  <si>
-    <t>UI030: AI Feedback dialog spacing layout</t>
-  </si>
-  <si>
-    <t>UI031: Onboarding page dot animation transition duration checks</t>
-  </si>
-  <si>
-    <t>UI032: Onboarding skip button typography style properties matching</t>
-  </si>
-  <si>
-    <t>UI033: Splash logo container dimensions ratio verification</t>
-  </si>
-  <si>
-    <t>UI034: Splash loader indicator circular progress thickness details</t>
-  </si>
-  <si>
-    <t>UI035: Authentication textfield error messaging text font style alignment</t>
-  </si>
-  <si>
-    <t>UI036: Login submit button responsive hover opacity changes</t>
-  </si>
-  <si>
-    <t>UI037: Register page input padding offsets consistency checks</t>
-  </si>
-  <si>
-    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
-  </si>
-  <si>
-    <t>UI039: Dark mode active body background color matching parameters</t>
-  </si>
-  <si>
-    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
-  </si>
-  <si>
-    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
-  </si>
-  <si>
-    <t>UI042: AI mock interview feedback container border lines styling</t>
-  </si>
-  <si>
-    <t>UI043: Chatbot user response chat bubble alignment properties</t>
-  </si>
-  <si>
-    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
-  </si>
-  <si>
-    <t>UI045: Profile user name typography scale weight and contrast check</t>
-  </si>
-  <si>
-    <t>UI046: Settings theme toggle switch active color verification parameters</t>
-  </si>
-  <si>
-    <t>UI047: Onboarding title layout alignment centered checking</t>
-  </si>
-  <si>
-    <t>UI048: Textfields active cursor focus color validation</t>
-  </si>
-  <si>
-    <t>UI049: Error messages warning badge layout constraints</t>
-  </si>
-  <si>
-    <t>UI050: App notification icon badges count scaling parameters</t>
-  </si>
-  <si>
-    <t>UI051: Profile card statistics counts label typography sizing</t>
-  </si>
-  <si>
-    <t>UI052: HR round option button icons visual alignment</t>
-  </si>
-  <si>
-    <t>UI053: Tech round option card layout spacing check</t>
-  </si>
-  <si>
-    <t>UI054: Aptitude test category cards layout alignment parameters</t>
-  </si>
-  <si>
-    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
-  </si>
-  <si>
-    <t>UI056: Alert dialog box overlay transparency index verification</t>
-  </si>
-  <si>
-    <t>UI057: Groq feedback score badge layout circular border alignment</t>
-  </si>
-  <si>
-    <t>UI058: Speech input icon active mic glow styling parameters</t>
-  </si>
-  <si>
-    <t>UI059: Dark theme input borders contrast rating validation</t>
-  </si>
-  <si>
-    <t>UI060: Onboarding next button icon placement side margins checking</t>
-  </si>
-  <si>
-    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
-  </si>
-  <si>
-    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
-  </si>
-  <si>
-    <t>UI063: Aptitude quiz progress bar line color status verification</t>
-  </si>
-  <si>
-    <t>UI064: Custom card elements scaling values on larger resolutions</t>
-  </si>
-  <si>
-    <t>UI065: Custom list dividers height thickness checking parameters</t>
-  </si>
-  <si>
-    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
-  </si>
-  <si>
-    <t>UI067: App header icon menu spacing and positioning specifications</t>
-  </si>
-  <si>
-    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
-  </si>
-  <si>
-    <t>UI069: Text input fields placeholder character font styling rules</t>
-  </si>
-  <si>
-    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
-  </si>
-  <si>
-    <t>UI071: Profile credentials edit inputs layout alignment values</t>
-  </si>
-  <si>
-    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
-  </si>
-  <si>
-    <t>UI073: Custom snackbar popup notifications container design styles</t>
-  </si>
-  <si>
-    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
-  </si>
-  <si>
-    <t>UI075: Webapp container shadow outline styling matching specifications</t>
-  </si>
-  <si>
-    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
-  </si>
-  <si>
-    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
-  </si>
-  <si>
-    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
-  </si>
-  <si>
-    <t>UI079: Chat suggestion chips outline border thickness details</t>
-  </si>
-  <si>
-    <t>UI080: Settings section headers font size transformations checking</t>
-  </si>
-  <si>
-    <t>UI081: Login forgot password link visual underline toggle checks</t>
-  </si>
-  <si>
-    <t>UI082: Register legal policies agreements text box layouts checks</t>
-  </si>
-  <si>
-    <t>UI083: Placement details document viewer layout padding verification</t>
-  </si>
-  <si>
-    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
-  </si>
-  <si>
-    <t>UI085: Custom dropdown selectors hover outline border width check</t>
-  </si>
-  <si>
-    <t>UI086: Dialog confirmations layouts check icon centering values</t>
-  </si>
-  <si>
-    <t>UI087: Chat input field icons click state opacity level updates</t>
-  </si>
-  <si>
-    <t>UI088: User avatar badge active placement online status display</t>
-  </si>
-  <si>
-    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
-  </si>
-  <si>
-    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
-  </si>
-  <si>
-    <t>UI091: Aptitude result summary page visual headers scaling check</t>
-  </si>
-  <si>
-    <t>UI092: AI feedback details accordion expand collapse height values</t>
-  </si>
-  <si>
-    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
-  </si>
-  <si>
-    <t>UI094: Navigation bar labels selected font color parameter checks</t>
-  </si>
-  <si>
-    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
-  </si>
-  <si>
-    <t>UI096: Settings section divider margins layout alignment specifications</t>
-  </si>
-  <si>
-    <t>UI097: Placement company filters panel layout drawer design styles</t>
-  </si>
-  <si>
-    <t>UI098: Notification toggle buttons sliding animation duration check</t>
-  </si>
-  <si>
-    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
-  </si>
-  <si>
-    <t>UI100: Auth form title secondary text decoration attributes check</t>
-  </si>
-  <si>
-    <t>UI101: Chat message time badge indicator font weight properties</t>
-  </si>
-  <si>
-    <t>UI102: Profile page history entries list spacing parameters</t>
-  </si>
-  <si>
-    <t>UI103: Feedback text block alignment rules inside cards check</t>
-  </si>
-  <si>
-    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
-  </si>
-  <si>
-    <t>0.04s</t>
-  </si>
-  <si>
-    <t>UI105: Interview review card layout horizontal borders constraint</t>
-  </si>
-  <si>
-    <t>UI106: Light mode inputs focus border shadow layout checks</t>
-  </si>
-  <si>
-    <t>UI107: Settings clear cache option text style parameters matching</t>
-  </si>
-  <si>
-    <t>UI108: Placement job card badges layout visual check rules</t>
-  </si>
-  <si>
-    <t>UI109: Speech processing overlay spinner styling visual verification</t>
-  </si>
-  <si>
-    <t>UI110: Test report dashboard header title color styling verification</t>
-  </si>
-  <si>
-    <t>FN001: Load app page successfully</t>
-  </si>
-  <si>
-    <t>FN002: Click Next to access page 2</t>
+    <t>FN003: Click Next to access page 3</t>
+  </si>
+  <si>
+    <t>FN004: Skip button bypasses onboarding screen</t>
+  </si>
+  <si>
+    <t>6.17s</t>
+  </si>
+  <si>
+    <t>FN005: Complete onboarding and transition to authentication page</t>
+  </si>
+  <si>
+    <t>2.13s</t>
+  </si>
+  <si>
+    <t>FN006: Select register navigation path</t>
+  </si>
+  <si>
+    <t>FN007: Register a new account with valid unique details</t>
+  </si>
+  <si>
+    <t>FN008: Submit register account credentials to Firestore</t>
   </si>
   <si>
     <t>2.07s</t>
   </si>
   <si>
-    <t>FN003: Click Next to access page 3</t>
-  </si>
-  <si>
-    <t>2.08s</t>
-  </si>
-  <si>
-    <t>FN004: Skip button bypasses onboarding screen</t>
-  </si>
-  <si>
-    <t>6.24s</t>
-  </si>
-  <si>
-    <t>FN005: Complete onboarding and transition to authentication page</t>
-  </si>
-  <si>
-    <t>FN006: Select register navigation path</t>
-  </si>
-  <si>
-    <t>2.11s</t>
-  </si>
-  <si>
-    <t>FN007: Register a new account with valid unique details</t>
-  </si>
-  <si>
-    <t>FN008: Submit register account credentials to Firestore</t>
-  </si>
-  <si>
     <t>FN009: Verify user main dashboard is successfully loaded</t>
   </si>
   <si>
-    <t>0.54s</t>
+    <t>0.53s</t>
   </si>
   <si>
     <t>FN010: Navigate to Aptitude &amp; Technical Tests tab</t>
   </si>
   <si>
+    <t>2.12s</t>
+  </si>
+  <si>
     <t>FN011: Render Aptitude list categories</t>
   </si>
   <si>
@@ -530,37 +530,40 @@
     <t>FN019: Input answer to the generated mock question</t>
   </si>
   <si>
+    <t>4.19s</t>
+  </si>
+  <si>
+    <t>FN020: Submit answer to AI evaluation engine</t>
+  </si>
+  <si>
+    <t>FN021: Retrieve feedback score from Groq API response</t>
+  </si>
+  <si>
+    <t>2.01s</t>
+  </si>
+  <si>
+    <t>FN022: Display evaluation advice layout</t>
+  </si>
+  <si>
+    <t>FN023: Exit active interview page using close option</t>
+  </si>
+  <si>
+    <t>FN024: Exit dialog confirmation redirects back to dashboard</t>
+  </si>
+  <si>
+    <t>FN025: Navigate to Chatbot assistant tab</t>
+  </si>
+  <si>
+    <t>FN026: Enter custom text message in chat query input</t>
+  </si>
+  <si>
     <t>4.18s</t>
   </si>
   <si>
-    <t>FN020: Submit answer to AI evaluation engine</t>
-  </si>
-  <si>
-    <t>FN021: Retrieve feedback score from Groq API response</t>
-  </si>
-  <si>
-    <t>2.03s</t>
-  </si>
-  <si>
-    <t>FN022: Display evaluation advice layout</t>
-  </si>
-  <si>
-    <t>FN023: Exit active interview page using close option</t>
-  </si>
-  <si>
-    <t>FN024: Exit dialog confirmation redirects back to dashboard</t>
-  </si>
-  <si>
-    <t>FN025: Navigate to Chatbot assistant tab</t>
-  </si>
-  <si>
-    <t>FN026: Enter custom text message in chat query input</t>
-  </si>
-  <si>
     <t>FN027: Receive chatbot answer correctly</t>
   </si>
   <si>
-    <t>1.01s</t>
+    <t>1.04s</t>
   </si>
   <si>
     <t>FN028: Access user settings &amp; profile tab</t>
@@ -1121,39 +1124,39 @@
     <t>VL002: Register user empty last name triggers validation</t>
   </si>
   <si>
+    <t>VL003: Register user blank email validation toast</t>
+  </si>
+  <si>
+    <t>VL004: Register user invalid email format display</t>
+  </si>
+  <si>
+    <t>VL005: Register user weak password complexity warning display</t>
+  </si>
+  <si>
+    <t>VL006: Authenticate with invalid email formatting</t>
+  </si>
+  <si>
+    <t>VL007: Authenticate with wrong password key error toast</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>VL008: Submit empty text answer to HR Interviewer returns validation message</t>
+  </si>
+  <si>
+    <t>VL009: Check question counts upper limit constraint</t>
+  </si>
+  <si>
+    <t>VL010: Check question counts lower limit constraint</t>
+  </si>
+  <si>
+    <t>VL011: Submit aptitude test with no questions answered displays alert dialog</t>
+  </si>
+  <si>
     <t>0.10s</t>
   </si>
   <si>
-    <t>VL003: Register user blank email validation toast</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>VL004: Register user invalid email format display</t>
-  </si>
-  <si>
-    <t>VL005: Register user weak password complexity warning display</t>
-  </si>
-  <si>
-    <t>VL006: Authenticate with invalid email formatting</t>
-  </si>
-  <si>
-    <t>VL007: Authenticate with wrong password key error toast</t>
-  </si>
-  <si>
-    <t>VL008: Submit empty text answer to HR Interviewer returns validation message</t>
-  </si>
-  <si>
-    <t>VL009: Check question counts upper limit constraint</t>
-  </si>
-  <si>
-    <t>VL010: Check question counts lower limit constraint</t>
-  </si>
-  <si>
-    <t>VL011: Submit aptitude test with no questions answered displays alert dialog</t>
-  </si>
-  <si>
     <t>VL012: Save offline test session log validation check</t>
   </si>
   <si>
@@ -1272,9 +1275,6 @@
   </si>
   <si>
     <t>VL051: Auth token formats validation checks matches regex syntax rules</t>
-  </si>
-  <si>
-    <t>0.05s</t>
   </si>
   <si>
     <t>VL052: Custom dashboard stats metrics numerical constraints boundaries</t>
@@ -2232,7 +2232,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>27</v>
@@ -2334,7 +2334,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>27</v>
@@ -2345,13 +2345,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>27</v>
@@ -2362,13 +2362,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>27</v>
@@ -2379,7 +2379,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>25</v>
@@ -2396,13 +2396,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>27</v>
@@ -2413,13 +2413,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>27</v>
@@ -2430,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>25</v>
@@ -2447,7 +2447,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>25</v>
@@ -2464,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>25</v>
@@ -2481,7 +2481,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>25</v>
@@ -2498,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>25</v>
@@ -2515,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>25</v>
@@ -2532,7 +2532,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>25</v>
@@ -2549,7 +2549,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>25</v>
@@ -2566,7 +2566,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>25</v>
@@ -2583,7 +2583,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>25</v>
@@ -2600,7 +2600,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>25</v>
@@ -2617,7 +2617,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>25</v>
@@ -2634,7 +2634,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>25</v>
@@ -2651,7 +2651,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>25</v>
@@ -2668,13 +2668,13 @@
         <v>7</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>27</v>
@@ -2685,13 +2685,13 @@
         <v>7</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>27</v>
@@ -2702,7 +2702,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>25</v>
@@ -2719,7 +2719,7 @@
         <v>7</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>25</v>
@@ -2736,7 +2736,7 @@
         <v>7</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>25</v>
@@ -2753,7 +2753,7 @@
         <v>7</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>25</v>
@@ -2770,7 +2770,7 @@
         <v>7</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>25</v>
@@ -2787,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>25</v>
@@ -2804,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>25</v>
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>25</v>
@@ -2838,7 +2838,7 @@
         <v>7</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>25</v>
@@ -2855,7 +2855,7 @@
         <v>7</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>25</v>
@@ -2872,7 +2872,7 @@
         <v>7</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>25</v>
@@ -2889,7 +2889,7 @@
         <v>7</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>25</v>
@@ -2906,7 +2906,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>25</v>
@@ -2923,7 +2923,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>25</v>
@@ -2940,7 +2940,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>25</v>
@@ -2957,7 +2957,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>25</v>
@@ -2974,7 +2974,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>25</v>
@@ -2991,7 +2991,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>25</v>
@@ -3008,7 +3008,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>25</v>
@@ -3025,7 +3025,7 @@
         <v>7</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>25</v>
@@ -3042,7 +3042,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>25</v>
@@ -3059,7 +3059,7 @@
         <v>7</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>25</v>
@@ -3076,7 +3076,7 @@
         <v>7</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>25</v>
@@ -3093,7 +3093,7 @@
         <v>7</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>25</v>
@@ -3110,7 +3110,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>25</v>
@@ -3127,7 +3127,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>25</v>
@@ -3144,7 +3144,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>25</v>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>25</v>
@@ -3178,7 +3178,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>25</v>
@@ -3195,7 +3195,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>25</v>
@@ -3212,7 +3212,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>25</v>
@@ -3229,7 +3229,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>25</v>
@@ -3246,7 +3246,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>25</v>
@@ -3263,7 +3263,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>25</v>
@@ -3280,7 +3280,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>25</v>
@@ -3297,7 +3297,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>25</v>
@@ -3314,7 +3314,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>25</v>
@@ -3331,7 +3331,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>25</v>
@@ -3348,7 +3348,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>25</v>
@@ -3365,7 +3365,7 @@
         <v>7</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>25</v>
@@ -3382,7 +3382,7 @@
         <v>7</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>25</v>
@@ -3399,7 +3399,7 @@
         <v>7</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>25</v>
@@ -3416,7 +3416,7 @@
         <v>7</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>25</v>
@@ -3433,7 +3433,7 @@
         <v>7</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>25</v>
@@ -3450,7 +3450,7 @@
         <v>7</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C83" s="11" t="s">
         <v>25</v>
@@ -3467,7 +3467,7 @@
         <v>7</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>25</v>
@@ -3484,7 +3484,7 @@
         <v>7</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>25</v>
@@ -3501,7 +3501,7 @@
         <v>7</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>25</v>
@@ -3518,7 +3518,7 @@
         <v>7</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>25</v>
@@ -3535,7 +3535,7 @@
         <v>7</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>25</v>
@@ -3552,7 +3552,7 @@
         <v>7</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>25</v>
@@ -3569,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>25</v>
@@ -3586,7 +3586,7 @@
         <v>7</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>25</v>
@@ -3603,7 +3603,7 @@
         <v>7</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>25</v>
@@ -3620,7 +3620,7 @@
         <v>7</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>25</v>
@@ -3637,13 +3637,13 @@
         <v>7</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>27</v>
@@ -3654,7 +3654,7 @@
         <v>7</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>25</v>
@@ -3671,7 +3671,7 @@
         <v>7</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>25</v>
@@ -3688,7 +3688,7 @@
         <v>7</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>25</v>
@@ -3705,7 +3705,7 @@
         <v>7</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>25</v>
@@ -3722,7 +3722,7 @@
         <v>7</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>25</v>
@@ -3739,13 +3739,13 @@
         <v>7</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>27</v>
@@ -3756,7 +3756,7 @@
         <v>7</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>25</v>
@@ -3773,7 +3773,7 @@
         <v>7</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>25</v>
@@ -3790,13 +3790,13 @@
         <v>7</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>27</v>
@@ -3807,13 +3807,13 @@
         <v>7</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>27</v>
@@ -3824,13 +3824,13 @@
         <v>7</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>27</v>
@@ -3841,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>25</v>
@@ -3858,13 +3858,13 @@
         <v>7</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>27</v>
@@ -3875,7 +3875,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>25</v>
@@ -3892,7 +3892,7 @@
         <v>7</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>25</v>
@@ -3909,7 +3909,7 @@
         <v>7</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>25</v>
@@ -3926,7 +3926,7 @@
         <v>7</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>25</v>
@@ -3943,13 +3943,13 @@
         <v>10</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>27</v>
@@ -3960,13 +3960,13 @@
         <v>10</v>
       </c>
       <c r="B113" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D113" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D113" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>27</v>
@@ -3977,13 +3977,13 @@
         <v>10</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>27</v>
@@ -3994,13 +3994,13 @@
         <v>10</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C115" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>27</v>
@@ -4011,13 +4011,13 @@
         <v>10</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>27</v>
@@ -4028,13 +4028,13 @@
         <v>10</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C117" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>27</v>
@@ -4045,13 +4045,13 @@
         <v>10</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>27</v>
@@ -4062,13 +4062,13 @@
         <v>10</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C119" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>27</v>
@@ -4079,13 +4079,13 @@
         <v>10</v>
       </c>
       <c r="B120" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>160</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>27</v>
@@ -4096,13 +4096,13 @@
         <v>10</v>
       </c>
       <c r="B121" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D121" s="12" t="s">
         <v>161</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>27</v>
@@ -4136,7 +4136,7 @@
         <v>25</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>27</v>
@@ -4153,7 +4153,7 @@
         <v>25</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>27</v>
@@ -4170,7 +4170,7 @@
         <v>25</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>27</v>
@@ -4187,7 +4187,7 @@
         <v>25</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>27</v>
@@ -4204,7 +4204,7 @@
         <v>25</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>27</v>
@@ -4238,7 +4238,7 @@
         <v>25</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>27</v>
@@ -4272,7 +4272,7 @@
         <v>25</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>27</v>
@@ -4306,7 +4306,7 @@
         <v>25</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>27</v>
@@ -4323,7 +4323,7 @@
         <v>25</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>27</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>27</v>
@@ -4357,7 +4357,7 @@
         <v>25</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>27</v>
@@ -4374,7 +4374,7 @@
         <v>25</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>27</v>
@@ -4385,13 +4385,13 @@
         <v>10</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>27</v>
@@ -4402,13 +4402,13 @@
         <v>10</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C139" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>27</v>
@@ -4419,13 +4419,13 @@
         <v>10</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>27</v>
@@ -4436,13 +4436,13 @@
         <v>10</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>27</v>
@@ -4453,7 +4453,7 @@
         <v>10</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>25</v>
@@ -4470,7 +4470,7 @@
         <v>10</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>25</v>
@@ -4487,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>25</v>
@@ -4504,7 +4504,7 @@
         <v>10</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>25</v>
@@ -4521,7 +4521,7 @@
         <v>10</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>25</v>
@@ -4538,7 +4538,7 @@
         <v>10</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>25</v>
@@ -4555,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>25</v>
@@ -4572,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>25</v>
@@ -4589,13 +4589,13 @@
         <v>10</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>27</v>
@@ -4606,7 +4606,7 @@
         <v>10</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>25</v>
@@ -4623,7 +4623,7 @@
         <v>10</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>25</v>
@@ -4640,7 +4640,7 @@
         <v>10</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>25</v>
@@ -4657,7 +4657,7 @@
         <v>10</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>25</v>
@@ -4674,7 +4674,7 @@
         <v>10</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C155" s="11" t="s">
         <v>25</v>
@@ -4691,7 +4691,7 @@
         <v>10</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C156" s="11" t="s">
         <v>25</v>
@@ -4708,7 +4708,7 @@
         <v>10</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>25</v>
@@ -4725,7 +4725,7 @@
         <v>10</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>25</v>
@@ -4742,7 +4742,7 @@
         <v>10</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C159" s="11" t="s">
         <v>25</v>
@@ -4759,13 +4759,13 @@
         <v>10</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E160" s="10" t="s">
         <v>27</v>
@@ -4776,7 +4776,7 @@
         <v>10</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>25</v>
@@ -4793,7 +4793,7 @@
         <v>10</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>25</v>
@@ -4810,7 +4810,7 @@
         <v>10</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>25</v>
@@ -4827,7 +4827,7 @@
         <v>10</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>25</v>
@@ -4844,7 +4844,7 @@
         <v>10</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>25</v>
@@ -4861,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>25</v>
@@ -4878,7 +4878,7 @@
         <v>10</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>25</v>
@@ -4895,7 +4895,7 @@
         <v>10</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>25</v>
@@ -4912,7 +4912,7 @@
         <v>10</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>25</v>
@@ -4929,7 +4929,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>25</v>
@@ -4946,7 +4946,7 @@
         <v>10</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>25</v>
@@ -4963,7 +4963,7 @@
         <v>10</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>25</v>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>25</v>
@@ -4997,7 +4997,7 @@
         <v>10</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>25</v>
@@ -5014,7 +5014,7 @@
         <v>10</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>25</v>
@@ -5031,7 +5031,7 @@
         <v>10</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>25</v>
@@ -5048,7 +5048,7 @@
         <v>10</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>25</v>
@@ -5065,7 +5065,7 @@
         <v>10</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>25</v>
@@ -5082,7 +5082,7 @@
         <v>10</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>25</v>
@@ -5099,7 +5099,7 @@
         <v>10</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>25</v>
@@ -5116,7 +5116,7 @@
         <v>10</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>25</v>
@@ -5133,13 +5133,13 @@
         <v>10</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E182" s="10" t="s">
         <v>27</v>
@@ -5150,7 +5150,7 @@
         <v>10</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C183" s="11" t="s">
         <v>25</v>
@@ -5167,7 +5167,7 @@
         <v>10</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>25</v>
@@ -5184,7 +5184,7 @@
         <v>10</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>25</v>
@@ -5201,7 +5201,7 @@
         <v>10</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>25</v>
@@ -5218,7 +5218,7 @@
         <v>10</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>25</v>
@@ -5235,7 +5235,7 @@
         <v>10</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>25</v>
@@ -5252,7 +5252,7 @@
         <v>10</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>25</v>
@@ -5269,7 +5269,7 @@
         <v>10</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>25</v>
@@ -5286,7 +5286,7 @@
         <v>10</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>25</v>
@@ -5303,7 +5303,7 @@
         <v>10</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>25</v>
@@ -5320,7 +5320,7 @@
         <v>10</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>25</v>
@@ -5337,7 +5337,7 @@
         <v>10</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>25</v>
@@ -5354,7 +5354,7 @@
         <v>10</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>25</v>
@@ -5371,7 +5371,7 @@
         <v>10</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>25</v>
@@ -5388,7 +5388,7 @@
         <v>10</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>25</v>
@@ -5405,7 +5405,7 @@
         <v>10</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>25</v>
@@ -5422,7 +5422,7 @@
         <v>10</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>25</v>
@@ -5439,7 +5439,7 @@
         <v>10</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>25</v>
@@ -5456,7 +5456,7 @@
         <v>10</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>25</v>
@@ -5473,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>25</v>
@@ -5490,7 +5490,7 @@
         <v>10</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>25</v>
@@ -5507,7 +5507,7 @@
         <v>10</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>25</v>
@@ -5524,7 +5524,7 @@
         <v>10</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>25</v>
@@ -5541,7 +5541,7 @@
         <v>10</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>25</v>
@@ -5558,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>25</v>
@@ -5575,7 +5575,7 @@
         <v>10</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>25</v>
@@ -5592,7 +5592,7 @@
         <v>10</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>25</v>
@@ -5609,7 +5609,7 @@
         <v>10</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>25</v>
@@ -5626,7 +5626,7 @@
         <v>10</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C211" s="11" t="s">
         <v>25</v>
@@ -5643,7 +5643,7 @@
         <v>10</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>25</v>
@@ -5660,7 +5660,7 @@
         <v>10</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>25</v>
@@ -5677,7 +5677,7 @@
         <v>10</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C214" s="11" t="s">
         <v>25</v>
@@ -5694,7 +5694,7 @@
         <v>10</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C215" s="11" t="s">
         <v>25</v>
@@ -5711,7 +5711,7 @@
         <v>10</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>25</v>
@@ -5728,13 +5728,13 @@
         <v>10</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C217" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D217" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>27</v>
@@ -5745,7 +5745,7 @@
         <v>10</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>25</v>
@@ -5762,7 +5762,7 @@
         <v>10</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>25</v>
@@ -5779,7 +5779,7 @@
         <v>10</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C220" s="11" t="s">
         <v>25</v>
@@ -5796,7 +5796,7 @@
         <v>10</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C221" s="11" t="s">
         <v>25</v>
@@ -5813,7 +5813,7 @@
         <v>12</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C222" s="11" t="s">
         <v>25</v>
@@ -5830,7 +5830,7 @@
         <v>12</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C223" s="11" t="s">
         <v>25</v>
@@ -5847,7 +5847,7 @@
         <v>12</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C224" s="11" t="s">
         <v>25</v>
@@ -5864,7 +5864,7 @@
         <v>12</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C225" s="11" t="s">
         <v>25</v>
@@ -5881,7 +5881,7 @@
         <v>12</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C226" s="11" t="s">
         <v>25</v>
@@ -5898,7 +5898,7 @@
         <v>12</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C227" s="11" t="s">
         <v>25</v>
@@ -5915,7 +5915,7 @@
         <v>12</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C228" s="11" t="s">
         <v>25</v>
@@ -5932,7 +5932,7 @@
         <v>12</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C229" s="11" t="s">
         <v>25</v>
@@ -5949,7 +5949,7 @@
         <v>12</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C230" s="11" t="s">
         <v>25</v>
@@ -5966,7 +5966,7 @@
         <v>12</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C231" s="11" t="s">
         <v>25</v>
@@ -5983,7 +5983,7 @@
         <v>12</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C232" s="11" t="s">
         <v>25</v>
@@ -6000,7 +6000,7 @@
         <v>12</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C233" s="11" t="s">
         <v>25</v>
@@ -6017,7 +6017,7 @@
         <v>12</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C234" s="11" t="s">
         <v>25</v>
@@ -6034,7 +6034,7 @@
         <v>12</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C235" s="11" t="s">
         <v>25</v>
@@ -6051,7 +6051,7 @@
         <v>12</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C236" s="11" t="s">
         <v>25</v>
@@ -6068,7 +6068,7 @@
         <v>12</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C237" s="11" t="s">
         <v>25</v>
@@ -6085,7 +6085,7 @@
         <v>12</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C238" s="11" t="s">
         <v>25</v>
@@ -6102,7 +6102,7 @@
         <v>12</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C239" s="11" t="s">
         <v>25</v>
@@ -6119,7 +6119,7 @@
         <v>12</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C240" s="11" t="s">
         <v>25</v>
@@ -6136,7 +6136,7 @@
         <v>12</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C241" s="11" t="s">
         <v>25</v>
@@ -6153,7 +6153,7 @@
         <v>12</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C242" s="11" t="s">
         <v>25</v>
@@ -6170,7 +6170,7 @@
         <v>12</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C243" s="11" t="s">
         <v>25</v>
@@ -6187,7 +6187,7 @@
         <v>12</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C244" s="11" t="s">
         <v>25</v>
@@ -6204,7 +6204,7 @@
         <v>12</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C245" s="11" t="s">
         <v>25</v>
@@ -6221,7 +6221,7 @@
         <v>12</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C246" s="11" t="s">
         <v>25</v>
@@ -6238,7 +6238,7 @@
         <v>12</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C247" s="11" t="s">
         <v>25</v>
@@ -6255,7 +6255,7 @@
         <v>12</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C248" s="11" t="s">
         <v>25</v>
@@ -6272,7 +6272,7 @@
         <v>12</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C249" s="11" t="s">
         <v>25</v>
@@ -6289,7 +6289,7 @@
         <v>12</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C250" s="11" t="s">
         <v>25</v>
@@ -6306,7 +6306,7 @@
         <v>12</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C251" s="11" t="s">
         <v>25</v>
@@ -6323,7 +6323,7 @@
         <v>12</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C252" s="11" t="s">
         <v>25</v>
@@ -6340,7 +6340,7 @@
         <v>12</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C253" s="11" t="s">
         <v>25</v>
@@ -6357,7 +6357,7 @@
         <v>12</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C254" s="11" t="s">
         <v>25</v>
@@ -6374,7 +6374,7 @@
         <v>12</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C255" s="11" t="s">
         <v>25</v>
@@ -6391,7 +6391,7 @@
         <v>12</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>25</v>
@@ -6408,7 +6408,7 @@
         <v>12</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>25</v>
@@ -6425,7 +6425,7 @@
         <v>12</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>25</v>
@@ -6442,7 +6442,7 @@
         <v>12</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>25</v>
@@ -6459,7 +6459,7 @@
         <v>12</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>25</v>
@@ -6476,7 +6476,7 @@
         <v>12</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>25</v>
@@ -6493,7 +6493,7 @@
         <v>12</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>25</v>
@@ -6510,7 +6510,7 @@
         <v>12</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C263" s="11" t="s">
         <v>25</v>
@@ -6527,7 +6527,7 @@
         <v>12</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C264" s="11" t="s">
         <v>25</v>
@@ -6544,7 +6544,7 @@
         <v>12</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>25</v>
@@ -6561,7 +6561,7 @@
         <v>12</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C266" s="11" t="s">
         <v>25</v>
@@ -6578,7 +6578,7 @@
         <v>12</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C267" s="11" t="s">
         <v>25</v>
@@ -6595,7 +6595,7 @@
         <v>12</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C268" s="11" t="s">
         <v>25</v>
@@ -6612,7 +6612,7 @@
         <v>12</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C269" s="11" t="s">
         <v>25</v>
@@ -6629,7 +6629,7 @@
         <v>12</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C270" s="11" t="s">
         <v>25</v>
@@ -6646,7 +6646,7 @@
         <v>12</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C271" s="11" t="s">
         <v>25</v>
@@ -6663,7 +6663,7 @@
         <v>12</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C272" s="11" t="s">
         <v>25</v>
@@ -6680,7 +6680,7 @@
         <v>12</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C273" s="11" t="s">
         <v>25</v>
@@ -6697,7 +6697,7 @@
         <v>12</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C274" s="11" t="s">
         <v>25</v>
@@ -6714,7 +6714,7 @@
         <v>12</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C275" s="11" t="s">
         <v>25</v>
@@ -6731,7 +6731,7 @@
         <v>12</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C276" s="11" t="s">
         <v>25</v>
@@ -6748,7 +6748,7 @@
         <v>12</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C277" s="11" t="s">
         <v>25</v>
@@ -6765,7 +6765,7 @@
         <v>12</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C278" s="11" t="s">
         <v>25</v>
@@ -6782,7 +6782,7 @@
         <v>12</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C279" s="11" t="s">
         <v>25</v>
@@ -6799,7 +6799,7 @@
         <v>12</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C280" s="11" t="s">
         <v>25</v>
@@ -6816,7 +6816,7 @@
         <v>12</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C281" s="11" t="s">
         <v>25</v>
@@ -6833,7 +6833,7 @@
         <v>12</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C282" s="11" t="s">
         <v>25</v>
@@ -6850,7 +6850,7 @@
         <v>12</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C283" s="11" t="s">
         <v>25</v>
@@ -6867,7 +6867,7 @@
         <v>12</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C284" s="11" t="s">
         <v>25</v>
@@ -6884,7 +6884,7 @@
         <v>12</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C285" s="11" t="s">
         <v>25</v>
@@ -6901,7 +6901,7 @@
         <v>12</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C286" s="11" t="s">
         <v>25</v>
@@ -6918,7 +6918,7 @@
         <v>12</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C287" s="11" t="s">
         <v>25</v>
@@ -6935,7 +6935,7 @@
         <v>12</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C288" s="11" t="s">
         <v>25</v>
@@ -6952,7 +6952,7 @@
         <v>12</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C289" s="11" t="s">
         <v>25</v>
@@ -6969,7 +6969,7 @@
         <v>12</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C290" s="11" t="s">
         <v>25</v>
@@ -6986,7 +6986,7 @@
         <v>12</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C291" s="11" t="s">
         <v>25</v>
@@ -7003,7 +7003,7 @@
         <v>12</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C292" s="11" t="s">
         <v>25</v>
@@ -7020,7 +7020,7 @@
         <v>12</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C293" s="11" t="s">
         <v>25</v>
@@ -7037,7 +7037,7 @@
         <v>12</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C294" s="11" t="s">
         <v>25</v>
@@ -7054,7 +7054,7 @@
         <v>12</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C295" s="11" t="s">
         <v>25</v>
@@ -7071,7 +7071,7 @@
         <v>12</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C296" s="11" t="s">
         <v>25</v>
@@ -7088,7 +7088,7 @@
         <v>12</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C297" s="11" t="s">
         <v>25</v>
@@ -7105,7 +7105,7 @@
         <v>12</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C298" s="11" t="s">
         <v>25</v>
@@ -7122,7 +7122,7 @@
         <v>12</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C299" s="11" t="s">
         <v>25</v>
@@ -7139,7 +7139,7 @@
         <v>12</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C300" s="11" t="s">
         <v>25</v>
@@ -7156,7 +7156,7 @@
         <v>12</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C301" s="11" t="s">
         <v>25</v>
@@ -7173,7 +7173,7 @@
         <v>12</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C302" s="11" t="s">
         <v>25</v>
@@ -7190,7 +7190,7 @@
         <v>12</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C303" s="11" t="s">
         <v>25</v>
@@ -7207,7 +7207,7 @@
         <v>12</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C304" s="11" t="s">
         <v>25</v>
@@ -7224,7 +7224,7 @@
         <v>12</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C305" s="11" t="s">
         <v>25</v>
@@ -7241,7 +7241,7 @@
         <v>12</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C306" s="11" t="s">
         <v>25</v>
@@ -7258,7 +7258,7 @@
         <v>12</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C307" s="11" t="s">
         <v>25</v>
@@ -7275,7 +7275,7 @@
         <v>12</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C308" s="11" t="s">
         <v>25</v>
@@ -7292,7 +7292,7 @@
         <v>12</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C309" s="11" t="s">
         <v>25</v>
@@ -7309,7 +7309,7 @@
         <v>12</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C310" s="11" t="s">
         <v>25</v>
@@ -7326,7 +7326,7 @@
         <v>12</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C311" s="11" t="s">
         <v>25</v>
@@ -7343,7 +7343,7 @@
         <v>12</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C312" s="11" t="s">
         <v>25</v>
@@ -7360,7 +7360,7 @@
         <v>12</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C313" s="11" t="s">
         <v>25</v>
@@ -7377,7 +7377,7 @@
         <v>12</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C314" s="11" t="s">
         <v>25</v>
@@ -7394,7 +7394,7 @@
         <v>12</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C315" s="11" t="s">
         <v>25</v>
@@ -7411,7 +7411,7 @@
         <v>12</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C316" s="11" t="s">
         <v>25</v>
@@ -7428,7 +7428,7 @@
         <v>12</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C317" s="11" t="s">
         <v>25</v>
@@ -7445,7 +7445,7 @@
         <v>12</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C318" s="11" t="s">
         <v>25</v>
@@ -7462,7 +7462,7 @@
         <v>12</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C319" s="11" t="s">
         <v>25</v>
@@ -7479,7 +7479,7 @@
         <v>12</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C320" s="11" t="s">
         <v>25</v>
@@ -7496,7 +7496,7 @@
         <v>12</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C321" s="11" t="s">
         <v>25</v>
@@ -7513,13 +7513,13 @@
         <v>14</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C322" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D322" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E322" s="10" t="s">
         <v>27</v>
@@ -7530,13 +7530,13 @@
         <v>14</v>
       </c>
       <c r="B323" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C323" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D323" s="12" t="s">
         <v>368</v>
-      </c>
-      <c r="C323" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D323" s="12" t="s">
-        <v>369</v>
       </c>
       <c r="E323" s="10" t="s">
         <v>27</v>
@@ -7553,7 +7553,7 @@
         <v>25</v>
       </c>
       <c r="D324" s="12" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E324" s="10" t="s">
         <v>27</v>
@@ -7564,13 +7564,13 @@
         <v>14</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C325" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D325" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E325" s="10" t="s">
         <v>27</v>
@@ -7581,13 +7581,13 @@
         <v>14</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C326" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D326" s="12" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E326" s="10" t="s">
         <v>27</v>
@@ -7598,13 +7598,13 @@
         <v>14</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C327" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D327" s="12" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E327" s="10" t="s">
         <v>27</v>
@@ -7615,13 +7615,13 @@
         <v>14</v>
       </c>
       <c r="B328" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C328" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D328" s="12" t="s">
         <v>375</v>
-      </c>
-      <c r="C328" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D328" s="12" t="s">
-        <v>371</v>
       </c>
       <c r="E328" s="10" t="s">
         <v>27</v>
@@ -7638,7 +7638,7 @@
         <v>25</v>
       </c>
       <c r="D329" s="12" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E329" s="10" t="s">
         <v>27</v>
@@ -7689,7 +7689,7 @@
         <v>25</v>
       </c>
       <c r="D332" s="12" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E332" s="10" t="s">
         <v>27</v>
@@ -7700,7 +7700,7 @@
         <v>14</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C333" s="11" t="s">
         <v>25</v>
@@ -7717,13 +7717,13 @@
         <v>14</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C334" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D334" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E334" s="10" t="s">
         <v>27</v>
@@ -7734,13 +7734,13 @@
         <v>14</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C335" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D335" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E335" s="10" t="s">
         <v>27</v>
@@ -7751,13 +7751,13 @@
         <v>14</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C336" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D336" s="12" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E336" s="10" t="s">
         <v>27</v>
@@ -7768,7 +7768,7 @@
         <v>14</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C337" s="11" t="s">
         <v>25</v>
@@ -7785,7 +7785,7 @@
         <v>14</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C338" s="11" t="s">
         <v>25</v>
@@ -7802,13 +7802,13 @@
         <v>14</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C339" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D339" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E339" s="10" t="s">
         <v>27</v>
@@ -7819,13 +7819,13 @@
         <v>14</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C340" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D340" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E340" s="10" t="s">
         <v>27</v>
@@ -7836,13 +7836,13 @@
         <v>14</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C341" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D341" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E341" s="10" t="s">
         <v>27</v>
@@ -7853,13 +7853,13 @@
         <v>14</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C342" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D342" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E342" s="10" t="s">
         <v>27</v>
@@ -7870,7 +7870,7 @@
         <v>14</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C343" s="11" t="s">
         <v>25</v>
@@ -7887,13 +7887,13 @@
         <v>14</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C344" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E344" s="10" t="s">
         <v>27</v>
@@ -7904,13 +7904,13 @@
         <v>14</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C345" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D345" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E345" s="10" t="s">
         <v>27</v>
@@ -7921,7 +7921,7 @@
         <v>14</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C346" s="11" t="s">
         <v>25</v>
@@ -7938,13 +7938,13 @@
         <v>14</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C347" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E347" s="10" t="s">
         <v>27</v>
@@ -7955,13 +7955,13 @@
         <v>14</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C348" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E348" s="10" t="s">
         <v>27</v>
@@ -7972,7 +7972,7 @@
         <v>14</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C349" s="11" t="s">
         <v>25</v>
@@ -7989,13 +7989,13 @@
         <v>14</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C350" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E350" s="10" t="s">
         <v>27</v>
@@ -8006,13 +8006,13 @@
         <v>14</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C351" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D351" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E351" s="10" t="s">
         <v>27</v>
@@ -8023,13 +8023,13 @@
         <v>14</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C352" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E352" s="10" t="s">
         <v>27</v>
@@ -8040,13 +8040,13 @@
         <v>14</v>
       </c>
       <c r="B353" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C353" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E353" s="10" t="s">
         <v>27</v>
@@ -8057,13 +8057,13 @@
         <v>14</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C354" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E354" s="10" t="s">
         <v>27</v>
@@ -8074,13 +8074,13 @@
         <v>14</v>
       </c>
       <c r="B355" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C355" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E355" s="10" t="s">
         <v>27</v>
@@ -8091,13 +8091,13 @@
         <v>14</v>
       </c>
       <c r="B356" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C356" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E356" s="10" t="s">
         <v>27</v>
@@ -8108,13 +8108,13 @@
         <v>14</v>
       </c>
       <c r="B357" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C357" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E357" s="10" t="s">
         <v>27</v>
@@ -8125,13 +8125,13 @@
         <v>14</v>
       </c>
       <c r="B358" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C358" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E358" s="10" t="s">
         <v>27</v>
@@ -8142,13 +8142,13 @@
         <v>14</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C359" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E359" s="10" t="s">
         <v>27</v>
@@ -8159,7 +8159,7 @@
         <v>14</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C360" s="11" t="s">
         <v>25</v>
@@ -8176,7 +8176,7 @@
         <v>14</v>
       </c>
       <c r="B361" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C361" s="11" t="s">
         <v>25</v>
@@ -8193,13 +8193,13 @@
         <v>14</v>
       </c>
       <c r="B362" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C362" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D362" s="12" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E362" s="10" t="s">
         <v>27</v>
@@ -8210,13 +8210,13 @@
         <v>14</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C363" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E363" s="10" t="s">
         <v>27</v>
@@ -8227,7 +8227,7 @@
         <v>14</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C364" s="11" t="s">
         <v>25</v>
@@ -8244,13 +8244,13 @@
         <v>14</v>
       </c>
       <c r="B365" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C365" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E365" s="10" t="s">
         <v>27</v>
@@ -8261,13 +8261,13 @@
         <v>14</v>
       </c>
       <c r="B366" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C366" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E366" s="10" t="s">
         <v>27</v>
@@ -8278,13 +8278,13 @@
         <v>14</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C367" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E367" s="10" t="s">
         <v>27</v>
@@ -8295,13 +8295,13 @@
         <v>14</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C368" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E368" s="10" t="s">
         <v>27</v>
@@ -8312,13 +8312,13 @@
         <v>14</v>
       </c>
       <c r="B369" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C369" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E369" s="10" t="s">
         <v>27</v>
@@ -8329,13 +8329,13 @@
         <v>14</v>
       </c>
       <c r="B370" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C370" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D370" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E370" s="10" t="s">
         <v>27</v>
@@ -8346,13 +8346,13 @@
         <v>14</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C371" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D371" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E371" s="10" t="s">
         <v>27</v>
@@ -8363,13 +8363,13 @@
         <v>14</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C372" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D372" s="12" t="s">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="E372" s="10" t="s">
         <v>27</v>
@@ -8386,7 +8386,7 @@
         <v>25</v>
       </c>
       <c r="D373" s="12" t="s">
-        <v>420</v>
+        <v>29</v>
       </c>
       <c r="E373" s="10" t="s">
         <v>27</v>
@@ -8403,7 +8403,7 @@
         <v>25</v>
       </c>
       <c r="D374" s="12" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="E374" s="10" t="s">
         <v>27</v>
@@ -8437,7 +8437,7 @@
         <v>25</v>
       </c>
       <c r="D376" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E376" s="10" t="s">
         <v>27</v>
@@ -8454,7 +8454,7 @@
         <v>25</v>
       </c>
       <c r="D377" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E377" s="10" t="s">
         <v>27</v>
@@ -8505,7 +8505,7 @@
         <v>25</v>
       </c>
       <c r="D380" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E380" s="10" t="s">
         <v>27</v>
@@ -8522,7 +8522,7 @@
         <v>25</v>
       </c>
       <c r="D381" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E381" s="10" t="s">
         <v>27</v>
@@ -8556,7 +8556,7 @@
         <v>25</v>
       </c>
       <c r="D383" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E383" s="10" t="s">
         <v>27</v>
@@ -8573,7 +8573,7 @@
         <v>25</v>
       </c>
       <c r="D384" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E384" s="10" t="s">
         <v>27</v>
@@ -8590,7 +8590,7 @@
         <v>25</v>
       </c>
       <c r="D385" s="12" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E385" s="10" t="s">
         <v>27</v>
@@ -8607,7 +8607,7 @@
         <v>25</v>
       </c>
       <c r="D386" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E386" s="10" t="s">
         <v>27</v>
@@ -8624,7 +8624,7 @@
         <v>25</v>
       </c>
       <c r="D387" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E387" s="10" t="s">
         <v>27</v>
@@ -8641,7 +8641,7 @@
         <v>25</v>
       </c>
       <c r="D388" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E388" s="10" t="s">
         <v>27</v>
@@ -8692,7 +8692,7 @@
         <v>25</v>
       </c>
       <c r="D391" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E391" s="10" t="s">
         <v>27</v>
@@ -8709,7 +8709,7 @@
         <v>25</v>
       </c>
       <c r="D392" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E392" s="10" t="s">
         <v>27</v>
@@ -8726,7 +8726,7 @@
         <v>25</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E393" s="10" t="s">
         <v>27</v>
@@ -8743,7 +8743,7 @@
         <v>25</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E394" s="10" t="s">
         <v>27</v>
@@ -8760,7 +8760,7 @@
         <v>25</v>
       </c>
       <c r="D395" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E395" s="10" t="s">
         <v>27</v>
@@ -8777,7 +8777,7 @@
         <v>25</v>
       </c>
       <c r="D396" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E396" s="10" t="s">
         <v>27</v>
@@ -8811,7 +8811,7 @@
         <v>25</v>
       </c>
       <c r="D398" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E398" s="10" t="s">
         <v>27</v>
@@ -8845,7 +8845,7 @@
         <v>25</v>
       </c>
       <c r="D400" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E400" s="10" t="s">
         <v>27</v>
@@ -8862,7 +8862,7 @@
         <v>25</v>
       </c>
       <c r="D401" s="12" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E401" s="10" t="s">
         <v>27</v>
@@ -8879,7 +8879,7 @@
         <v>25</v>
       </c>
       <c r="D402" s="12" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E402" s="10" t="s">
         <v>27</v>
@@ -8896,7 +8896,7 @@
         <v>25</v>
       </c>
       <c r="D403" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E403" s="10" t="s">
         <v>27</v>
@@ -8913,7 +8913,7 @@
         <v>25</v>
       </c>
       <c r="D404" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E404" s="10" t="s">
         <v>27</v>
@@ -8930,7 +8930,7 @@
         <v>25</v>
       </c>
       <c r="D405" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E405" s="10" t="s">
         <v>27</v>
@@ -8964,7 +8964,7 @@
         <v>25</v>
       </c>
       <c r="D407" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E407" s="10" t="s">
         <v>27</v>
@@ -8981,7 +8981,7 @@
         <v>25</v>
       </c>
       <c r="D408" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E408" s="10" t="s">
         <v>27</v>
@@ -8998,7 +8998,7 @@
         <v>25</v>
       </c>
       <c r="D409" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E409" s="10" t="s">
         <v>27</v>
@@ -9015,7 +9015,7 @@
         <v>25</v>
       </c>
       <c r="D410" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E410" s="10" t="s">
         <v>27</v>
@@ -9032,7 +9032,7 @@
         <v>25</v>
       </c>
       <c r="D411" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E411" s="10" t="s">
         <v>27</v>
@@ -9066,7 +9066,7 @@
         <v>25</v>
       </c>
       <c r="D413" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E413" s="10" t="s">
         <v>27</v>
@@ -9083,7 +9083,7 @@
         <v>25</v>
       </c>
       <c r="D414" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E414" s="10" t="s">
         <v>27</v>
@@ -9100,7 +9100,7 @@
         <v>25</v>
       </c>
       <c r="D415" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E415" s="10" t="s">
         <v>27</v>
@@ -9117,7 +9117,7 @@
         <v>25</v>
       </c>
       <c r="D416" s="12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E416" s="10" t="s">
         <v>27</v>
@@ -9134,7 +9134,7 @@
         <v>25</v>
       </c>
       <c r="D417" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E417" s="10" t="s">
         <v>27</v>
@@ -9168,7 +9168,7 @@
         <v>25</v>
       </c>
       <c r="D419" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E419" s="10" t="s">
         <v>27</v>
@@ -9185,7 +9185,7 @@
         <v>25</v>
       </c>
       <c r="D420" s="12" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E420" s="10" t="s">
         <v>27</v>
@@ -9202,7 +9202,7 @@
         <v>25</v>
       </c>
       <c r="D421" s="12" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E421" s="10" t="s">
         <v>27</v>

--- a/test-cases-reports/selinium-test/selenium_web_report.xlsx
+++ b/test-cases-reports/selinium-test/selenium_web_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="473">
   <si>
     <t>STRIVECAMPUS WEB E2E TEST SUMMARY</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>90.58s</t>
+    <t>91.29s</t>
   </si>
   <si>
     <t>Deployable Status</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>4.32s</t>
+    <t>4.17s</t>
   </si>
   <si>
     <t>-</t>
@@ -128,453 +128,468 @@
     <t>UI009: Onboarding page 2 title display</t>
   </si>
   <si>
+    <t>2.26s</t>
+  </si>
+  <si>
+    <t>UI010: Onboarding page 2 description text layout</t>
+  </si>
+  <si>
+    <t>UI011: Onboarding page 2 active page indicator state</t>
+  </si>
+  <si>
+    <t>0.02s</t>
+  </si>
+  <si>
+    <t>UI012: Onboarding page 3 title display</t>
+  </si>
+  <si>
+    <t>2.08s</t>
+  </si>
+  <si>
+    <t>UI013: Onboarding page 3 description text layout</t>
+  </si>
+  <si>
+    <t>UI014: Onboarding page 3 Get Started button layout</t>
+  </si>
+  <si>
+    <t>UI015: Login Screen background card shape</t>
+  </si>
+  <si>
+    <t>4.15s</t>
+  </si>
+  <si>
+    <t>UI016: Login screen email input container styling</t>
+  </si>
+  <si>
+    <t>UI017: Login screen password input container styling</t>
+  </si>
+  <si>
+    <t>0.05s</t>
+  </si>
+  <si>
+    <t>UI018: Login button background design</t>
+  </si>
+  <si>
+    <t>UI019: Login header branding typography</t>
+  </si>
+  <si>
+    <t>UI020: Register screen fields typography and spacing</t>
+  </si>
+  <si>
+    <t>2.11s</t>
+  </si>
+  <si>
+    <t>UI021: Register button border radius</t>
+  </si>
+  <si>
+    <t>0.03s</t>
+  </si>
+  <si>
+    <t>UI022: Register footer link styling</t>
+  </si>
+  <si>
+    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
+  </si>
+  <si>
+    <t>UI024: Dashboard header title formatting</t>
+  </si>
+  <si>
+    <t>UI025: Theme toggler button visual contrast</t>
+  </si>
+  <si>
+    <t>UI026: Light mode dashboard theme colors</t>
+  </si>
+  <si>
+    <t>UI027: Dark mode theme transition styles</t>
+  </si>
+  <si>
+    <t>UI028: Profile screen user avatar size layout</t>
+  </si>
+  <si>
+    <t>UI029: Test session card border margins</t>
+  </si>
+  <si>
+    <t>UI030: AI Feedback dialog spacing layout</t>
+  </si>
+  <si>
+    <t>UI031: Onboarding page dot animation transition duration checks</t>
+  </si>
+  <si>
+    <t>UI032: Onboarding skip button typography style properties matching</t>
+  </si>
+  <si>
+    <t>UI033: Splash logo container dimensions ratio verification</t>
+  </si>
+  <si>
+    <t>UI034: Splash loader indicator circular progress thickness details</t>
+  </si>
+  <si>
+    <t>UI035: Authentication textfield error messaging text font style alignment</t>
+  </si>
+  <si>
+    <t>UI036: Login submit button responsive hover opacity changes</t>
+  </si>
+  <si>
+    <t>UI037: Register page input padding offsets consistency checks</t>
+  </si>
+  <si>
+    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
+  </si>
+  <si>
+    <t>UI039: Dark mode active body background color matching parameters</t>
+  </si>
+  <si>
+    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
+  </si>
+  <si>
+    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
+  </si>
+  <si>
+    <t>UI042: AI mock interview feedback container border lines styling</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>UI043: Chatbot user response chat bubble alignment properties</t>
+  </si>
+  <si>
+    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
+  </si>
+  <si>
+    <t>UI045: Profile user name typography scale weight and contrast check</t>
+  </si>
+  <si>
+    <t>UI046: Settings theme toggle switch active color verification parameters</t>
+  </si>
+  <si>
+    <t>UI047: Onboarding title layout alignment centered checking</t>
+  </si>
+  <si>
+    <t>UI048: Textfields active cursor focus color validation</t>
+  </si>
+  <si>
+    <t>UI049: Error messages warning badge layout constraints</t>
+  </si>
+  <si>
+    <t>UI050: App notification icon badges count scaling parameters</t>
+  </si>
+  <si>
+    <t>UI051: Profile card statistics counts label typography sizing</t>
+  </si>
+  <si>
+    <t>UI052: HR round option button icons visual alignment</t>
+  </si>
+  <si>
+    <t>UI053: Tech round option card layout spacing check</t>
+  </si>
+  <si>
+    <t>UI054: Aptitude test category cards layout alignment parameters</t>
+  </si>
+  <si>
+    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
+  </si>
+  <si>
+    <t>UI056: Alert dialog box overlay transparency index verification</t>
+  </si>
+  <si>
+    <t>UI057: Groq feedback score badge layout circular border alignment</t>
+  </si>
+  <si>
+    <t>UI058: Speech input icon active mic glow styling parameters</t>
+  </si>
+  <si>
+    <t>UI059: Dark theme input borders contrast rating validation</t>
+  </si>
+  <si>
+    <t>UI060: Onboarding next button icon placement side margins checking</t>
+  </si>
+  <si>
+    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
+  </si>
+  <si>
+    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
+  </si>
+  <si>
+    <t>UI063: Aptitude quiz progress bar line color status verification</t>
+  </si>
+  <si>
+    <t>UI064: Custom card elements scaling values on larger resolutions</t>
+  </si>
+  <si>
+    <t>UI065: Custom list dividers height thickness checking parameters</t>
+  </si>
+  <si>
+    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
+  </si>
+  <si>
+    <t>UI067: App header icon menu spacing and positioning specifications</t>
+  </si>
+  <si>
+    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
+  </si>
+  <si>
+    <t>UI069: Text input fields placeholder character font styling rules</t>
+  </si>
+  <si>
+    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
+  </si>
+  <si>
+    <t>UI071: Profile credentials edit inputs layout alignment values</t>
+  </si>
+  <si>
+    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
+  </si>
+  <si>
+    <t>UI073: Custom snackbar popup notifications container design styles</t>
+  </si>
+  <si>
+    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
+  </si>
+  <si>
+    <t>UI075: Webapp container shadow outline styling matching specifications</t>
+  </si>
+  <si>
+    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
+  </si>
+  <si>
+    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
+  </si>
+  <si>
+    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
+  </si>
+  <si>
+    <t>UI079: Chat suggestion chips outline border thickness details</t>
+  </si>
+  <si>
+    <t>UI080: Settings section headers font size transformations checking</t>
+  </si>
+  <si>
+    <t>UI081: Login forgot password link visual underline toggle checks</t>
+  </si>
+  <si>
+    <t>UI082: Register legal policies agreements text box layouts checks</t>
+  </si>
+  <si>
+    <t>UI083: Placement details document viewer layout padding verification</t>
+  </si>
+  <si>
+    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
+  </si>
+  <si>
+    <t>UI085: Custom dropdown selectors hover outline border width check</t>
+  </si>
+  <si>
+    <t>UI086: Dialog confirmations layouts check icon centering values</t>
+  </si>
+  <si>
+    <t>UI087: Chat input field icons click state opacity level updates</t>
+  </si>
+  <si>
+    <t>UI088: User avatar badge active placement online status display</t>
+  </si>
+  <si>
+    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
+  </si>
+  <si>
+    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
+  </si>
+  <si>
+    <t>UI091: Aptitude result summary page visual headers scaling check</t>
+  </si>
+  <si>
+    <t>UI092: AI feedback details accordion expand collapse height values</t>
+  </si>
+  <si>
+    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
+  </si>
+  <si>
+    <t>UI094: Navigation bar labels selected font color parameter checks</t>
+  </si>
+  <si>
+    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
+  </si>
+  <si>
+    <t>UI096: Settings section divider margins layout alignment specifications</t>
+  </si>
+  <si>
+    <t>UI097: Placement company filters panel layout drawer design styles</t>
+  </si>
+  <si>
+    <t>UI098: Notification toggle buttons sliding animation duration check</t>
+  </si>
+  <si>
+    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
+  </si>
+  <si>
+    <t>UI100: Auth form title secondary text decoration attributes check</t>
+  </si>
+  <si>
+    <t>UI101: Chat message time badge indicator font weight properties</t>
+  </si>
+  <si>
+    <t>UI102: Profile page history entries list spacing parameters</t>
+  </si>
+  <si>
+    <t>UI103: Feedback text block alignment rules inside cards check</t>
+  </si>
+  <si>
+    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
+  </si>
+  <si>
+    <t>UI105: Interview review card layout horizontal borders constraint</t>
+  </si>
+  <si>
+    <t>UI106: Light mode inputs focus border shadow layout checks</t>
+  </si>
+  <si>
+    <t>UI107: Settings clear cache option text style parameters matching</t>
+  </si>
+  <si>
+    <t>UI108: Placement job card badges layout visual check rules</t>
+  </si>
+  <si>
+    <t>UI109: Speech processing overlay spinner styling visual verification</t>
+  </si>
+  <si>
+    <t>UI110: Test report dashboard header title color styling verification</t>
+  </si>
+  <si>
+    <t>FN001: Load app page successfully</t>
+  </si>
+  <si>
+    <t>4.14s</t>
+  </si>
+  <si>
+    <t>FN002: Click Next to access page 2</t>
+  </si>
+  <si>
     <t>2.10s</t>
   </si>
   <si>
-    <t>UI010: Onboarding page 2 description text layout</t>
-  </si>
-  <si>
-    <t>UI011: Onboarding page 2 active page indicator state</t>
-  </si>
-  <si>
-    <t>UI012: Onboarding page 3 title display</t>
-  </si>
-  <si>
-    <t>2.11s</t>
-  </si>
-  <si>
-    <t>UI013: Onboarding page 3 description text layout</t>
-  </si>
-  <si>
-    <t>UI014: Onboarding page 3 Get Started button layout</t>
-  </si>
-  <si>
-    <t>UI015: Login Screen background card shape</t>
-  </si>
-  <si>
-    <t>4.12s</t>
-  </si>
-  <si>
-    <t>UI016: Login screen email input container styling</t>
-  </si>
-  <si>
-    <t>UI017: Login screen password input container styling</t>
-  </si>
-  <si>
-    <t>UI018: Login button background design</t>
-  </si>
-  <si>
-    <t>UI019: Login header branding typography</t>
-  </si>
-  <si>
-    <t>UI020: Register screen fields typography and spacing</t>
-  </si>
-  <si>
-    <t>2.08s</t>
-  </si>
-  <si>
-    <t>UI021: Register button border radius</t>
-  </si>
-  <si>
-    <t>UI022: Register footer link styling</t>
-  </si>
-  <si>
-    <t>UI023: Bottom navigation bar alignment &amp; icon sets</t>
-  </si>
-  <si>
-    <t>UI024: Dashboard header title formatting</t>
-  </si>
-  <si>
-    <t>UI025: Theme toggler button visual contrast</t>
-  </si>
-  <si>
-    <t>UI026: Light mode dashboard theme colors</t>
-  </si>
-  <si>
-    <t>UI027: Dark mode theme transition styles</t>
-  </si>
-  <si>
-    <t>UI028: Profile screen user avatar size layout</t>
-  </si>
-  <si>
-    <t>UI029: Test session card border margins</t>
-  </si>
-  <si>
-    <t>UI030: AI Feedback dialog spacing layout</t>
-  </si>
-  <si>
-    <t>UI031: Onboarding page dot animation transition duration checks</t>
-  </si>
-  <si>
-    <t>UI032: Onboarding skip button typography style properties matching</t>
-  </si>
-  <si>
-    <t>UI033: Splash logo container dimensions ratio verification</t>
-  </si>
-  <si>
-    <t>UI034: Splash loader indicator circular progress thickness details</t>
-  </si>
-  <si>
-    <t>UI035: Authentication textfield error messaging text font style alignment</t>
-  </si>
-  <si>
-    <t>UI036: Login submit button responsive hover opacity changes</t>
-  </si>
-  <si>
-    <t>UI037: Register page input padding offsets consistency checks</t>
-  </si>
-  <si>
-    <t>0.02s</t>
-  </si>
-  <si>
-    <t>UI038: Custom appbar back navigation icon asset visual sizing</t>
-  </si>
-  <si>
-    <t>UI039: Dark mode active body background color matching parameters</t>
-  </si>
-  <si>
-    <t>UI040: Dashboard card shadows soft elevation border rendering</t>
-  </si>
-  <si>
-    <t>UI041: Tests tab bar category tab selected state visual highlight check</t>
-  </si>
-  <si>
-    <t>UI042: AI mock interview feedback container border lines styling</t>
-  </si>
-  <si>
-    <t>UI043: Chatbot user response chat bubble alignment properties</t>
-  </si>
-  <si>
-    <t>UI044: Chatbot assistant AI response bubble border radius constraints</t>
-  </si>
-  <si>
-    <t>UI045: Profile user name typography scale weight and contrast check</t>
-  </si>
-  <si>
-    <t>UI046: Settings theme toggle switch active color verification parameters</t>
-  </si>
-  <si>
-    <t>UI047: Onboarding title layout alignment centered checking</t>
-  </si>
-  <si>
-    <t>UI048: Textfields active cursor focus color validation</t>
-  </si>
-  <si>
-    <t>UI049: Error messages warning badge layout constraints</t>
-  </si>
-  <si>
-    <t>UI050: App notification icon badges count scaling parameters</t>
-  </si>
-  <si>
-    <t>UI051: Profile card statistics counts label typography sizing</t>
-  </si>
-  <si>
-    <t>UI052: HR round option button icons visual alignment</t>
-  </si>
-  <si>
-    <t>UI053: Tech round option card layout spacing check</t>
-  </si>
-  <si>
-    <t>UI054: Aptitude test category cards layout alignment parameters</t>
-  </si>
-  <si>
-    <t>UI055: Bottom sheet dialog header drag indicator bar styling</t>
-  </si>
-  <si>
-    <t>UI056: Alert dialog box overlay transparency index verification</t>
-  </si>
-  <si>
-    <t>UI057: Groq feedback score badge layout circular border alignment</t>
-  </si>
-  <si>
-    <t>UI058: Speech input icon active mic glow styling parameters</t>
-  </si>
-  <si>
-    <t>UI059: Dark theme input borders contrast rating validation</t>
-  </si>
-  <si>
-    <t>UI060: Onboarding next button icon placement side margins checking</t>
-  </si>
-  <si>
-    <t>UI061: Login form subtitle text wrapping behavior bounds verification</t>
-  </si>
-  <si>
-    <t>UI062: Profile layout scroll indicator visibility and design parameters</t>
-  </si>
-  <si>
-    <t>UI063: Aptitude quiz progress bar line color status verification</t>
-  </si>
-  <si>
-    <t>UI064: Custom card elements scaling values on larger resolutions</t>
-  </si>
-  <si>
-    <t>UI065: Custom list dividers height thickness checking parameters</t>
-  </si>
-  <si>
-    <t>UI066: Chat list loading skeleton screen layout alignment details</t>
-  </si>
-  <si>
-    <t>UI067: App header icon menu spacing and positioning specifications</t>
-  </si>
-  <si>
-    <t>UI068: Dialog dismiss button visual contrast and margin constraints</t>
-  </si>
-  <si>
-    <t>UI069: Text input fields placeholder character font styling rules</t>
-  </si>
-  <si>
-    <t>UI070: Feedback ratings star icons design grid layout parameters</t>
-  </si>
-  <si>
-    <t>UI071: Profile credentials edit inputs layout alignment values</t>
-  </si>
-  <si>
-    <t>UI072: Dashboard summary graphs axes labels readability scores check</t>
-  </si>
-  <si>
-    <t>UI073: Custom snackbar popup notifications container design styles</t>
-  </si>
-  <si>
-    <t>UI074: Speech to text helper guidelines panel visibility parameters</t>
-  </si>
-  <si>
-    <t>UI075: Webapp container shadow outline styling matching specifications</t>
-  </si>
-  <si>
-    <t>UI076: HR questions text wrapper paragraph line height constraints</t>
-  </si>
-  <si>
-    <t>UI077: Test score progress ring gauge indicator layout parameters</t>
-  </si>
-  <si>
-    <t>UI078: Dark theme headers shadow drop transitions layout options</t>
-  </si>
-  <si>
-    <t>UI079: Chat suggestion chips outline border thickness details</t>
-  </si>
-  <si>
-    <t>UI080: Settings section headers font size transformations checking</t>
-  </si>
-  <si>
-    <t>UI081: Login forgot password link visual underline toggle checks</t>
-  </si>
-  <si>
-    <t>UI082: Register legal policies agreements text box layouts checks</t>
-  </si>
-  <si>
-    <t>UI083: Placement details document viewer layout padding verification</t>
-  </si>
-  <si>
-    <t>UI084: Onboarding page transitions ease in curve validation limits</t>
-  </si>
-  <si>
-    <t>UI085: Custom dropdown selectors hover outline border width check</t>
-  </si>
-  <si>
-    <t>UI086: Dialog confirmations layouts check icon centering values</t>
-  </si>
-  <si>
-    <t>UI087: Chat input field icons click state opacity level updates</t>
-  </si>
-  <si>
-    <t>UI088: User avatar badge active placement online status display</t>
-  </si>
-  <si>
-    <t>UI089: Dashboard widgets responsive grid wrap breakpoint parameters</t>
-  </si>
-  <si>
-    <t>UI090: Error boundary layout screen logo styling matches guidelines</t>
-  </si>
-  <si>
-    <t>UI091: Aptitude result summary page visual headers scaling check</t>
-  </si>
-  <si>
-    <t>UI092: AI feedback details accordion expand collapse height values</t>
-  </si>
-  <si>
-    <t>UI093: Tech stack tags background pills color schemes mapping check</t>
-  </si>
-  <si>
-    <t>0.04s</t>
-  </si>
-  <si>
-    <t>UI094: Navigation bar labels selected font color parameter checks</t>
-  </si>
-  <si>
-    <t>UI095: Chat bot scroll to bottom button visual position layout</t>
-  </si>
-  <si>
-    <t>UI096: Settings section divider margins layout alignment specifications</t>
-  </si>
-  <si>
-    <t>UI097: Placement company filters panel layout drawer design styles</t>
-  </si>
-  <si>
-    <t>UI098: Notification toggle buttons sliding animation duration check</t>
-  </si>
-  <si>
-    <t>UI099: Onboarding screen 3 logo container height check bounds</t>
-  </si>
-  <si>
-    <t>UI100: Auth form title secondary text decoration attributes check</t>
-  </si>
-  <si>
-    <t>UI101: Chat message time badge indicator font weight properties</t>
-  </si>
-  <si>
-    <t>UI102: Profile page history entries list spacing parameters</t>
-  </si>
-  <si>
-    <t>UI103: Feedback text block alignment rules inside cards check</t>
-  </si>
-  <si>
-    <t>UI104: Custom tooltips hover dynamic layout rendering boundaries</t>
-  </si>
-  <si>
-    <t>UI105: Interview review card layout horizontal borders constraint</t>
-  </si>
-  <si>
-    <t>UI106: Light mode inputs focus border shadow layout checks</t>
-  </si>
-  <si>
-    <t>UI107: Settings clear cache option text style parameters matching</t>
-  </si>
-  <si>
-    <t>UI108: Placement job card badges layout visual check rules</t>
-  </si>
-  <si>
-    <t>UI109: Speech processing overlay spinner styling visual verification</t>
-  </si>
-  <si>
-    <t>UI110: Test report dashboard header title color styling verification</t>
-  </si>
-  <si>
-    <t>FN001: Load app page successfully</t>
-  </si>
-  <si>
-    <t>4.09s</t>
-  </si>
-  <si>
-    <t>FN002: Click Next to access page 2</t>
+    <t>FN003: Click Next to access page 3</t>
+  </si>
+  <si>
+    <t>2.06s</t>
+  </si>
+  <si>
+    <t>FN004: Skip button bypasses onboarding screen</t>
+  </si>
+  <si>
+    <t>6.28s</t>
+  </si>
+  <si>
+    <t>FN005: Complete onboarding and transition to authentication page</t>
+  </si>
+  <si>
+    <t>2.18s</t>
+  </si>
+  <si>
+    <t>FN006: Select register navigation path</t>
+  </si>
+  <si>
+    <t>FN007: Register a new account with valid unique details</t>
+  </si>
+  <si>
+    <t>2.14s</t>
+  </si>
+  <si>
+    <t>FN008: Submit register account credentials to Firestore</t>
+  </si>
+  <si>
+    <t>2.13s</t>
+  </si>
+  <si>
+    <t>FN009: Verify user main dashboard is successfully loaded</t>
+  </si>
+  <si>
+    <t>0.51s</t>
+  </si>
+  <si>
+    <t>FN010: Navigate to Aptitude &amp; Technical Tests tab</t>
+  </si>
+  <si>
+    <t>FN011: Render Aptitude list categories</t>
+  </si>
+  <si>
+    <t>FN012: Switch tests list to Technical category</t>
+  </si>
+  <si>
+    <t>FN013: Switch tests list to HR category</t>
   </si>
   <si>
     <t>2.09s</t>
   </si>
   <si>
-    <t>FN003: Click Next to access page 3</t>
-  </si>
-  <si>
-    <t>FN004: Skip button bypasses onboarding screen</t>
-  </si>
-  <si>
-    <t>6.17s</t>
-  </si>
-  <si>
-    <t>FN005: Complete onboarding and transition to authentication page</t>
-  </si>
-  <si>
-    <t>2.13s</t>
-  </si>
-  <si>
-    <t>FN006: Select register navigation path</t>
-  </si>
-  <si>
-    <t>FN007: Register a new account with valid unique details</t>
-  </si>
-  <si>
-    <t>FN008: Submit register account credentials to Firestore</t>
-  </si>
-  <si>
-    <t>2.07s</t>
-  </si>
-  <si>
-    <t>FN009: Verify user main dashboard is successfully loaded</t>
-  </si>
-  <si>
-    <t>0.53s</t>
-  </si>
-  <si>
-    <t>FN010: Navigate to Aptitude &amp; Technical Tests tab</t>
+    <t>FN014: Select HR Mock Interview session card</t>
+  </si>
+  <si>
+    <t>FN015: Set question counts in configuration card</t>
+  </si>
+  <si>
+    <t>FN016: Launch the HR Interview round</t>
+  </si>
+  <si>
+    <t>FN017: Wait for AI Interviewer to load question details</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>FN018: Retrieve visual text of mock question</t>
+  </si>
+  <si>
+    <t>FN019: Input answer to the generated mock question</t>
+  </si>
+  <si>
+    <t>FN020: Submit answer to AI evaluation engine</t>
+  </si>
+  <si>
+    <t>FN021: Retrieve feedback score from Groq API response</t>
+  </si>
+  <si>
+    <t>2.04s</t>
+  </si>
+  <si>
+    <t>FN022: Display evaluation advice layout</t>
+  </si>
+  <si>
+    <t>FN023: Exit active interview page using close option</t>
+  </si>
+  <si>
+    <t>2.21s</t>
+  </si>
+  <si>
+    <t>FN024: Exit dialog confirmation redirects back to dashboard</t>
+  </si>
+  <si>
+    <t>FN025: Navigate to Chatbot assistant tab</t>
+  </si>
+  <si>
+    <t>FN026: Enter custom text message in chat query input</t>
+  </si>
+  <si>
+    <t>4.16s</t>
+  </si>
+  <si>
+    <t>FN027: Receive chatbot answer correctly</t>
+  </si>
+  <si>
+    <t>1.02s</t>
+  </si>
+  <si>
+    <t>FN028: Access user settings &amp; profile tab</t>
+  </si>
+  <si>
+    <t>FN029: Trigger log out process</t>
+  </si>
+  <si>
+    <t>FN030: Confirm sign out dialog returns user to login view</t>
   </si>
   <si>
     <t>2.12s</t>
   </si>
   <si>
-    <t>FN011: Render Aptitude list categories</t>
-  </si>
-  <si>
-    <t>FN012: Switch tests list to Technical category</t>
-  </si>
-  <si>
-    <t>FN013: Switch tests list to HR category</t>
-  </si>
-  <si>
-    <t>FN014: Select HR Mock Interview session card</t>
-  </si>
-  <si>
-    <t>FN015: Set question counts in configuration card</t>
-  </si>
-  <si>
-    <t>FN016: Launch the HR Interview round</t>
-  </si>
-  <si>
-    <t>FN017: Wait for AI Interviewer to load question details</t>
-  </si>
-  <si>
-    <t>1.51s</t>
-  </si>
-  <si>
-    <t>FN018: Retrieve visual text of mock question</t>
-  </si>
-  <si>
-    <t>FN019: Input answer to the generated mock question</t>
-  </si>
-  <si>
-    <t>4.19s</t>
-  </si>
-  <si>
-    <t>FN020: Submit answer to AI evaluation engine</t>
-  </si>
-  <si>
-    <t>FN021: Retrieve feedback score from Groq API response</t>
-  </si>
-  <si>
-    <t>2.01s</t>
-  </si>
-  <si>
-    <t>FN022: Display evaluation advice layout</t>
-  </si>
-  <si>
-    <t>FN023: Exit active interview page using close option</t>
-  </si>
-  <si>
-    <t>FN024: Exit dialog confirmation redirects back to dashboard</t>
-  </si>
-  <si>
-    <t>FN025: Navigate to Chatbot assistant tab</t>
-  </si>
-  <si>
-    <t>FN026: Enter custom text message in chat query input</t>
-  </si>
-  <si>
-    <t>4.18s</t>
-  </si>
-  <si>
-    <t>FN027: Receive chatbot answer correctly</t>
-  </si>
-  <si>
-    <t>1.04s</t>
-  </si>
-  <si>
-    <t>FN028: Access user settings &amp; profile tab</t>
-  </si>
-  <si>
-    <t>FN029: Trigger log out process</t>
-  </si>
-  <si>
-    <t>FN030: Confirm sign out dialog returns user to login view</t>
-  </si>
-  <si>
     <t>FN031: Onboarding page swiping triggers screen text transitions</t>
   </si>
   <si>
@@ -1139,9 +1154,6 @@
     <t>VL007: Authenticate with wrong password key error toast</t>
   </si>
   <si>
-    <t>0.12s</t>
-  </si>
-  <si>
     <t>VL008: Submit empty text answer to HR Interviewer returns validation message</t>
   </si>
   <si>
@@ -1152,9 +1164,6 @@
   </si>
   <si>
     <t>VL011: Submit aptitude test with no questions answered displays alert dialog</t>
-  </si>
-  <si>
-    <t>0.10s</t>
   </si>
   <si>
     <t>VL012: Save offline test session log validation check</t>
@@ -2181,7 +2190,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>27</v>
@@ -2232,7 +2241,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>27</v>
@@ -2249,7 +2258,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>27</v>
@@ -2260,13 +2269,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>27</v>
@@ -2277,7 +2286,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>25</v>
@@ -2294,7 +2303,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>25</v>
@@ -2311,13 +2320,13 @@
         <v>7</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>27</v>
@@ -2328,13 +2337,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>27</v>
@@ -2345,13 +2354,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>27</v>
@@ -2362,13 +2371,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>27</v>
@@ -2379,7 +2388,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>25</v>
@@ -2396,13 +2405,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>27</v>
@@ -2413,13 +2422,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>27</v>
@@ -2430,13 +2439,13 @@
         <v>7</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>27</v>
@@ -2447,7 +2456,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>25</v>
@@ -2464,7 +2473,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>25</v>
@@ -2481,7 +2490,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>25</v>
@@ -2498,13 +2507,13 @@
         <v>7</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>27</v>
@@ -2515,13 +2524,13 @@
         <v>7</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>27</v>
@@ -2532,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>25</v>
@@ -2549,13 +2558,13 @@
         <v>7</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>27</v>
@@ -2566,7 +2575,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>25</v>
@@ -2583,7 +2592,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>25</v>
@@ -2600,7 +2609,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>25</v>
@@ -2617,7 +2626,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>25</v>
@@ -2634,7 +2643,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>25</v>
@@ -2651,7 +2660,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>25</v>
@@ -2668,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>25</v>
@@ -2685,13 +2694,13 @@
         <v>7</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>27</v>
@@ -2702,7 +2711,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>25</v>
@@ -2719,7 +2728,7 @@
         <v>7</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>25</v>
@@ -2736,13 +2745,13 @@
         <v>7</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>27</v>
@@ -2753,13 +2762,13 @@
         <v>7</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>27</v>
@@ -2770,13 +2779,13 @@
         <v>7</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>27</v>
@@ -2787,7 +2796,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>25</v>
@@ -2804,7 +2813,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>25</v>
@@ -2821,7 +2830,7 @@
         <v>7</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>25</v>
@@ -2838,7 +2847,7 @@
         <v>7</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>25</v>
@@ -2855,13 +2864,13 @@
         <v>7</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>27</v>
@@ -2872,7 +2881,7 @@
         <v>7</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>25</v>
@@ -2889,7 +2898,7 @@
         <v>7</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>25</v>
@@ -2906,7 +2915,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>25</v>
@@ -2923,13 +2932,13 @@
         <v>7</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>27</v>
@@ -2940,7 +2949,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>25</v>
@@ -2957,7 +2966,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>25</v>
@@ -2974,7 +2983,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>25</v>
@@ -2991,7 +3000,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>25</v>
@@ -3008,7 +3017,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>25</v>
@@ -3025,7 +3034,7 @@
         <v>7</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>25</v>
@@ -3042,7 +3051,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>25</v>
@@ -3059,7 +3068,7 @@
         <v>7</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>25</v>
@@ -3076,7 +3085,7 @@
         <v>7</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>25</v>
@@ -3093,7 +3102,7 @@
         <v>7</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>25</v>
@@ -3110,7 +3119,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>25</v>
@@ -3127,7 +3136,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>25</v>
@@ -3144,7 +3153,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>25</v>
@@ -3161,7 +3170,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>25</v>
@@ -3178,13 +3187,13 @@
         <v>7</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>27</v>
@@ -3195,7 +3204,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>25</v>
@@ -3212,7 +3221,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>25</v>
@@ -3229,7 +3238,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>25</v>
@@ -3246,7 +3255,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>25</v>
@@ -3263,7 +3272,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>25</v>
@@ -3280,7 +3289,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>25</v>
@@ -3297,7 +3306,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>25</v>
@@ -3314,7 +3323,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>25</v>
@@ -3331,7 +3340,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>25</v>
@@ -3348,13 +3357,13 @@
         <v>7</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>27</v>
@@ -3365,7 +3374,7 @@
         <v>7</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>25</v>
@@ -3382,13 +3391,13 @@
         <v>7</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>27</v>
@@ -3399,13 +3408,13 @@
         <v>7</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>27</v>
@@ -3416,7 +3425,7 @@
         <v>7</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>25</v>
@@ -3433,7 +3442,7 @@
         <v>7</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>25</v>
@@ -3450,7 +3459,7 @@
         <v>7</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C83" s="11" t="s">
         <v>25</v>
@@ -3467,7 +3476,7 @@
         <v>7</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>25</v>
@@ -3484,7 +3493,7 @@
         <v>7</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>25</v>
@@ -3501,7 +3510,7 @@
         <v>7</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>25</v>
@@ -3518,7 +3527,7 @@
         <v>7</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>25</v>
@@ -3535,7 +3544,7 @@
         <v>7</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>25</v>
@@ -3552,7 +3561,7 @@
         <v>7</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>25</v>
@@ -3569,7 +3578,7 @@
         <v>7</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>25</v>
@@ -3586,13 +3595,13 @@
         <v>7</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>27</v>
@@ -3603,7 +3612,7 @@
         <v>7</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>25</v>
@@ -3620,7 +3629,7 @@
         <v>7</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>25</v>
@@ -3637,13 +3646,13 @@
         <v>7</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>27</v>
@@ -3654,13 +3663,13 @@
         <v>7</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>27</v>
@@ -3671,13 +3680,13 @@
         <v>7</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>27</v>
@@ -3688,7 +3697,7 @@
         <v>7</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>25</v>
@@ -3705,7 +3714,7 @@
         <v>7</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>25</v>
@@ -3722,7 +3731,7 @@
         <v>7</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>25</v>
@@ -3739,13 +3748,13 @@
         <v>7</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>27</v>
@@ -3756,13 +3765,13 @@
         <v>7</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>27</v>
@@ -3773,13 +3782,13 @@
         <v>7</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>27</v>
@@ -3790,7 +3799,7 @@
         <v>7</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>25</v>
@@ -3807,7 +3816,7 @@
         <v>7</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>25</v>
@@ -3824,7 +3833,7 @@
         <v>7</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>25</v>
@@ -3841,7 +3850,7 @@
         <v>7</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>25</v>
@@ -3858,7 +3867,7 @@
         <v>7</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>25</v>
@@ -3875,7 +3884,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>25</v>
@@ -3892,7 +3901,7 @@
         <v>7</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>25</v>
@@ -3909,7 +3918,7 @@
         <v>7</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>25</v>
@@ -3926,7 +3935,7 @@
         <v>7</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>25</v>
@@ -3943,13 +3952,13 @@
         <v>10</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>27</v>
@@ -3960,13 +3969,13 @@
         <v>10</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C113" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>27</v>
@@ -3977,13 +3986,13 @@
         <v>10</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>27</v>
@@ -3994,13 +4003,13 @@
         <v>10</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C115" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>27</v>
@@ -4011,13 +4020,13 @@
         <v>10</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>27</v>
@@ -4028,13 +4037,13 @@
         <v>10</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C117" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>27</v>
@@ -4045,13 +4054,13 @@
         <v>10</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>27</v>
@@ -4062,13 +4071,13 @@
         <v>10</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C119" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>27</v>
@@ -4079,13 +4088,13 @@
         <v>10</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C120" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>27</v>
@@ -4096,13 +4105,13 @@
         <v>10</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C121" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>27</v>
@@ -4113,7 +4122,7 @@
         <v>10</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>25</v>
@@ -4130,13 +4139,13 @@
         <v>10</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C123" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>27</v>
@@ -4147,13 +4156,13 @@
         <v>10</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C124" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>27</v>
@@ -4164,13 +4173,13 @@
         <v>10</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C125" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>27</v>
@@ -4181,13 +4190,13 @@
         <v>10</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>27</v>
@@ -4198,13 +4207,13 @@
         <v>10</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C127" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>27</v>
@@ -4215,13 +4224,13 @@
         <v>10</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C128" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>27</v>
@@ -4232,7 +4241,7 @@
         <v>10</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C129" s="11" t="s">
         <v>25</v>
@@ -4249,13 +4258,13 @@
         <v>10</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C130" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>27</v>
@@ -4266,13 +4275,13 @@
         <v>10</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C131" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>27</v>
@@ -4283,13 +4292,13 @@
         <v>10</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>27</v>
@@ -4300,13 +4309,13 @@
         <v>10</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C133" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>27</v>
@@ -4317,13 +4326,13 @@
         <v>10</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>27</v>
@@ -4334,13 +4343,13 @@
         <v>10</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C135" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>27</v>
@@ -4351,13 +4360,13 @@
         <v>10</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>27</v>
@@ -4368,13 +4377,13 @@
         <v>10</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C137" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>27</v>
@@ -4385,13 +4394,13 @@
         <v>10</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>27</v>
@@ -4402,13 +4411,13 @@
         <v>10</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C139" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>27</v>
@@ -4419,13 +4428,13 @@
         <v>10</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>27</v>
@@ -4436,13 +4445,13 @@
         <v>10</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>27</v>
@@ -4453,13 +4462,13 @@
         <v>10</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C142" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>27</v>
@@ -4470,7 +4479,7 @@
         <v>10</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>25</v>
@@ -4487,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>25</v>
@@ -4504,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>25</v>
@@ -4521,7 +4530,7 @@
         <v>10</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>25</v>
@@ -4538,7 +4547,7 @@
         <v>10</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>25</v>
@@ -4555,7 +4564,7 @@
         <v>10</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>25</v>
@@ -4572,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>25</v>
@@ -4589,7 +4598,7 @@
         <v>10</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>25</v>
@@ -4606,7 +4615,7 @@
         <v>10</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C151" s="11" t="s">
         <v>25</v>
@@ -4623,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C152" s="11" t="s">
         <v>25</v>
@@ -4640,7 +4649,7 @@
         <v>10</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C153" s="11" t="s">
         <v>25</v>
@@ -4657,7 +4666,7 @@
         <v>10</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>25</v>
@@ -4674,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C155" s="11" t="s">
         <v>25</v>
@@ -4691,7 +4700,7 @@
         <v>10</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C156" s="11" t="s">
         <v>25</v>
@@ -4708,7 +4717,7 @@
         <v>10</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>25</v>
@@ -4725,7 +4734,7 @@
         <v>10</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>25</v>
@@ -4742,7 +4751,7 @@
         <v>10</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C159" s="11" t="s">
         <v>25</v>
@@ -4759,7 +4768,7 @@
         <v>10</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>25</v>
@@ -4776,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>25</v>
@@ -4793,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>25</v>
@@ -4810,7 +4819,7 @@
         <v>10</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>25</v>
@@ -4827,7 +4836,7 @@
         <v>10</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>25</v>
@@ -4844,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>25</v>
@@ -4861,7 +4870,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>25</v>
@@ -4878,7 +4887,7 @@
         <v>10</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>25</v>
@@ -4895,7 +4904,7 @@
         <v>10</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>25</v>
@@ -4912,7 +4921,7 @@
         <v>10</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>25</v>
@@ -4929,7 +4938,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>25</v>
@@ -4946,7 +4955,7 @@
         <v>10</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>25</v>
@@ -4963,7 +4972,7 @@
         <v>10</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>25</v>
@@ -4980,7 +4989,7 @@
         <v>10</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>25</v>
@@ -4997,7 +5006,7 @@
         <v>10</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>25</v>
@@ -5014,7 +5023,7 @@
         <v>10</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>25</v>
@@ -5031,7 +5040,7 @@
         <v>10</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>25</v>
@@ -5048,7 +5057,7 @@
         <v>10</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>25</v>
@@ -5065,7 +5074,7 @@
         <v>10</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>25</v>
@@ -5082,7 +5091,7 @@
         <v>10</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>25</v>
@@ -5099,7 +5108,7 @@
         <v>10</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>25</v>
@@ -5116,7 +5125,7 @@
         <v>10</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>25</v>
@@ -5133,7 +5142,7 @@
         <v>10</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>25</v>
@@ -5150,7 +5159,7 @@
         <v>10</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C183" s="11" t="s">
         <v>25</v>
@@ -5167,7 +5176,7 @@
         <v>10</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>25</v>
@@ -5184,7 +5193,7 @@
         <v>10</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>25</v>
@@ -5201,7 +5210,7 @@
         <v>10</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>25</v>
@@ -5218,7 +5227,7 @@
         <v>10</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>25</v>
@@ -5235,7 +5244,7 @@
         <v>10</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>25</v>
@@ -5252,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>25</v>
@@ -5269,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>25</v>
@@ -5286,7 +5295,7 @@
         <v>10</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C191" s="11" t="s">
         <v>25</v>
@@ -5303,7 +5312,7 @@
         <v>10</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>25</v>
@@ -5320,7 +5329,7 @@
         <v>10</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>25</v>
@@ -5337,7 +5346,7 @@
         <v>10</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>25</v>
@@ -5354,7 +5363,7 @@
         <v>10</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>25</v>
@@ -5371,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>25</v>
@@ -5388,7 +5397,7 @@
         <v>10</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>25</v>
@@ -5405,7 +5414,7 @@
         <v>10</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>25</v>
@@ -5422,7 +5431,7 @@
         <v>10</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>25</v>
@@ -5439,7 +5448,7 @@
         <v>10</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>25</v>
@@ -5456,7 +5465,7 @@
         <v>10</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>25</v>
@@ -5473,7 +5482,7 @@
         <v>10</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>25</v>
@@ -5490,7 +5499,7 @@
         <v>10</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>25</v>
@@ -5507,7 +5516,7 @@
         <v>10</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>25</v>
@@ -5524,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>25</v>
@@ -5541,7 +5550,7 @@
         <v>10</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>25</v>
@@ -5558,7 +5567,7 @@
         <v>10</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>25</v>
@@ -5575,7 +5584,7 @@
         <v>10</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>25</v>
@@ -5592,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>25</v>
@@ -5609,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>25</v>
@@ -5626,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C211" s="11" t="s">
         <v>25</v>
@@ -5643,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>25</v>
@@ -5660,7 +5669,7 @@
         <v>10</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>25</v>
@@ -5677,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C214" s="11" t="s">
         <v>25</v>
@@ -5694,7 +5703,7 @@
         <v>10</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C215" s="11" t="s">
         <v>25</v>
@@ -5711,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>25</v>
@@ -5728,7 +5737,7 @@
         <v>10</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C217" s="11" t="s">
         <v>25</v>
@@ -5745,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>25</v>
@@ -5762,7 +5771,7 @@
         <v>10</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>25</v>
@@ -5779,7 +5788,7 @@
         <v>10</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C220" s="11" t="s">
         <v>25</v>
@@ -5796,7 +5805,7 @@
         <v>10</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C221" s="11" t="s">
         <v>25</v>
@@ -5813,7 +5822,7 @@
         <v>12</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C222" s="11" t="s">
         <v>25</v>
@@ -5830,7 +5839,7 @@
         <v>12</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C223" s="11" t="s">
         <v>25</v>
@@ -5847,7 +5856,7 @@
         <v>12</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C224" s="11" t="s">
         <v>25</v>
@@ -5864,7 +5873,7 @@
         <v>12</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C225" s="11" t="s">
         <v>25</v>
@@ -5881,7 +5890,7 @@
         <v>12</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C226" s="11" t="s">
         <v>25</v>
@@ -5898,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C227" s="11" t="s">
         <v>25</v>
@@ -5915,7 +5924,7 @@
         <v>12</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C228" s="11" t="s">
         <v>25</v>
@@ -5932,7 +5941,7 @@
         <v>12</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C229" s="11" t="s">
         <v>25</v>
@@ -5949,7 +5958,7 @@
         <v>12</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C230" s="11" t="s">
         <v>25</v>
@@ -5966,7 +5975,7 @@
         <v>12</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C231" s="11" t="s">
         <v>25</v>
@@ -5983,7 +5992,7 @@
         <v>12</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C232" s="11" t="s">
         <v>25</v>
@@ -6000,7 +6009,7 @@
         <v>12</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C233" s="11" t="s">
         <v>25</v>
@@ -6017,7 +6026,7 @@
         <v>12</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C234" s="11" t="s">
         <v>25</v>
@@ -6034,7 +6043,7 @@
         <v>12</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C235" s="11" t="s">
         <v>25</v>
@@ -6051,7 +6060,7 @@
         <v>12</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C236" s="11" t="s">
         <v>25</v>
@@ -6068,7 +6077,7 @@
         <v>12</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C237" s="11" t="s">
         <v>25</v>
@@ -6085,7 +6094,7 @@
         <v>12</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C238" s="11" t="s">
         <v>25</v>
@@ -6102,7 +6111,7 @@
         <v>12</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C239" s="11" t="s">
         <v>25</v>
@@ -6119,7 +6128,7 @@
         <v>12</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C240" s="11" t="s">
         <v>25</v>
@@ -6136,7 +6145,7 @@
         <v>12</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C241" s="11" t="s">
         <v>25</v>
@@ -6153,7 +6162,7 @@
         <v>12</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C242" s="11" t="s">
         <v>25</v>
@@ -6170,7 +6179,7 @@
         <v>12</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C243" s="11" t="s">
         <v>25</v>
@@ -6187,7 +6196,7 @@
         <v>12</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C244" s="11" t="s">
         <v>25</v>
@@ -6204,7 +6213,7 @@
         <v>12</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C245" s="11" t="s">
         <v>25</v>
@@ -6221,7 +6230,7 @@
         <v>12</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C246" s="11" t="s">
         <v>25</v>
@@ -6238,7 +6247,7 @@
         <v>12</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C247" s="11" t="s">
         <v>25</v>
@@ -6255,7 +6264,7 @@
         <v>12</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C248" s="11" t="s">
         <v>25</v>
@@ -6272,7 +6281,7 @@
         <v>12</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C249" s="11" t="s">
         <v>25</v>
@@ -6289,7 +6298,7 @@
         <v>12</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C250" s="11" t="s">
         <v>25</v>
@@ -6306,7 +6315,7 @@
         <v>12</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C251" s="11" t="s">
         <v>25</v>
@@ -6323,7 +6332,7 @@
         <v>12</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C252" s="11" t="s">
         <v>25</v>
@@ -6340,7 +6349,7 @@
         <v>12</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C253" s="11" t="s">
         <v>25</v>
@@ -6357,7 +6366,7 @@
         <v>12</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C254" s="11" t="s">
         <v>25</v>
@@ -6374,7 +6383,7 @@
         <v>12</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C255" s="11" t="s">
         <v>25</v>
@@ -6391,7 +6400,7 @@
         <v>12</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C256" s="11" t="s">
         <v>25</v>
@@ -6408,7 +6417,7 @@
         <v>12</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C257" s="11" t="s">
         <v>25</v>
@@ -6425,7 +6434,7 @@
         <v>12</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C258" s="11" t="s">
         <v>25</v>
@@ -6442,7 +6451,7 @@
         <v>12</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C259" s="11" t="s">
         <v>25</v>
@@ -6459,7 +6468,7 @@
         <v>12</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C260" s="11" t="s">
         <v>25</v>
@@ -6476,7 +6485,7 @@
         <v>12</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C261" s="11" t="s">
         <v>25</v>
@@ -6493,7 +6502,7 @@
         <v>12</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C262" s="11" t="s">
         <v>25</v>
@@ -6510,7 +6519,7 @@
         <v>12</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C263" s="11" t="s">
         <v>25</v>
@@ -6527,7 +6536,7 @@
         <v>12</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C264" s="11" t="s">
         <v>25</v>
@@ -6544,7 +6553,7 @@
         <v>12</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C265" s="11" t="s">
         <v>25</v>
@@ -6561,7 +6570,7 @@
         <v>12</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C266" s="11" t="s">
         <v>25</v>
@@ -6578,7 +6587,7 @@
         <v>12</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C267" s="11" t="s">
         <v>25</v>
@@ -6595,7 +6604,7 @@
         <v>12</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C268" s="11" t="s">
         <v>25</v>
@@ -6612,7 +6621,7 @@
         <v>12</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C269" s="11" t="s">
         <v>25</v>
@@ -6629,7 +6638,7 @@
         <v>12</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C270" s="11" t="s">
         <v>25</v>
@@ -6646,7 +6655,7 @@
         <v>12</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C271" s="11" t="s">
         <v>25</v>
@@ -6663,7 +6672,7 @@
         <v>12</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C272" s="11" t="s">
         <v>25</v>
@@ -6680,7 +6689,7 @@
         <v>12</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C273" s="11" t="s">
         <v>25</v>
@@ -6697,7 +6706,7 @@
         <v>12</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C274" s="11" t="s">
         <v>25</v>
@@ -6714,7 +6723,7 @@
         <v>12</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C275" s="11" t="s">
         <v>25</v>
@@ -6731,7 +6740,7 @@
         <v>12</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C276" s="11" t="s">
         <v>25</v>
@@ -6748,7 +6757,7 @@
         <v>12</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C277" s="11" t="s">
         <v>25</v>
@@ -6765,7 +6774,7 @@
         <v>12</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C278" s="11" t="s">
         <v>25</v>
@@ -6782,7 +6791,7 @@
         <v>12</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C279" s="11" t="s">
         <v>25</v>
@@ -6799,7 +6808,7 @@
         <v>12</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C280" s="11" t="s">
         <v>25</v>
@@ -6816,7 +6825,7 @@
         <v>12</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C281" s="11" t="s">
         <v>25</v>
@@ -6833,7 +6842,7 @@
         <v>12</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C282" s="11" t="s">
         <v>25</v>
@@ -6850,7 +6859,7 @@
         <v>12</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C283" s="11" t="s">
         <v>25</v>
@@ -6867,7 +6876,7 @@
         <v>12</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C284" s="11" t="s">
         <v>25</v>
@@ -6884,7 +6893,7 @@
         <v>12</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C285" s="11" t="s">
         <v>25</v>
@@ -6901,7 +6910,7 @@
         <v>12</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C286" s="11" t="s">
         <v>25</v>
@@ -6918,7 +6927,7 @@
         <v>12</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C287" s="11" t="s">
         <v>25</v>
@@ -6935,7 +6944,7 @@
         <v>12</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C288" s="11" t="s">
         <v>25</v>
@@ -6952,7 +6961,7 @@
         <v>12</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C289" s="11" t="s">
         <v>25</v>
@@ -6969,7 +6978,7 @@
         <v>12</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C290" s="11" t="s">
         <v>25</v>
@@ -6986,7 +6995,7 @@
         <v>12</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C291" s="11" t="s">
         <v>25</v>
@@ -7003,7 +7012,7 @@
         <v>12</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C292" s="11" t="s">
         <v>25</v>
@@ -7020,7 +7029,7 @@
         <v>12</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C293" s="11" t="s">
         <v>25</v>
@@ -7037,7 +7046,7 @@
         <v>12</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C294" s="11" t="s">
         <v>25</v>
@@ -7054,7 +7063,7 @@
         <v>12</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C295" s="11" t="s">
         <v>25</v>
@@ -7071,7 +7080,7 @@
         <v>12</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C296" s="11" t="s">
         <v>25</v>
@@ -7088,7 +7097,7 @@
         <v>12</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C297" s="11" t="s">
         <v>25</v>
@@ -7105,7 +7114,7 @@
         <v>12</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C298" s="11" t="s">
         <v>25</v>
@@ -7122,7 +7131,7 @@
         <v>12</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C299" s="11" t="s">
         <v>25</v>
@@ -7139,7 +7148,7 @@
         <v>12</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C300" s="11" t="s">
         <v>25</v>
@@ -7156,7 +7165,7 @@
         <v>12</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C301" s="11" t="s">
         <v>25</v>
@@ -7173,7 +7182,7 @@
         <v>12</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C302" s="11" t="s">
         <v>25</v>
@@ -7190,7 +7199,7 @@
         <v>12</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C303" s="11" t="s">
         <v>25</v>
@@ -7207,7 +7216,7 @@
         <v>12</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C304" s="11" t="s">
         <v>25</v>
@@ -7224,7 +7233,7 @@
         <v>12</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C305" s="11" t="s">
         <v>25</v>
@@ -7241,7 +7250,7 @@
         <v>12</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C306" s="11" t="s">
         <v>25</v>
@@ -7258,7 +7267,7 @@
         <v>12</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C307" s="11" t="s">
         <v>25</v>
@@ -7275,7 +7284,7 @@
         <v>12</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C308" s="11" t="s">
         <v>25</v>
@@ -7292,7 +7301,7 @@
         <v>12</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C309" s="11" t="s">
         <v>25</v>
@@ -7309,7 +7318,7 @@
         <v>12</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C310" s="11" t="s">
         <v>25</v>
@@ -7326,7 +7335,7 @@
         <v>12</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C311" s="11" t="s">
         <v>25</v>
@@ -7343,7 +7352,7 @@
         <v>12</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C312" s="11" t="s">
         <v>25</v>
@@ -7360,7 +7369,7 @@
         <v>12</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C313" s="11" t="s">
         <v>25</v>
@@ -7377,7 +7386,7 @@
         <v>12</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C314" s="11" t="s">
         <v>25</v>
@@ -7394,7 +7403,7 @@
         <v>12</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C315" s="11" t="s">
         <v>25</v>
@@ -7411,7 +7420,7 @@
         <v>12</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C316" s="11" t="s">
         <v>25</v>
@@ -7428,7 +7437,7 @@
         <v>12</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C317" s="11" t="s">
         <v>25</v>
@@ -7445,7 +7454,7 @@
         <v>12</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C318" s="11" t="s">
         <v>25</v>
@@ -7462,7 +7471,7 @@
         <v>12</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C319" s="11" t="s">
         <v>25</v>
@@ -7479,7 +7488,7 @@
         <v>12</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C320" s="11" t="s">
         <v>25</v>
@@ -7496,7 +7505,7 @@
         <v>12</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C321" s="11" t="s">
         <v>25</v>
@@ -7513,13 +7522,13 @@
         <v>14</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C322" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D322" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E322" s="10" t="s">
         <v>27</v>
@@ -7530,13 +7539,13 @@
         <v>14</v>
       </c>
       <c r="B323" s="10" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C323" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D323" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E323" s="10" t="s">
         <v>27</v>
@@ -7547,13 +7556,13 @@
         <v>14</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C324" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D324" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E324" s="10" t="s">
         <v>27</v>
@@ -7564,13 +7573,13 @@
         <v>14</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C325" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D325" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E325" s="10" t="s">
         <v>27</v>
@@ -7581,13 +7590,13 @@
         <v>14</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C326" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D326" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E326" s="10" t="s">
         <v>27</v>
@@ -7598,13 +7607,13 @@
         <v>14</v>
       </c>
       <c r="B327" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C327" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D327" s="12" t="s">
         <v>373</v>
-      </c>
-      <c r="C327" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D327" s="12" t="s">
-        <v>368</v>
       </c>
       <c r="E327" s="10" t="s">
         <v>27</v>
@@ -7615,13 +7624,13 @@
         <v>14</v>
       </c>
       <c r="B328" s="10" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C328" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D328" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E328" s="10" t="s">
         <v>27</v>
@@ -7632,13 +7641,13 @@
         <v>14</v>
       </c>
       <c r="B329" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C329" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D329" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E329" s="10" t="s">
         <v>27</v>
@@ -7649,7 +7658,7 @@
         <v>14</v>
       </c>
       <c r="B330" s="10" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C330" s="11" t="s">
         <v>25</v>
@@ -7666,7 +7675,7 @@
         <v>14</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C331" s="11" t="s">
         <v>25</v>
@@ -7683,13 +7692,13 @@
         <v>14</v>
       </c>
       <c r="B332" s="10" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C332" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D332" s="12" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E332" s="10" t="s">
         <v>27</v>
@@ -7700,7 +7709,7 @@
         <v>14</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C333" s="11" t="s">
         <v>25</v>
@@ -7717,13 +7726,13 @@
         <v>14</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C334" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D334" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E334" s="10" t="s">
         <v>27</v>
@@ -7734,13 +7743,13 @@
         <v>14</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C335" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D335" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E335" s="10" t="s">
         <v>27</v>
@@ -7751,13 +7760,13 @@
         <v>14</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C336" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D336" s="12" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E336" s="10" t="s">
         <v>27</v>
@@ -7768,7 +7777,7 @@
         <v>14</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C337" s="11" t="s">
         <v>25</v>
@@ -7785,7 +7794,7 @@
         <v>14</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C338" s="11" t="s">
         <v>25</v>
@@ -7802,13 +7811,13 @@
         <v>14</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C339" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D339" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E339" s="10" t="s">
         <v>27</v>
@@ -7819,13 +7828,13 @@
         <v>14</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C340" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D340" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E340" s="10" t="s">
         <v>27</v>
@@ -7836,13 +7845,13 @@
         <v>14</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C341" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D341" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E341" s="10" t="s">
         <v>27</v>
@@ -7853,13 +7862,13 @@
         <v>14</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C342" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D342" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E342" s="10" t="s">
         <v>27</v>
@@ -7870,7 +7879,7 @@
         <v>14</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C343" s="11" t="s">
         <v>25</v>
@@ -7887,7 +7896,7 @@
         <v>14</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C344" s="11" t="s">
         <v>25</v>
@@ -7904,7 +7913,7 @@
         <v>14</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C345" s="11" t="s">
         <v>25</v>
@@ -7921,7 +7930,7 @@
         <v>14</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C346" s="11" t="s">
         <v>25</v>
@@ -7938,7 +7947,7 @@
         <v>14</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C347" s="11" t="s">
         <v>25</v>
@@ -7955,7 +7964,7 @@
         <v>14</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C348" s="11" t="s">
         <v>25</v>
@@ -7972,7 +7981,7 @@
         <v>14</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C349" s="11" t="s">
         <v>25</v>
@@ -7989,13 +7998,13 @@
         <v>14</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C350" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E350" s="10" t="s">
         <v>27</v>
@@ -8006,7 +8015,7 @@
         <v>14</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C351" s="11" t="s">
         <v>25</v>
@@ -8023,13 +8032,13 @@
         <v>14</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C352" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E352" s="10" t="s">
         <v>27</v>
@@ -8040,7 +8049,7 @@
         <v>14</v>
       </c>
       <c r="B353" s="10" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C353" s="11" t="s">
         <v>25</v>
@@ -8057,13 +8066,13 @@
         <v>14</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C354" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E354" s="10" t="s">
         <v>27</v>
@@ -8074,13 +8083,13 @@
         <v>14</v>
       </c>
       <c r="B355" s="10" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C355" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E355" s="10" t="s">
         <v>27</v>
@@ -8091,13 +8100,13 @@
         <v>14</v>
       </c>
       <c r="B356" s="10" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C356" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E356" s="10" t="s">
         <v>27</v>
@@ -8108,13 +8117,13 @@
         <v>14</v>
       </c>
       <c r="B357" s="10" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C357" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E357" s="10" t="s">
         <v>27</v>
@@ -8125,13 +8134,13 @@
         <v>14</v>
       </c>
       <c r="B358" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C358" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E358" s="10" t="s">
         <v>27</v>
@@ -8142,7 +8151,7 @@
         <v>14</v>
       </c>
       <c r="B359" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C359" s="11" t="s">
         <v>25</v>
@@ -8159,13 +8168,13 @@
         <v>14</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C360" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E360" s="10" t="s">
         <v>27</v>
@@ -8176,7 +8185,7 @@
         <v>14</v>
       </c>
       <c r="B361" s="10" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C361" s="11" t="s">
         <v>25</v>
@@ -8193,13 +8202,13 @@
         <v>14</v>
       </c>
       <c r="B362" s="10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C362" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D362" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E362" s="10" t="s">
         <v>27</v>
@@ -8210,7 +8219,7 @@
         <v>14</v>
       </c>
       <c r="B363" s="10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C363" s="11" t="s">
         <v>25</v>
@@ -8227,7 +8236,7 @@
         <v>14</v>
       </c>
       <c r="B364" s="10" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C364" s="11" t="s">
         <v>25</v>
@@ -8244,13 +8253,13 @@
         <v>14</v>
       </c>
       <c r="B365" s="10" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C365" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E365" s="10" t="s">
         <v>27</v>
@@ -8261,13 +8270,13 @@
         <v>14</v>
       </c>
       <c r="B366" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C366" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E366" s="10" t="s">
         <v>27</v>
@@ -8278,13 +8287,13 @@
         <v>14</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C367" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E367" s="10" t="s">
         <v>27</v>
@@ -8295,7 +8304,7 @@
         <v>14</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C368" s="11" t="s">
         <v>25</v>
@@ -8312,13 +8321,13 @@
         <v>14</v>
       </c>
       <c r="B369" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C369" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E369" s="10" t="s">
         <v>27</v>
@@ -8329,13 +8338,13 @@
         <v>14</v>
       </c>
       <c r="B370" s="10" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C370" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D370" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E370" s="10" t="s">
         <v>27</v>
@@ -8346,13 +8355,13 @@
         <v>14</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C371" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D371" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E371" s="10" t="s">
         <v>27</v>
@@ -8363,13 +8372,13 @@
         <v>14</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C372" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D372" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E372" s="10" t="s">
         <v>27</v>
@@ -8380,7 +8389,7 @@
         <v>14</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C373" s="11" t="s">
         <v>25</v>
@@ -8397,13 +8406,13 @@
         <v>14</v>
       </c>
       <c r="B374" s="10" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C374" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D374" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E374" s="10" t="s">
         <v>27</v>
@@ -8414,7 +8423,7 @@
         <v>14</v>
       </c>
       <c r="B375" s="10" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C375" s="11" t="s">
         <v>25</v>
@@ -8431,13 +8440,13 @@
         <v>14</v>
       </c>
       <c r="B376" s="10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C376" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D376" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E376" s="10" t="s">
         <v>27</v>
@@ -8448,13 +8457,13 @@
         <v>14</v>
       </c>
       <c r="B377" s="10" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C377" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D377" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E377" s="10" t="s">
         <v>27</v>
@@ -8465,7 +8474,7 @@
         <v>14</v>
       </c>
       <c r="B378" s="10" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C378" s="11" t="s">
         <v>25</v>
@@ -8482,13 +8491,13 @@
         <v>14</v>
       </c>
       <c r="B379" s="10" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C379" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D379" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E379" s="10" t="s">
         <v>27</v>
@@ -8499,7 +8508,7 @@
         <v>14</v>
       </c>
       <c r="B380" s="10" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C380" s="11" t="s">
         <v>25</v>
@@ -8516,13 +8525,13 @@
         <v>14</v>
       </c>
       <c r="B381" s="10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C381" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D381" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E381" s="10" t="s">
         <v>27</v>
@@ -8533,7 +8542,7 @@
         <v>14</v>
       </c>
       <c r="B382" s="10" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C382" s="11" t="s">
         <v>25</v>
@@ -8550,13 +8559,13 @@
         <v>14</v>
       </c>
       <c r="B383" s="10" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C383" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D383" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E383" s="10" t="s">
         <v>27</v>
@@ -8567,13 +8576,13 @@
         <v>14</v>
       </c>
       <c r="B384" s="10" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C384" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D384" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E384" s="10" t="s">
         <v>27</v>
@@ -8584,7 +8593,7 @@
         <v>14</v>
       </c>
       <c r="B385" s="10" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C385" s="11" t="s">
         <v>25</v>
@@ -8601,7 +8610,7 @@
         <v>14</v>
       </c>
       <c r="B386" s="10" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C386" s="11" t="s">
         <v>25</v>
@@ -8618,13 +8627,13 @@
         <v>14</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C387" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D387" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E387" s="10" t="s">
         <v>27</v>
@@ -8635,7 +8644,7 @@
         <v>14</v>
       </c>
       <c r="B388" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C388" s="11" t="s">
         <v>25</v>
@@ -8652,7 +8661,7 @@
         <v>14</v>
       </c>
       <c r="B389" s="10" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C389" s="11" t="s">
         <v>25</v>
@@ -8669,13 +8678,13 @@
         <v>14</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C390" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D390" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E390" s="10" t="s">
         <v>27</v>
@@ -8686,13 +8695,13 @@
         <v>14</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C391" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D391" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E391" s="10" t="s">
         <v>27</v>
@@ -8703,13 +8712,13 @@
         <v>14</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C392" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D392" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E392" s="10" t="s">
         <v>27</v>
@@ -8720,13 +8729,13 @@
         <v>14</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C393" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E393" s="10" t="s">
         <v>27</v>
@@ -8737,13 +8746,13 @@
         <v>14</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C394" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E394" s="10" t="s">
         <v>27</v>
@@ -8754,7 +8763,7 @@
         <v>14</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C395" s="11" t="s">
         <v>25</v>
@@ -8771,13 +8780,13 @@
         <v>14</v>
       </c>
       <c r="B396" s="10" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C396" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D396" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E396" s="10" t="s">
         <v>27</v>
@@ -8788,7 +8797,7 @@
         <v>14</v>
       </c>
       <c r="B397" s="10" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C397" s="11" t="s">
         <v>25</v>
@@ -8805,13 +8814,13 @@
         <v>14</v>
       </c>
       <c r="B398" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C398" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D398" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E398" s="10" t="s">
         <v>27</v>
@@ -8822,7 +8831,7 @@
         <v>14</v>
       </c>
       <c r="B399" s="10" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C399" s="11" t="s">
         <v>25</v>
@@ -8839,13 +8848,13 @@
         <v>14</v>
       </c>
       <c r="B400" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C400" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D400" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E400" s="10" t="s">
         <v>27</v>
@@ -8856,7 +8865,7 @@
         <v>14</v>
       </c>
       <c r="B401" s="10" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C401" s="11" t="s">
         <v>25</v>
@@ -8873,7 +8882,7 @@
         <v>14</v>
       </c>
       <c r="B402" s="10" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C402" s="11" t="s">
         <v>25</v>
@@ -8890,13 +8899,13 @@
         <v>14</v>
       </c>
       <c r="B403" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C403" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D403" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E403" s="10" t="s">
         <v>27</v>
@@ -8907,7 +8916,7 @@
         <v>14</v>
       </c>
       <c r="B404" s="10" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C404" s="11" t="s">
         <v>25</v>
@@ -8924,13 +8933,13 @@
         <v>14</v>
       </c>
       <c r="B405" s="10" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C405" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D405" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E405" s="10" t="s">
         <v>27</v>
@@ -8941,7 +8950,7 @@
         <v>14</v>
       </c>
       <c r="B406" s="10" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C406" s="11" t="s">
         <v>25</v>
@@ -8958,13 +8967,13 @@
         <v>14</v>
       </c>
       <c r="B407" s="10" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C407" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D407" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E407" s="10" t="s">
         <v>27</v>
@@ -8975,13 +8984,13 @@
         <v>14</v>
       </c>
       <c r="B408" s="10" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C408" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D408" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E408" s="10" t="s">
         <v>27</v>
@@ -8992,13 +9001,13 @@
         <v>14</v>
       </c>
       <c r="B409" s="10" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C409" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D409" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E409" s="10" t="s">
         <v>27</v>
@@ -9009,13 +9018,13 @@
         <v>14</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C410" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D410" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E410" s="10" t="s">
         <v>27</v>
@@ -9026,13 +9035,13 @@
         <v>14</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C411" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D411" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E411" s="10" t="s">
         <v>27</v>
@@ -9043,7 +9052,7 @@
         <v>14</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C412" s="11" t="s">
         <v>25</v>
@@ -9060,7 +9069,7 @@
         <v>14</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C413" s="11" t="s">
         <v>25</v>
@@ -9077,13 +9086,13 @@
         <v>14</v>
       </c>
       <c r="B414" s="10" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C414" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D414" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E414" s="10" t="s">
         <v>27</v>
@@ -9094,7 +9103,7 @@
         <v>14</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C415" s="11" t="s">
         <v>25</v>
@@ -9111,13 +9120,13 @@
         <v>14</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C416" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D416" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E416" s="10" t="s">
         <v>27</v>
@@ -9128,13 +9137,13 @@
         <v>14</v>
       </c>
       <c r="B417" s="10" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C417" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D417" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E417" s="10" t="s">
         <v>27</v>
@@ -9145,7 +9154,7 @@
         <v>14</v>
       </c>
       <c r="B418" s="10" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C418" s="11" t="s">
         <v>25</v>
@@ -9162,13 +9171,13 @@
         <v>14</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C419" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D419" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E419" s="10" t="s">
         <v>27</v>
@@ -9179,13 +9188,13 @@
         <v>14</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C420" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D420" s="12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E420" s="10" t="s">
         <v>27</v>
@@ -9196,13 +9205,13 @@
         <v>14</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C421" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D421" s="12" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E421" s="10" t="s">
         <v>27</v>
